--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -83,6 +83,156 @@
 "Insofern glaube ich als Ständerat, dass wir nicht Dinge, die in der Vernehmlassung sind, quasi im Expresstempo in einen Bundesbeschluss schreiben sollten."
 Je suis d'accord avec vous sur le fait qu'un objet en consultation doit suivre son cours normal et que nous ne devrions pas anticiper des résultats pas encore issus de la procédure ordinaire. Dès lors, si à l'issue de la procédure de consultation sur la modification des valeurs limites, le Conseil fédéral modifie cette dernière, l'OSAV procédera évidemment à l'adaptation de ces directives. Ce n'est pas à nous, ce n'est pas au Parlement, d'anticiper le résultat d'une consultation et l'adoption de la loi spéciale par le Conseil fédéral, au contraire, ce serait un signal extrêmement singulier.
 Dès lors, je vous invite à ne pas anticiper les résultats de la consultation de cette loi spéciale, à laisser le processus démocratique se dérouler et à rejeter la motion Würth. Si les valeurs limites des PFAS doivent être changées, elles le seront dans le temps ordinaire de la procédure législative.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Büchel Roland Rino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die SVP-Fraktion wird auf die Vorlage eintreten. Es geht um unsere Unternehmen, es geht um unsere Arbeitsplätze, es geht um Zölle; es geht nicht darum, die Welt zu retten. Mercosur umfasst 270 Millionen Menschen. Die Schweiz exportiert bereits heute Waren im Wert von mehr als 4 Milliarden Franken jährlich in die Mercosur-Länder. Mit dem Abkommen sollen rund 96 Prozent unserer Ausfuhren nach Ablauf der vorgesehenen Übergangsfrist zollfrei werden. Das eröffnet unseren Unternehmen zusätzliche Markt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die SVP-Fraktion wird auf die Vorlage eintreten. Es geht um unsere Unternehmen, es geht um unsere Arbeitsplätze, es geht um Zölle; es geht nicht darum, die Welt zu retten. Mercosur umfasst 270 Millionen Menschen. Die Schweiz exportiert bereits heute Waren im Wert von mehr als 4 Milliarden Franken jährlich in die Mercosur-Länder. Mit dem Abkommen sollen rund 96 Prozent unserer Ausfuhren nach Ablauf der vorgesehenen Übergangsfrist zollfrei werden. Das eröffnet unseren Unternehmen zusätzliche Marktchancen und ermöglicht Zollersparnisse von über 155 Millionen Franken pro Jahr. 
+Gerade für ein kleines, international ausgerichtetes Land wie die Schweiz ist der Zugang zu ausländischen Märkten von zentraler Bedeutung. Wir können es uns nicht leisten, uns in wichtigen Märkten ins Abseits zu manövrieren, während andere Wirtschaftsräume ihre Beziehungen ausbauen. Natürlich gibt es berechtigte Fragen zur Landwirtschaft. Das müssen wir sehr ernst nehmen. Die SVP-Fraktion nimmt das ernst. Entscheidend ist für uns deshalb die Frage, wie wir mit den möglichen Auswirkungen auf die Landwirtschaft umgehen. Hier liegt gegenüber der ursprünglichen Vorlage inzwischen eine Lösung auf dem Tisch. Der Ständerat hat insgesamt 517 Millionen Franken für flankierende Massnahmen beschlossen; Sie haben das auch schon gehört. Vorgesehen sind insbesondere Mittel zur Verbesserung der Wettbewerbsfähigkeit der Landwirtschaft, darunter Investitionskredite und Beiträge zur Absatzförderung. Das ist ein erheblicher Betrag. Es geht darum, unseren Landwirtschaftsbetrieben Investitionen, Anpassungen und eine Stärkung ihrer Wettbewerbsfähigkeit zu ermöglichen. 
+Für eine vernünftige Wirtschaftspolitik gehört Folgendes zusammen: offene Märkte für unsere exportorientierte Wirtschaft und verlässliche Rahmenbedingungen für unsere Landwirtschaft. Wir sollten die Diskussion über Mercosur auch deshalb nüchtern führen. Es geht um Marktzugang, wirtschaftliche Chancen, konkrete Agrarkontingente und die Abgeltung für die Landwirtschaft. Es geht um weniger "tariffs" - das ist ja der Begriff, den wir kennen - für die EFTA-Länder. Zu Recht wurde gesagt, wir seien mit Südamerika zum Teil auf Trump-Niveau; davon müssen wir wegkommen. Es geht um Arbeitsplätze im Jura. Es geht um Arbeitsplätze im Sankt-Galler Rheintal. Es geht um Arbeitsplätze im Fürstentum Liechtenstein. Es geht um Arbeitsplätze in unserem Land. Es geht um Arbeitsplätze in den angrenzenden Ländern - im angrenzenden Ländle auch. Es geht um Arbeitsplätze in den mit uns via EFTA verbundenen Ländern Island und Norwegen. Nur: Sie können das Abkommen in Kraft setzen, auch wenn wir Nein stimmen, und sie werden das Abkommen in Kraft setzen, auch wenn wir es nicht tun. Meine Damen und Herren gerade von der Opposition: wollen wir die letzten Mohikaner sein, die mit Mercosur kein Abkommen abschliessen? Wollen Sie das ernsthaft? Wollen Sie die Landwirtschaft plagen? Wollen Sie die Arbeitsplätze gefährden? 
+Der Ständerat ist zu durchaus vernünftigen Schlüssen gekommen. Die SVP-Fraktion wird diese unterstützen und nicht das fantasievolle Durcheinander inklusive Millionenraubzug auf die Steuergelder, welches Ihnen von der Aussenpolitischen Kommission des Nationalrates, teils in der Minderheit und teils in der Mehrheit, präsentiert worden ist. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stettler Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le président de la Confédération, les importations actuelles de viande sont inférieures aux quantités concédées dans l'accord, si bien que l'équilibre ne devrait pas être ébranlé et que les prix aux producteurs devraient être maintenus. Cela m'encourage plutôt à soutenir cet accord. Qu'en serait-il si la consommation indigène devait s'effondrer, comme cela a été le cas au moment de la crise de la vache folle ? Pouvez-vous me rassurer sur cet élément ?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dobler Loïc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imaginez : vous voudriez vivre dans votre propre appartement avec le soutien dont vous avez besoin au quotidien, mais ce soutien n'existe pas, ou pas assez. Alors, c'est dans un foyer ou une institution que vous devez vivre, pas parce que vous l'avez choisi, mais parce que personne ne vous a donné le choix. Ce ne sont pas des cas isolés ; c'est le quotidien de milliers de personnes en Suisse aujourd'hui. Douze ans après avoir ratifié la Convention de l'ONU relative aux droits des personnes handi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imaginez : vous voudriez vivre dans votre propre appartement avec le soutien dont vous avez besoin au quotidien, mais ce soutien n'existe pas, ou pas assez. Alors, c'est dans un foyer ou une institution que vous devez vivre, pas parce que vous l'avez choisi, mais parce que personne ne vous a donné le choix. Ce ne sont pas des cas isolés ; c'est le quotidien de milliers de personnes en Suisse aujourd'hui. Douze ans après avoir ratifié la Convention de l'ONU relative aux droits des personnes handicapées, nous en sommes encore là.
+Alors, chers et chers collègues, la question qui nous est posée aujourd'hui tient en un mot : l'autodétermination. Décider soi-même où l'on vit, décider soi-même comment on vit ; décider soi-même où l'on travaille, où l'on se cultive, où l'on se divertit. Ce n'est pas un supplément d'âme qu'on accorde quand le budget le permet. C'est un droit fondamental. Or, un droit fondamental, cela ne se négocie pas.
+C'est pourquoi nous soutenons l'initiative pour l'inclusion. Parce qu'elle inscrit dans notre Constitution ce que la loi seule ne garantit pas : une égalité effective, un droit au soutien nécessaire, et la liberté de choisir sa vie. Une loi, une majorité peut la défaire ; un droit constitutionnel, on le protège. Nous soutenons tout autant le contre-projet indirect du Conseil fédéral. La commission a choisi de le renforcer encore sur plusieurs points essentiels. C'est ce travail qu'il faut défendre aujourd'hui devant notre conseil.
+Regardons ce qui est sur la table, dans les domaines du travail et de la formation d'abord. Aujourd'hui encore, trop de personnes en situation de handicap n'accèdent pas à un emploi qui correspond à leurs compétences, parce que la transition depuis une institution se heurte à des obstacles administratifs, à un manque d'accompagnement, à des mesures de soutien insuffisantes. Le texte propose des structures plus souples, moins de bureaucratie, des conditions-cadres plus fiables, autant pour les salariés que pour les employeurs, jusqu'à 90 heures d'assistance par mois pour garder un emploi, et une protection contre la discrimination qui couvre enfin tous les rapports de travail, de l'embauche au salaire en passant par la formation continue. Pour que le parcours ne s'arrête plus faute de possibilités adaptées, le texte encourage aussi des formations ciblées et une meilleure représentation des personnes concernées au sein des commissions qui préparent nos décisions.
+Dans le domaine du logement, ensuite, les personnes en situation de handicap doivent pouvoir décider elles-mêmes où, comment et avec qui elles vivent. Le texte encourage le logement autonome et revalorise l'assistance qui rend cette vie autonome possible au quotidien.
+Dans le domaine de l'accès aux services et à la vie sociale, enfin, les entreprises privées et les services numériques devront être conçus pour être accessibles à toutes et tous. Le sport, la culture, les loisirs ne doivent plus rester des privilèges réservés à celles et ceux qui n'ont pas de handicap. Pour que personne ne renonce à un appareillage faute de moyens, l'assurance-invalidité obtient enfin les leviers pour peser sur les prix des moyens auxiliaires techniques.
+Ce ne sont pas des lignes budgétaires ; ce sont des vies qui changent. On ne devrait jamais avoir à demander la permission de vivre sa propre vie. Décider où l'on habite, avec qui, comment on travaille ; ce n'est pas un privilège qu'on accorde, c'est un droit qu'on doit garantir. Tant qu'il ne l'est pas pour tout le monde, il ne l'est vraiment pour personne.
+Oui, des minorités voudront renier ces avancées, une par une, sous prétexte de coûts ou de complexité. À chacune de ces minorités, notre réponse sera la même : non à l'affaiblissement de la protection contre la discrimination, non à la réduction des prestations d'assistance, non aux restrictions sur le libre choix du logement. Il y a un principe que nous ne devons jamais perdre de vue dans ce débat : ce ne sont pas les autorités ni les institutions qui doivent décider à la place des personnes en situation de handicap. C'est à elles de décider pour elles-mêmes. Défendons le travail accompli par la commission, et votons en fin de course pour l'initiative comme pour ce contre-projet renforcé. Il est temps que l'autodétermination que l'on promet depuis douze ans devienne une réalité.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broulis Pascal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nous traitons aujourd'hui un dossier qui touche à la sécurité de notre pays. Cette première modification de la loi sur le renseignement (LRens) va dans la bonne direction. Deux autres paquets de modifications sont encore prévus. Ils seront présentés prochainement. L'un d'entre eux est en consultation et le suivant traitera de ce qui touche au Tribunal administratif fédéral, avec des modifications légales.
+Cette modification n'est pas trop rapide, car la géopolitique a changé. Les blocs politique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nous traitons aujourd'hui un dossier qui touche à la sécurité de notre pays. Cette première modification de la loi sur le renseignement (LRens) va dans la bonne direction. Deux autres paquets de modifications sont encore prévus. Ils seront présentés prochainement. L'un d'entre eux est en consultation et le suivant traitera de ce qui touche au Tribunal administratif fédéral, avec des modifications légales.
+Cette modification n'est pas trop rapide, car la géopolitique a changé. Les blocs politiques sont en train d'évoluer. Les outils de renseignement, d'écoute, d'espionnage, ainsi que l'avènement et le renforcement de l'utilisation de l'IA nous obligent à réagir. Nous avons une responsabilité vis-à-vis de notre population. On le voit avec certaines informations ou renseignements mal utilisés ou pas utilisés du tout, comme avec l'attentat du 7 octobre en Israël. Ils sont en pleine campagne électorale. Est-ce vrai ou pas ? Le gouvernement israélien était-il au courant des attentats qui se préparaient ? Acte potentiel de terrorisme : on sait qu'à l'échelle internationale, d'autres pays nous renseignent. Il nous semble important de pouvoir se coordonner et d'anticiper ces différents aspects.
+Le renforcement du Service de renseignement de la Confédération (SRC) est fondamental pour détecter précocement les menaces. Il en va de notre devoir d'anticiper. Comme on dit : mieux vaut prévenir que guérir. Nous devrons veiller à mettre en place des garde-fous supplémentaires et des voies de droit. Le projet va dans ce sens. En cas de besoin, la loi pourra toujours être adaptée et corrigée.
+Je ne vais pas commenter tout le projet de loi, qui me convient globalement, mais me concentrer, dans ce débat d'entrée en matière, sur quelques éléments qui concernent les cantons. La capacité opérationnelle des autorités cantonales d'exécution reste insuffisante dans le projet du Conseil fédéral. Dans un contexte sécuritaire qui se dégrade, les services de renseignement cantonaux constituent un maillage essentiel du renseignement en Suisse. À ce propos, pour ceux qui s'en souviennent, en ce qui concerne l'attentat qui a conduit à un meurtre à Morges, on ne sait toujours pas si le canton était au courant ou pas. L'échelon fédéral a-t-il correctement informé les cantons ? Des enquêtes sont toujours en cours. On voit que le maillage cantons-Confédération est important, surtout pour les cantons qui ont des services organisés principalement en lien avec la police.
+Dans un contexte sécuritaire qui se dégrade, les services de renseignement cantonaux constituent donc un maillage essentiel à l'échelle suisse. Il est ainsi nécessaire que les acteurs cantonaux disposent de moyens suffisants pour effectuer leur travail. Les services cantonaux fournissent le gros du travail de surveillance et assurent la recherche d'informations sur le territoire suisse ; informations qui profitent au SRC.
+C'est pourquoi j'ai déposé en commission des propositions visant à maintenir la capacité opérationnelle des services de renseignement cantonaux. Le principe de ces propositions est soutenu par de nombreux cantons, dont les cantons de Vaud, du Jura, du Valais, de Berne, d'Argovie, de Thurgovie, du Tessin, de Genève, voire de Fribourg. La première proposition - j'y reviendrai dans le cadre de la discussion par article - permet de prévoir une exploitation technique réaliste des appareils de localisation lors d'observations, y compris pour les services de renseignement cantonaux. La deuxième proposition permet de garantir le traitement des données personnelles et le profilage par les autorités cantonales d'exécution. En commission, on m'a dit que c'était implicite, mais, dans le domaine du renseignement, il est parfois mieux de l'indiquer dans la loi.
+Je vous encourage à entrer en matière, à soutenir le Conseil fédéral et ensuite à adopter mes deux propositions de minorité.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notre Commission des affaires juridiques a examiné le protocole d'amendement à la Convention d'établissement conclue entre la Suisse et l'Iran lors de sa séance du 26 juin dernier et l'a approuvé.
+La Suisse a conclu la présente convention d'établissement avec l'Iran, alors l'Empire de Perse, en 1934. Cette convention prévoyait, pour ce qui concerne le droit des personnes et de la famille, ainsi que le droit successoral, que ce soit le droit iranien qui s'applique aux ressortissants en Suisse. El</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notre Commission des affaires juridiques a examiné le protocole d'amendement à la Convention d'établissement conclue entre la Suisse et l'Iran lors de sa séance du 26 juin dernier et l'a approuvé.
+La Suisse a conclu la présente convention d'établissement avec l'Iran, alors l'Empire de Perse, en 1934. Cette convention prévoyait, pour ce qui concerne le droit des personnes et de la famille, ainsi que le droit successoral, que ce soit le droit iranien qui s'applique aux ressortissants en Suisse. Elle contient en outre des mesures de protection pour les ressortissants et ressortissantes de chacun des deux États et règle, entre autres, la liberté de voyager et le droit d'exercer un travail. Or, l'application du droit de la famille iranien dans notre pays est problématique pour la justice suisse, ainsi qu'en regard des droits fondamentaux. Certaines des dispositions du droit iranien de la famille sont incompatibles avec l'ordre public et donc inapplicables, ce qui entraîne une insécurité juridique. Il engendre également une inégalité de traitement par rapport au reste de la population résidente, a priori soumise au droit de l'État de domicile.
+Signé à Téhéran le 18 décembre 2024 et adopté par le Conseil fédéral le 19 décembre 2025, le protocole d'amendement qui nous est soumis aujourd'hui supprime les dispositions relatives au droit applicable contenues à l'article 8 de la convention. Dès lors, les ressortissants et ressortissantes de nationalité iranienne en Suisse seront soumis aux règles du droit international privé et aux conventions de La Haye en matière de protection de l'enfant et de l'adulte, ainsi que notamment sur les obligations alimentaires. Les règles internationales renvoient au droit en vigueur au lieu de domicile et de résidence et c'est donc le droit suisse qui s'appliquera dorénavant. L'amendement à la convention concernera potentiellement plusieurs milliers de personnes de nationalité iranienne en Suisse. Jusqu'à présent, les dispositions de la convention renvoyaient au droit iranien, par exemple pour ce qui concerne les conditions de divorce ou encore la garde et l'entretien des enfants, lorsque l'ensemble des personnes concernées étaient iraniennes. D'une part, cela soulevait des questions légitimes en matière de droit des personnes. D'autre part, dans la pratique, les tribunaux suisses renonçaient fréquemment à appliquer ce droit au motif de la réserve de l'ordre public. À l'inverse, très peu de personnes de nationalité suisse sont actuellement établies en Iran : moins de 10 selon les informations reçues par la commission, hormis le personnel diplomatique. Pour ces personnes, il est toutefois à relever que l'Iran applique déjà à l'heure actuelle le droit de l'État d'origine dans les cas relevant de la famille et des successions.
+Lors de la consultation, le protocole d'amendement a été approuvé à l'unanimité, quelques participants déplorant toutefois le temps qui a été nécessaire pour aboutir à ce résultat. À noter également que la Convention d'établissement conclue entre la Suisse et l'Iran a donné lieu à plusieurs interventions parlementaires par le passé, qui dénonçaient l'applicabilité d'un droit national peu compatible avec les valeurs de la Suisse. Le présent amendement résout ce problème tout en maintenant les acquis de la convention dans d'autres domaines qui contribuent à la stabilité des relations entre la Suisse et l'Iran.
+En un mot commençant, le protocole d'amendement à la Convention d'établissement conclue entre la Suisse et l'Iran améliore notablement la sécurité juridique et les droits fondamentaux des personnes concernées. La Commission des affaires juridiques a salué ces améliorations, relevant qu'au regard de la dégradation des droits fondamentaux depuis la signature de la convention en 1934, en particulier des droits des femmes, il était plus que temps de placer les ressortissants et ressortissantes iraniens établis en Suisse sous la protection du droit suisse des personnes, de la famille et des successions. La commission salue également les négociations menées par la Suisse pour parvenir à ce résultat.
+Elle est donc entrée en matière sans opposition et a approuvé à l'unanimité l'arrêté fédéral portant approbation du protocole d'amendement et vous invite à en faire de même.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juillard Charles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je prendrai exactement le même exemple que notre collègue présidente de la Délégation des Commissions de gestion (DélCdG), mais pour vous dire de soutenir la proposition de la minorité de la commission. Faisons de la politique fiction ; imaginons qu'un parti gouvernemental de notre pays soit tout à coup infiltré par des éléments extrémistes provenant de l'étranger qui seraient susceptibles de prendre à contre-pied la politique menée par notre pays ou par ce parti même au sein du Conseil fédéral,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je prendrai exactement le même exemple que notre collègue présidente de la Délégation des Commissions de gestion (DélCdG), mais pour vous dire de soutenir la proposition de la minorité de la commission. Faisons de la politique fiction ; imaginons qu'un parti gouvernemental de notre pays soit tout à coup infiltré par des éléments extrémistes provenant de l'étranger qui seraient susceptibles de prendre à contre-pied la politique menée par notre pays ou par ce parti même au sein du Conseil fédéral, et qui seraient susceptibles de mettre en danger l'ordre politique et juridique suisses. En tant que responsable de ce parti, je serais très content que le Service de renseignement de la Confédération (SRC) s'y intéresse et puisse nous prévenir en nous informant que nous avons un problème, un risque, qu'il y a une suspicion qui pourrait nous mettre en danger et nous mettre en porte-à-faux avec la Constitution de ce pays. C'est la raison pour laquelle je soutiens la proposition de la minorité Gmür-Schönenberger à l'article 5 alinéa 6 lettre c, qui permettrait précisément au SRC de protéger cette organisation contre son avis, peut-être, ou en l'absence de son avis, parce qu'elle n'est pas consciente du risque qu'elle encourt. Par le biais de cette disposition, avec toutes les restrictions qui sont contenues dans la loi et qui sont justifiées dans un État de droit, je serais content, en tant que responsable de cette organisation, que quelqu'un m'avertisse qu'un risque est encouru par mon organisation.
+C'est la raison pour laquelle je vous invite vraiment à soutenir la proposition de la minorité Gmür-Schönenberger, selon le projet du Conseil fédéral.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma motion porte sur un sujet encore trop peu visible, à mon avis, dans le débat public, mais qui concerne directement la sécurité de notre pays, de notre économie et de nos infrastructures. Nous parlons aujourd'hui de cryptographie post-quantique. Cela peut sembler très technique, mais en réalité, derrière ce terme se cache une question très simple : comment garantir que les données et les communications que nous protégeons aujourd'hui resteront protégées demain.
+Notre société repose sur la cryp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma motion porte sur un sujet encore trop peu visible, à mon avis, dans le débat public, mais qui concerne directement la sécurité de notre pays, de notre économie et de nos infrastructures. Nous parlons aujourd'hui de cryptographie post-quantique. Cela peut sembler très technique, mais en réalité, derrière ce terme se cache une question très simple : comment garantir que les données et les communications que nous protégeons aujourd'hui resteront protégées demain.
+Notre société repose sur la cryptographie. Les paiements électroniques, les communications de l'administration, les dossiers médicaux, les identités numériques, les signatures électroniques, les systèmes industriels ou encore les infrastructures critiques dépendent tous, à des degrés divers, de mécanismes cryptographiques. Or, certains des algorithmes de cryptographie à clé publique que nous utilisons actuellement pourraient être rendus vulnérables par des ordinateurs quantiques suffisamment puissants.
+Le problème est que nous ne pouvons pas attendre le jour où un ordinateur quantique capable de casser ses protections sera disponible pour commencer à agir. Pourquoi cela ? Parce que la migration cryptographique est un processus long, complexe et coûteux. Il faut identifier les systèmes concernés, comprendre leurs dépendances, vérifier les logiciels et les équipements, travailler avec les fournisseurs, tester les nouveaux mécanismes, garantir l'interopérabilité et, dans certains cas, remplacer des systèmes qui ont une durée de vie de dix, vingt ou trente ans. Autrement dit, le moment d'agir est avant que la menace ne devienne opérationnelle.
+Il existe également un risque, déjà présent aujourd'hui, de "moissonner maintenant pour déchiffrer plus tard". Des données peuvent être capturées aujourd'hui alors qu'elles sont encore correctement protégées. Si leurs valeurs ou leur caractère confidentiel perdurent pendant dix, vingt ou trente ans, elles pourraient être déchiffrées à l'avenir lorsque les capacités technologiques le permettront. Cela concerne notamment les informations de l'État, les données médicales, les données de recherche, les secrets industriels ou certaines informations liées à la sécurité nationale. Nous devons donc raisonner non seulement en fonction de la menace actuelle, mais aussi de la durée pendant laquelle une information doit rester confidentielle.
+C'est précisément ce que vise ma motion : ne pas céder à la panique et ne pas imposer une technologie particulière, mais planifier la transition de manière progressive, coordonnée et fondée sur les risques. C'est un élément essentiel. Sans inventaire, nous ne pouvons pas piloter correctement une migration. C'est pourquoi la notion de crypto-agilité est particulièrement importante. Nos systèmes doivent être conçus de manière à pouvoir faire évoluer leurs mécanismes cryptographiques sans devoir tout reconstruire à chaque changement de standard.
+C'est une question de cybersécurité, mais également une question de bonne gestion des deniers publics. Si une migration anticipée peut être planifiée, une migration imposée dans l'urgence risque quant à elle d'être beaucoup plus coûteuse, plus complexe et beaucoup plus risquée. La Suisse ne part heureusement pas de zéro. La Confédération a déjà identifié cette problématique et dispose de compétences importantes dans le domaine de la cybersécurité et de l'informatique. Ce qui manque encore, c'est précisément une vision nationale, commune, avec des responsabilités, des priorités et des échéances clairement définies.
+Nos partenaires internationaux avancent : l'Union européenne travaille sur la transition vers la cryptographie post-quantique, et les États-Unis, le Royaume-Uni, la France et l'Allemagne ont également engagé des démarches. La motion prévoit à juste titre des échéances différenciées, une priorité aux cas à haut risque d'ici 2030, puis une transition progressive des autres systèmes critiques ou sensibles d'ici 2035 en fonction de la maturité des standards et de l'interopérabilité. Cette approche permet d'éviter deux erreurs. La première serait de ne rien faire en attendant que la menace soit certaine. La seconde serait d'imposer aujourd'hui des investissements massifs dans des technologies qui pourraient encore évoluer. La bonne réponse se situe entre les deux : préparer maintenant, migrer progressivement et adapter les exigences sur le plan des risques.
+Permettez-moi de revenir encore quelques instants sur l'avis du Conseil fédéral. Il reconnait l'importance du sujet et je l'en remercie, mais il rejette le point relatif au soutien aux cantons, aux PME, aux entreprises et aux hautes écoles au motif que certaines mesures dépasseraient les compétences actuelles de la Confédération. Je me rallie à sa proposition et ne conteste pas le rejet de la lettre i. Je souhaite néanmoins, pour la clarté des délibérations et la mise en oeuvre à venir, préciser l'esprit de cette lettre i. Mon intention n'a jamais été de créer une compétence fédérale nouvelle ni de transférer à la Confédération une responsabilité qui incombe aux cantons, aux entreprises et aux hautes écoles en matière de cybersécurité, car la responsabilité individuelle de chaque acteur demeure entière. Sur ce point, je partage entièrement l'analyse du Conseil fédéral.
+Ce que visait la lettre i, c'est la coordination et non le soutien financier. Une transition vers la cryptographie post-quantique, conduite en ordre dispersé, sans référentiel commun ni interopérabilité, coûterait beaucoup plus cher à tous et affaiblirait la sécurité de l'ensemble. Je prends donc acte du fait que le Conseil fédéral, dans le cadre de ses compétences, assurera cette coordination, avec la mise à disposition de lignes directrices, de modèles d'inventaire, de tests d'interopérabilité et de retours d'expériences utiles aux cantons et à l'économie. Je forme le voeu que le rapport biennal, prévu à la lettre c, rende compte de la manière dont cette coordination est assurée afin que le Parlement puisse en suivre les effets.
+En résumé et pour conclure, la cryptographie post-quantique n'est peut-être pas encore une urgence visible pour la population. Mais précisément parce que la transition prendra du temps, il est nécessaire d'agir aujourd'hui avant que cela ne devienne une urgence.
+Je vous invite donc à soutenir ma motion sans la lettre i, comme demandé par le Conseil fédéral, et je vous en remercie.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sans trop rallonger, je voudrais vous dire que si vous soutenez la minorité Hurni, vous aurez une première solution qui pourra être débattue soit par la commission du Conseil national soit par notre Commission des affaires juridiques, qui pourrait entretemps y réfléchir. Si nous refusons cette proposition de minorité, nous n'aurons rien pour régler ce problème qui est pourtant clair, évident, qui a été soulevé ici et où il y a vraiment une nécessité d'agir. La résolution du problème sera donc re</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sans trop rallonger, je voudrais vous dire que si vous soutenez la minorité Hurni, vous aurez une première solution qui pourra être débattue soit par la commission du Conseil national soit par notre Commission des affaires juridiques, qui pourrait entretemps y réfléchir. Si nous refusons cette proposition de minorité, nous n'aurons rien pour régler ce problème qui est pourtant clair, évident, qui a été soulevé ici et où il y a vraiment une nécessité d'agir. La résolution du problème sera donc reportée aux calendes grecques. Excusez l'expression !
+Donc, je crois qu'il faut prendre ce que l'on a. Comme un bon tiens vaut mieux que deux tu l'auras, je vous invite aujourd'hui, parce qu'il y a un vrai problème, à soutenir ce que vous propose la minorité de la commission, quitte à peut-être améliorer cette solution à un autre moment. Mais au moins, on aura déjà fait un pas dans la bonne direction.
+Il s'agit d'une situation qui est quand même particulière. Comme on l'a dit, c'est dans un avion et pas dans un restaurant, ou sur la route où l'on peut s'arrêter pour faire venir les agents de la force publique. Il y a une question de protection des passagers mais, plus globalement, de sécurité dans l'avion, qu'il faut pouvoir régler. C'est pour cela que, à mon avis, il faut offrir cette protection au personnel qui travaille dans les avions et soutenir la minorité Hurni.
 </t>
   </si>
 </sst>
@@ -137,8 +287,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I3" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I11" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I11"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -523,6 +673,238 @@
         <v>17</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -107,10 +107,10 @@
     <t xml:space="preserve">Die SVP-Fraktion wird auf die Vorlage eintreten. Es geht um unsere Unternehmen, es geht um unsere Arbeitsplätze, es geht um Zölle; es geht nicht darum, die Welt zu retten. Mercosur umfasst 270 Millionen Menschen. Die Schweiz exportiert bereits heute Waren im Wert von mehr als 4 Milliarden Franken jährlich in die Mercosur-Länder. Mit dem Abkommen sollen rund 96 Prozent unserer Ausfuhren nach Ablauf der vorgesehenen Übergangsfrist zollfrei werden. Das eröffnet unseren Unternehmen zusätzliche Markt</t>
   </si>
   <si>
-    <t xml:space="preserve">Die SVP-Fraktion wird auf die Vorlage eintreten. Es geht um unsere Unternehmen, es geht um unsere Arbeitsplätze, es geht um Zölle; es geht nicht darum, die Welt zu retten. Mercosur umfasst 270 Millionen Menschen. Die Schweiz exportiert bereits heute Waren im Wert von mehr als 4 Milliarden Franken jährlich in die Mercosur-Länder. Mit dem Abkommen sollen rund 96 Prozent unserer Ausfuhren nach Ablauf der vorgesehenen Übergangsfrist zollfrei werden. Das eröffnet unseren Unternehmen zusätzliche Marktchancen und ermöglicht Zollersparnisse von über 155 Millionen Franken pro Jahr. 
-Gerade für ein kleines, international ausgerichtetes Land wie die Schweiz ist der Zugang zu ausländischen Märkten von zentraler Bedeutung. Wir können es uns nicht leisten, uns in wichtigen Märkten ins Abseits zu manövrieren, während andere Wirtschaftsräume ihre Beziehungen ausbauen. Natürlich gibt es berechtigte Fragen zur Landwirtschaft. Das müssen wir sehr ernst nehmen. Die SVP-Fraktion nimmt das ernst. Entscheidend ist für uns deshalb die Frage, wie wir mit den möglichen Auswirkungen auf die Landwirtschaft umgehen. Hier liegt gegenüber der ursprünglichen Vorlage inzwischen eine Lösung auf dem Tisch. Der Ständerat hat insgesamt 517 Millionen Franken für flankierende Massnahmen beschlossen; Sie haben das auch schon gehört. Vorgesehen sind insbesondere Mittel zur Verbesserung der Wettbewerbsfähigkeit der Landwirtschaft, darunter Investitionskredite und Beiträge zur Absatzförderung. Das ist ein erheblicher Betrag. Es geht darum, unseren Landwirtschaftsbetrieben Investitionen, Anpassungen und eine Stärkung ihrer Wettbewerbsfähigkeit zu ermöglichen. 
-Für eine vernünftige Wirtschaftspolitik gehört Folgendes zusammen: offene Märkte für unsere exportorientierte Wirtschaft und verlässliche Rahmenbedingungen für unsere Landwirtschaft. Wir sollten die Diskussion über Mercosur auch deshalb nüchtern führen. Es geht um Marktzugang, wirtschaftliche Chancen, konkrete Agrarkontingente und die Abgeltung für die Landwirtschaft. Es geht um weniger "tariffs" - das ist ja der Begriff, den wir kennen - für die EFTA-Länder. Zu Recht wurde gesagt, wir seien mit Südamerika zum Teil auf Trump-Niveau; davon müssen wir wegkommen. Es geht um Arbeitsplätze im Jura. Es geht um Arbeitsplätze im Sankt-Galler Rheintal. Es geht um Arbeitsplätze im Fürstentum Liechtenstein. Es geht um Arbeitsplätze in unserem Land. Es geht um Arbeitsplätze in den angrenzenden Ländern - im angrenzenden Ländle auch. Es geht um Arbeitsplätze in den mit uns via EFTA verbundenen Ländern Island und Norwegen. Nur: Sie können das Abkommen in Kraft setzen, auch wenn wir Nein stimmen, und sie werden das Abkommen in Kraft setzen, auch wenn wir es nicht tun. Meine Damen und Herren gerade von der Opposition: wollen wir die letzten Mohikaner sein, die mit Mercosur kein Abkommen abschliessen? Wollen Sie das ernsthaft? Wollen Sie die Landwirtschaft plagen? Wollen Sie die Arbeitsplätze gefährden? 
-Der Ständerat ist zu durchaus vernünftigen Schlüssen gekommen. Die SVP-Fraktion wird diese unterstützen und nicht das fantasievolle Durcheinander inklusive Millionenraubzug auf die Steuergelder, welches Ihnen von der Aussenpolitischen Kommission des Nationalrates, teils in der Minderheit und teils in der Mehrheit, präsentiert worden ist. 
+    <t xml:space="preserve">Die SVP-Fraktion wird auf die Vorlage eintreten. Es geht um unsere Unternehmen, es geht um unsere Arbeitsplätze, es geht um Zölle; es geht nicht darum, die Welt zu retten. Mercosur umfasst 270 Millionen Menschen. Die Schweiz exportiert bereits heute Waren im Wert von mehr als 4 Milliarden Franken jährlich in die Mercosur-Länder. Mit dem Abkommen sollen rund 96 Prozent unserer Ausfuhren nach Ablauf der vorgesehenen Übergangsfrist zollfrei werden. Das eröffnet unseren Unternehmen zusätzliche Marktchancen und ermöglicht Zollersparnisse von über 155 Millionen Franken pro Jahr.
+Gerade für ein kleines, international ausgerichtetes Land wie die Schweiz ist der Zugang zu ausländischen Märkten von zentraler Bedeutung. Wir können es uns nicht leisten, uns in wichtigen Märkten ins Abseits zu manövrieren, während andere Wirtschaftsräume ihre Beziehungen ausbauen. Natürlich gibt es berechtigte Fragen zur Landwirtschaft; diese müssen wir sehr ernst nehmen. Die SVP-Fraktion nimmt sie ernst. Entscheidend ist für uns deshalb die Frage, wie wir mit den möglichen Auswirkungen auf die Landwirtschaft umgehen. Hier liegt gegenüber der ursprünglichen Vorlage inzwischen eine Lösung auf dem Tisch. Der Ständerat hat insgesamt 517 Millionen Franken für flankierende Massnahmen beschlossen; Sie haben das auch schon gehört. Vorgesehen sind insbesondere Mittel zur Verbesserung der Wettbewerbsfähigkeit der Landwirtschaft, darunter Investitionskredite und Beiträge zur Absatzförderung. Das ist ein erheblicher Betrag. Es geht darum, unseren Landwirtschaftsbetrieben Investitionen, Anpassungen und eine Stärkung ihrer Wettbewerbsfähigkeit zu ermöglichen.
+Für eine vernünftige Wirtschaftspolitik gehört Folgendes zusammen: offene Märkte für unsere exportorientierte Wirtschaft und verlässliche Rahmenbedingungen für unsere Landwirtschaft. Wir sollten die Diskussion über Mercosur auch deshalb nüchtern führen. Es geht um Marktzugang, wirtschaftliche Chancen, konkrete Agrarkontingente und die Abgeltung für die Landwirtschaft. Es geht um weniger "tariffs" - das ist ja der Begriff, den wir kennen - für die EFTA-Länder. Zu Recht wurde gesagt, wir seien mit Südamerika zum Teil auf Trump-Niveau; davon müssen wir wegkommen. Es geht um Arbeitsplätze im Jura. Es geht um Arbeitsplätze im St. Galler Rheintal. Es geht um Arbeitsplätze im Fürstentum Liechtenstein. Es geht um Arbeitsplätze in unserem Land. Es geht um Arbeitsplätze in den angrenzenden Ländern - auch im angrenzenden Ländle. Es geht um Arbeitsplätze in den mit uns via EFTA verbundenen Ländern Island und Norwegen. Nur: Sie können das Abkommen in Kraft setzen, auch wenn wir Nein stimmen, und sie werden das Abkommen in Kraft setzen, auch wenn wir es nicht tun. Meine Damen und Herren gerade von der Opposition: Wollen wir die letzten Mohikaner sein, die mit Mercosur kein Abkommen abschliessen? Wollen Sie das ernsthaft? Wollen Sie die Landwirtschaft plagen? Wollen Sie die Arbeitsplätze gefährden?
+Der Ständerat ist zu durchaus vernünftigen Schlüssen gekommen. Die SVP-Fraktion wird diese unterstützen und nicht das fantasievolle Durcheinander, inklusive Millionenraubzug auf die Steuergelder, das Ihnen von der Aussenpolitischen Kommission des Nationalrates, teils in der Minderheit und teils in der Mehrheit, präsentiert worden ist.
 </t>
   </si>
   <si>
@@ -134,13 +134,13 @@
   </si>
   <si>
     <t xml:space="preserve">Imaginez : vous voudriez vivre dans votre propre appartement avec le soutien dont vous avez besoin au quotidien, mais ce soutien n'existe pas, ou pas assez. Alors, c'est dans un foyer ou une institution que vous devez vivre, pas parce que vous l'avez choisi, mais parce que personne ne vous a donné le choix. Ce ne sont pas des cas isolés ; c'est le quotidien de milliers de personnes en Suisse aujourd'hui. Douze ans après avoir ratifié la Convention de l'ONU relative aux droits des personnes handicapées, nous en sommes encore là.
-Alors, chers et chers collègues, la question qui nous est posée aujourd'hui tient en un mot : l'autodétermination. Décider soi-même où l'on vit, décider soi-même comment on vit ; décider soi-même où l'on travaille, où l'on se cultive, où l'on se divertit. Ce n'est pas un supplément d'âme qu'on accorde quand le budget le permet. C'est un droit fondamental. Or, un droit fondamental, cela ne se négocie pas.
+Alors, la question qui nous est posée aujourd'hui tient en un mot : l'autodétermination. Décider soi-même où l'on vit. Décider soi-même comment on vit. Décider soi-même où l'on travaille, où l'on se cultive, où l'on se divertit. Ce n'est pas un supplément d'âme qu'on accorde quand le budget le permet. C'est un droit fondamental. Or, un droit fondamental, cela ne se négocie pas.
 C'est pourquoi nous soutenons l'initiative pour l'inclusion. Parce qu'elle inscrit dans notre Constitution ce que la loi seule ne garantit pas : une égalité effective, un droit au soutien nécessaire, et la liberté de choisir sa vie. Une loi, une majorité peut la défaire ; un droit constitutionnel, on le protège. Nous soutenons tout autant le contre-projet indirect du Conseil fédéral. La commission a choisi de le renforcer encore sur plusieurs points essentiels. C'est ce travail qu'il faut défendre aujourd'hui devant notre conseil.
-Regardons ce qui est sur la table, dans les domaines du travail et de la formation d'abord. Aujourd'hui encore, trop de personnes en situation de handicap n'accèdent pas à un emploi qui correspond à leurs compétences, parce que la transition depuis une institution se heurte à des obstacles administratifs, à un manque d'accompagnement, à des mesures de soutien insuffisantes. Le texte propose des structures plus souples, moins de bureaucratie, des conditions-cadres plus fiables, autant pour les salariés que pour les employeurs, jusqu'à 90 heures d'assistance par mois pour garder un emploi, et une protection contre la discrimination qui couvre enfin tous les rapports de travail, de l'embauche au salaire en passant par la formation continue. Pour que le parcours ne s'arrête plus faute de possibilités adaptées, le texte encourage aussi des formations ciblées et une meilleure représentation des personnes concernées au sein des commissions qui préparent nos décisions.
+Regardons ce qui est sur la table, dans les domaines du travail et de la formation d'abord. Aujourd'hui encore, trop de personnes en situation de handicap n'accèdent pas à un emploi qui correspond à leurs compétences, parce que la transition depuis une institution se heurte à des obstacles administratifs, à un manque d'accompagnement, à des mesures de soutien insuffisantes. Le texte propose des structures plus souples, moins de bureaucratie, des conditions-cadres plus fiables autant pour les salariés que pour les employeurs, jusqu'à 90 heures d'assistance par mois pour garder un emploi, et une protection contre la discrimination qui couvre enfin tous les aspects des rapports de travail, de l'embauche au salaire en passant par la formation continue. Pour que le parcours ne s'arrête plus faute de possibilités adaptées, le texte encourage aussi des formations ciblées et une meilleure représentation des personnes concernées au sein des commissions qui préparent nos décisions.
 Dans le domaine du logement, ensuite, les personnes en situation de handicap doivent pouvoir décider elles-mêmes où, comment et avec qui elles vivent. Le texte encourage le logement autonome et revalorise l'assistance qui rend cette vie autonome possible au quotidien.
 Dans le domaine de l'accès aux services et à la vie sociale, enfin, les entreprises privées et les services numériques devront être conçus pour être accessibles à toutes et tous. Le sport, la culture, les loisirs ne doivent plus rester des privilèges réservés à celles et ceux qui n'ont pas de handicap. Pour que personne ne renonce à un appareillage faute de moyens, l'assurance-invalidité obtient enfin les leviers pour peser sur les prix des moyens auxiliaires techniques.
-Ce ne sont pas des lignes budgétaires ; ce sont des vies qui changent. On ne devrait jamais avoir à demander la permission de vivre sa propre vie. Décider où l'on habite, avec qui, comment on travaille ; ce n'est pas un privilège qu'on accorde, c'est un droit qu'on doit garantir. Tant qu'il ne l'est pas pour tout le monde, il ne l'est vraiment pour personne.
-Oui, des minorités voudront renier ces avancées, une par une, sous prétexte de coûts ou de complexité. À chacune de ces minorités, notre réponse sera la même : non à l'affaiblissement de la protection contre la discrimination, non à la réduction des prestations d'assistance, non aux restrictions sur le libre choix du logement. Il y a un principe que nous ne devons jamais perdre de vue dans ce débat : ce ne sont pas les autorités ni les institutions qui doivent décider à la place des personnes en situation de handicap. C'est à elles de décider pour elles-mêmes. Défendons le travail accompli par la commission, et votons en fin de course pour l'initiative comme pour ce contre-projet renforcé. Il est temps que l'autodétermination que l'on promet depuis douze ans devienne une réalité.
+Ce ne sont pas des lignes budgétaires ; ce sont des vies qui changent. On ne devrait jamais avoir à demander la permission de vivre sa propre vie. Décider où l'on habite, avec qui, comment on travaille : ce n'est pas un privilège qu'on accorde, c'est un droit que l'on doit garantir. Tant qu'il ne l'est pas pour tout le monde, il ne l'est vraiment pour personne.
+Oui, des minorités voudront renier ces avancées, une par une, sous prétexte de coûts ou de complexité. À chacune de ces minorités, notre réponse sera la même : non à l'affaiblissement de la protection contre la discrimination, non à la réduction des prestations d'assistance, non aux restrictions sur le libre choix du logement. Il y a un principe que nous ne devons jamais perdre de vue dans ce débat : ce ne sont pas les autorités ni les institutions qui doivent décider à la place des personnes en situation de handicap. C'est à elles de décider pour elles-mêmes. Défendons le travail accompli par la commission, et votons en fin de course en faveur de l'initiative comme de ce contre-projet renforcé. Il est temps que l'autodétermination que l'on promet depuis douze ans devienne une réalité.
 </t>
   </si>
   <si>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -233,6 +233,28 @@
     <t xml:space="preserve">Sans trop rallonger, je voudrais vous dire que si vous soutenez la minorité Hurni, vous aurez une première solution qui pourra être débattue soit par la commission du Conseil national soit par notre Commission des affaires juridiques, qui pourrait entretemps y réfléchir. Si nous refusons cette proposition de minorité, nous n'aurons rien pour régler ce problème qui est pourtant clair, évident, qui a été soulevé ici et où il y a vraiment une nécessité d'agir. La résolution du problème sera donc reportée aux calendes grecques. Excusez l'expression !
 Donc, je crois qu'il faut prendre ce que l'on a. Comme un bon tiens vaut mieux que deux tu l'auras, je vous invite aujourd'hui, parce qu'il y a un vrai problème, à soutenir ce que vous propose la minorité de la commission, quitte à peut-être améliorer cette solution à un autre moment. Mais au moins, on aura déjà fait un pas dans la bonne direction.
 Il s'agit d'une situation qui est quand même particulière. Comme on l'a dit, c'est dans un avion et pas dans un restaurant, ou sur la route où l'on peut s'arrêter pour faire venir les agents de la force publique. Il y a une question de protection des passagers mais, plus globalement, de sécurité dans l'avion, qu'il faut pouvoir régler. C'est pour cela que, à mon avis, il faut offrir cette protection au personnel qui travaille dans les avions et soutenir la minorité Hurni.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madame Amaudruz, vous évoquez à juste titre l'aspect de cette réforme relatif à l'indemnisation de l'assurance-chômage. Je ne vous ai pas entendu par exemple vous insurger du fait que, pour l'AVS également, les frontaliers sont indemnisés de la même manière que les résidents suisses puisqu'ils ont cotisé en Suisse. Ce combat semble un peu perdu d'avance, parce qu'il n'est pas lié à l'Union européenne, mais à l'OCDE, qui a des principes par rapport à cela. (Remarque intermédiaire du président : A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madame Amaudruz, vous évoquez à juste titre l'aspect de cette réforme relatif à l'indemnisation de l'assurance-chômage. Je ne vous ai pas entendu par exemple vous insurger du fait que, pour l'AVS également, les frontaliers sont indemnisés de la même manière que les résidents suisses puisqu'ils ont cotisé en Suisse. Ce combat semble un peu perdu d'avance, parce qu'il n'est pas lié à l'Union européenne, mais à l'OCDE, qui a des principes par rapport à cela. (Remarque intermédiaire du président : Avez-vous une question, Monsieur Loïc Dobler ?) Ma question est donc : l'enjeu qui se pose n'est-il pas plutôt l'imposition des frontaliers aussi en Suisse, plutôt que l'indemnisation par le biais du chômage en France ? Ne vous trompez-vous pas de combat avec cette motion ?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nous avons aujourd'hui le plaisir d'accueillir une délégation du canton du Jura et je remercie le président de m'avoir fait l'amitié de la saluer officiellement à la tribune de notre conseil. La délégation est conduite par M. Fabrice Macquat, président du Parlement jurassien, et c'est pour moi, évidemment, une joie et un honneur de pouvoir vous souhaiter la bienvenue dans la salle du Conseil des États. Pour y accéder, vous êtes passés sous la magnifique verrière de la coupole et avez pu admirer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nous avons aujourd'hui le plaisir d'accueillir une délégation du canton du Jura et je remercie le président de m'avoir fait l'amitié de la saluer officiellement à la tribune de notre conseil. La délégation est conduite par M. Fabrice Macquat, président du Parlement jurassien, et c'est pour moi, évidemment, une joie et un honneur de pouvoir vous souhaiter la bienvenue dans la salle du Conseil des États. Pour y accéder, vous êtes passés sous la magnifique verrière de la coupole et avez pu admirer les armoiries des cantons disposées autour de la croix suisse.
+Les guides s'amusent souvent à demander aux visiteuses et visiteurs où se trouvent les armoiries du Jura, car ces dernières ne trônent pas sous la coupole, puisqu'elles ont été ajoutées bien après la construction du Palais du Parlement. Pour cause, son inauguration en 1902 est intervenue 77 ans avant l'entrée en souveraineté du canton. Ainsi, absente de la coupole en 1902, la région jurassienne a néanmoins posé, cette année-là, un jalon important pour rallier un jour la Berne fédérale. Elle a en effet largement approuvé en votation populaire un projet de construction de nouvelle ligne de chemin de fer qui allait préfigurer le percement de la ligne ferroviaire Moutier-Bienne. Lorsqu'en 1979, le canton du Jura est entré en souveraineté au terme d'une histoire que l'on sait mouvementée, ces armoiries ont trouvé une place de choix au-dessus des trois Confédérés.
+La Confédération que nous représentons aujourd'hui n'est pas celle qui s'est unie sous cette coupole en 1902. Elle a changé, elle s'est agrandie, elle a évolué avec les générations et les territoires qui la composent. Unies sous un même toit, les armoiries sous la coupole sont le témoin de cette histoire. Elles nous rappellent, à l'instar du canton du Jura, que le fédéralisme sur lequel la Suisse s'est construite depuis ses origines porte les graines des changements dont la population se fait le moteur. Je vous souhaite une très cordiale bienvenue au Palais fédéral ainsi qu'une excellente visite. (Applaudissements)
 </t>
   </si>
 </sst>
@@ -287,8 +309,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I11" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I13" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I13"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -905,6 +927,64 @@
         <v>52</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">Madame Amaudruz, vous évoquez à juste titre l'aspect de cette réforme relatif à l'indemnisation de l'assurance-chômage. Je ne vous ai pas entendu par exemple vous insurger du fait que, pour l'AVS également, les frontaliers sont indemnisés de la même manière que les résidents suisses puisqu'ils ont cotisé en Suisse. Ce combat semble un peu perdu d'avance, parce qu'il n'est pas lié à l'Union européenne, mais à l'OCDE, qui a des principes par rapport à cela. (Remarque intermédiaire du président : A</t>
   </si>
   <si>
-    <t xml:space="preserve">Madame Amaudruz, vous évoquez à juste titre l'aspect de cette réforme relatif à l'indemnisation de l'assurance-chômage. Je ne vous ai pas entendu par exemple vous insurger du fait que, pour l'AVS également, les frontaliers sont indemnisés de la même manière que les résidents suisses puisqu'ils ont cotisé en Suisse. Ce combat semble un peu perdu d'avance, parce qu'il n'est pas lié à l'Union européenne, mais à l'OCDE, qui a des principes par rapport à cela. (Remarque intermédiaire du président : Avez-vous une question, Monsieur Loïc Dobler ?) Ma question est donc : l'enjeu qui se pose n'est-il pas plutôt l'imposition des frontaliers aussi en Suisse, plutôt que l'indemnisation par le biais du chômage en France ? Ne vous trompez-vous pas de combat avec cette motion ?
+    <t xml:space="preserve">Madame Amaudruz, vous évoquez à juste titre l'aspect de cette réforme relatif à l'indemnisation de l'assurance-chômage. Je ne vous ai pas entendu par exemple vous insurger du fait que, pour l'AVS également, les frontaliers sont indemnisés de la même manière que les résidents suisses puisqu'ils ont cotisé en Suisse. Ce combat semble un peu perdu d'avance, parce qu'il n'est pas lié à l'Union européenne, mais à l'OCDE, qui a des principes par rapport à cela. (Remarque intermédiaire du président : Avez-vous une question, Monsieur Dobler ?) Ma question est donc : l'enjeu qui se pose n'est-il pas plutôt l'imposition des frontaliers aussi en Suisse, plutôt que l'indemnisation par le biais du chômage en France ? Ne vous trompez-vous pas de combat avec cette motion ?
 </t>
   </si>
   <si>
@@ -255,6 +255,85 @@
     <t xml:space="preserve">Nous avons aujourd'hui le plaisir d'accueillir une délégation du canton du Jura et je remercie le président de m'avoir fait l'amitié de la saluer officiellement à la tribune de notre conseil. La délégation est conduite par M. Fabrice Macquat, président du Parlement jurassien, et c'est pour moi, évidemment, une joie et un honneur de pouvoir vous souhaiter la bienvenue dans la salle du Conseil des États. Pour y accéder, vous êtes passés sous la magnifique verrière de la coupole et avez pu admirer les armoiries des cantons disposées autour de la croix suisse.
 Les guides s'amusent souvent à demander aux visiteuses et visiteurs où se trouvent les armoiries du Jura, car ces dernières ne trônent pas sous la coupole, puisqu'elles ont été ajoutées bien après la construction du Palais du Parlement. Pour cause, son inauguration en 1902 est intervenue 77 ans avant l'entrée en souveraineté du canton. Ainsi, absente de la coupole en 1902, la région jurassienne a néanmoins posé, cette année-là, un jalon important pour rallier un jour la Berne fédérale. Elle a en effet largement approuvé en votation populaire un projet de construction de nouvelle ligne de chemin de fer qui allait préfigurer le percement de la ligne ferroviaire Moutier-Bienne. Lorsqu'en 1979, le canton du Jura est entré en souveraineté au terme d'une histoire que l'on sait mouvementée, ces armoiries ont trouvé une place de choix au-dessus des trois Confédérés.
 La Confédération que nous représentons aujourd'hui n'est pas celle qui s'est unie sous cette coupole en 1902. Elle a changé, elle s'est agrandie, elle a évolué avec les générations et les territoires qui la composent. Unies sous un même toit, les armoiries sous la coupole sont le témoin de cette histoire. Elles nous rappellent, à l'instar du canton du Jura, que le fédéralisme sur lequel la Suisse s'est construite depuis ses origines porte les graines des changements dont la population se fait le moteur. Je vous souhaite une très cordiale bienvenue au Palais fédéral ainsi qu'une excellente visite. (Applaudissements)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piller Carrard Valérie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je voudrais vous parler de Pierre.
+Pierre vit depuis plusieurs années dans une institution, dans le canton du Jura. Sa soeur Jacqueline habite dans un autre canton. Elle lui rend visite régulièrement, l'accompagne dans ses démarches et organise son quotidien avec lui. Depuis la mort de leurs parents, elle est son seul lien familial. Pierre voudrait se rapprocher d'elle, vivre à côté de sa soeur, comme n'importe qui d'entre nous voudrait vivre près des siens. Sa demande a été refusée, pas parce q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je voudrais vous parler de Pierre.
+Pierre vit depuis plusieurs années dans une institution, dans le canton du Jura. Sa soeur Jacqueline habite dans un autre canton. Elle lui rend visite régulièrement, l'accompagne dans ses démarches et organise son quotidien avec lui. Depuis la mort de leurs parents, elle est son seul lien familial. Pierre voudrait se rapprocher d'elle, vivre à côté de sa soeur, comme n'importe qui d'entre nous voudrait vivre près des siens. Sa demande a été refusée, pas parce que le projet n'est pas réaliste ni parce qu'il ne correspond pas à ses besoins, mais parce qu'un changement de canton coûterait plus cher aux autorités. Pierre ne demande pas un privilège. Il demande simplement de pouvoir choisir où il vit - ce que la plupart d'entre nous n'imaginent même pas devoir demander.
+Autre situation vécue : en arrivant au Palais fédéral cet après-midi, j'ai appris que pendant que nous débattons ici de l'inclusion, des personnes en fauteuil roulant ont été empêchées d'accéder aux tribunes et doivent suivre nos débats depuis la Galerie des Alpes. Des personnes aveugles ont, elles aussi, dû insister pour pouvoir entrer avec leur chien d'assistance. Ce n'est pas un détail logistique. Ce sont précisément ces barrières qui excluent encore les personnes en situation de handicap des débats qui les concernent directement. On parle d'elles ici, mais certaines ne peuvent même pas assister à ce débat comme les autres. Aujourd'hui, certaines d'entre elles sont littéralement tenues à l'écart du débat sur leurs propres droits.
+Ce sont ces réalités que vivent, à des degrés divers, les personnes en situation de handicap dans notre pays : un choix de vie sans cesse mis en balance avec une ligne budgétaire notamment. Le lieu de vie d'une personne ne devrait pas dépendre de frontières administratives ou de mécanismes de financement.
+En 2026, force est de constater que leur accès à des pans entiers de la vie - le logement, le travail, la formation, les loisirs, les transports publics ou encore le débat politique - reste incertain. L'interdiction de la discrimination figure dans notre Constitution depuis 25 ans, mais, contrairement à l'égalité entre femmes et hommes, cette égalité n'a jamais été confiée au législateur comme un mandat clair. Il est temps que cela change.
+Je salue la volonté du Conseil fédéral d'opposer un contre-projet indirect à l'initiative "pour l'égalité des personnes handicapées", ainsi que le travail accompli en commission pour s'en rapprocher. Mais à ce stade, ce contre-projet reste trop timide, et j'espère que nos débats permettront de le renforcer.
+En Suisse, 1,9 million de personnes vivent en situation de handicap - une personne sur cinq. Et contrairement à ce que l'on croit souvent, la plupart ne sont pas nées avec un handicap : il est survenu avec un accident, une maladie, l'âge. Cette réalité ne concerne donc pas seulement "les autres" ; elle peut un jour nous concerner toutes et tous.
+Le contre-projet reprend des éléments importants de l'initiative - c'est un progrès -, mais reste largement dépourvu de caractère contraignant, pour les cantons comme pour la Confédération. Il ne garantit aucune obligation cantonale d'assurer l'égalité en droit et en fait. Il n'accorde aucun droit nouveau, comme celui de décider de son propre logement ou de son lieu de vie, mais se contente d'un engagement de principe. Enfin, il ne prévoit pour l'heure aucune amélioration générale de l'accès aux prestations d'assistance, quel que soit le type de handicap.
+C'est pourquoi je soutiendrai un contre-projet qui renforce réellement l'autonomie des personnes en situation de handicap. Je recommanderai d'accepter l'initiative pour l'inclusion, parce qu'elle seule garantit ce que le contre-projet ne fait encore que promettre : l'égalité et l'autodétermination.
+Pierre ne demande rien d'extraordinaire. Il demande ce que la Constitution devrait déjà lui garantir : le droit de choisir sa vie. Les personnes en situation de handicap sont des citoyens à part entière. À nous de le traduire enfin dans la loi.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il ne reste plus beaucoup de divergences par rapport à la décision du Conseil national. Il nous a rejoints sur beaucoup de points et nous l'avons également rejoint sur un certain nombre de points, ce qui est souhaitable, notamment concernant le maintien de la protection des marais, qui était vraiment l'un des impératifs et l'une des lignes rouges, à notre sens, dans ce projet. 
+Pour ce qui est de la divergence à l'article 15bbis alinéa 3, notre conseil proposait de modifier trois choses par rapp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il ne reste plus beaucoup de divergences par rapport à la décision du Conseil national. Il nous a rejoints sur beaucoup de points et nous l'avons également rejoint sur un certain nombre de points, ce qui est souhaitable, notamment concernant le maintien de la protection des marais, qui était vraiment l'un des impératifs et l'une des lignes rouges, à notre sens, dans ce projet. 
+Pour ce qui est de la divergence à l'article 15bbis alinéa 3, notre conseil proposait de modifier trois choses par rapport au projet du Conseil fédéral. Premièrement, il souhaitait que les exigences environnementales ne soient plus prises en compte, mais examinées, ce qui introduisait un affaiblissement de l'alinéa. Deuxièmement, il souhaitait introduire les intérêts des propriétaires fonciers dans cet examen. Troisièmement, il souhaitait réduire les distances légales des lignes par rapport aux forêts et aux cours d'eau. Le Conseil national proposait, lui, de maintenir la version du Conseil fédéral.
+Pourquoi vous ai-je proposé de rester sur cette version par le biais de ma minorité ? Pour trois raisons. Premièrement, l'expression "prendre en compte" plutôt qu'"examiner" entraîne plutôt des incertitudes, parce qu'examiner n'implique pas forcément que l'on prendra en compte, et, pour les autorités d'application, cette notion "d'examiner les intérêts" n'est pas claire et entraîne plutôt des incertitudes. Deuxièmement, s'agissant des intérêts des propriétaires fonciers, notre conseil a souhaité intégrer l'examen des intérêts des propriétaires fonciers dans la pesée des intérêts. Sur une ligne qui réunirait plusieurs dizaines de propriétaires fonciers, cela serait plutôt un facteur de ralentissement que d'accélération de la procédure s'il fallait véritablement examiner leurs intérêts. Dès lors, la version du Conseil des États n'est pas un facteur d'accélération, ce qui est pourtant l'objectif premier de ce projet de loi.
+Enfin - et peut-être l'élément le plus important -, c'est la réduction des distances légales pour la construction à proximité des forêts et des cours d'eau. Ce qui est important, c'est le fait que la réduction de ces distances est déjà contenue dans une autre loi, à savoir la loi sur les forêts (LFo). Il est déjà possible, en vertu de l'article 17 alinéa 3 LFo, de réduire les distances pour la construction d'infrastructures par rapport aux forêts. Dès lors, il ne serait pas nécessaire d'introduire cette mention à l'alinéa 3.
+Le deuxième problème concerne la notion d'examen : si l'on peut réduire ces distances en examinant, mais sans faire de pesée des intérêts et approfondir les problématiques en place, on pourrait être amené à créer des problèmes de sécurité en construisant de nouvelles lignes. On pense notamment - ce ne sont pas des cas fictifs - à ce qu'il pourrait arriver en cas d'incendies de forêt s'ils entraient en contact avec les lignes électriques. On pense également aux tempêtes telles qu'on les a connues ces dernières années, qui peuvent déraciner des arbres et faire tomber des branches sur la ligne de contact. Il n'est donc pas souhaitable d'introduire une disposition qui permet, sans grand examen, de réduire les distances des constructions par rapport aux forêts dans la loi en vigueur.
+Dès lors, je vous invite, à l'instar du Conseil fédéral, à suivre ma minorité et à vous rallier au Conseil national pour cet article 15bbis alinéa 3.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Commission des transports et des télécommunications de notre conseil propose de ne pas classer ce postulat, contrairement à ce qu'indique, ou plutôt, en complément de ce qu'indique le Conseil fédéral, qui veut peut-être intégrer cela dans son projet Transports'45. Aujourd'hui, on n'a même pas encore terminé la consultation concernant le projet Transports'45 et on voit la nécessité qu'il y a d'agir dans ce secteur, puisque la semaine passée encore, il y a eu une interruption de trafic très imp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Commission des transports et des télécommunications de notre conseil propose de ne pas classer ce postulat, contrairement à ce qu'indique, ou plutôt, en complément de ce qu'indique le Conseil fédéral, qui veut peut-être intégrer cela dans son projet Transports'45. Aujourd'hui, on n'a même pas encore terminé la consultation concernant le projet Transports'45 et on voit la nécessité qu'il y a d'agir dans ce secteur, puisque la semaine passée encore, il y a eu une interruption de trafic très importante liée à une insuffisance de l'infrastructure. Il n'y avait pas de redondance pour faire circuler les trains et même l'autoroute était bloquée à cet endroit. Si la commission peut entendre que le Conseil fédéral introduira quelque chose, aujourd'hui on n'a rien de vraiment concret, raison pour laquelle nous proposons de maintenir ce postulat encore en suspens jusqu'à ce que nous ayons des éléments plus concrets du côté du Conseil fédéral.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme vous, Monsieur le président, je ne suis pas un adepte du fait que chaque membre de la commission participe au débat, mais en l'occurrence, permettez-moi quand même d'exprimer quelques mots en français, parce que, dans ce débat, il y a surtout des Alémaniques qui se sont exprimés. Je suis content d'apprendre que mon collègue Broulis va aussi intervenir ; ce qui fait qu'il ne restera plus que deux membres de la commission qui ne se seront pas exprimés, mais ça, c'est une autre question.
+Nous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme vous, Monsieur le président, je ne suis pas un adepte du fait que chaque membre de la commission participe au débat, mais en l'occurrence, permettez-moi quand même d'exprimer quelques mots en français, parce que, dans ce débat, il y a surtout des Alémaniques qui se sont exprimés. Je suis content d'apprendre que mon collègue Broulis va aussi intervenir ; ce qui fait qu'il ne restera plus que deux membres de la commission qui ne se seront pas exprimés, mais ça, c'est une autre question.
+Nous menons aujourd'hui un débat qui engage notre responsabilité face à la sécurité du pays et de sa population. Parler d'augmenter le budget de l'armée suisse, ce n'est pas céder à un réflexe militariste. C'est regarder avec lucidité l'état de nos infrastructures de défense en parallèle de la situation du monde qui nous entoure.
+Depuis le début des années 1990, la Suisse a vécu avec l'illusion d'une fin de l'histoire, d'une paix perpétuelle sur le continent européen. Cette illusion s'est traduite par des choix comptables clairs. Quelques rappels chiffrés qui ne sont que des faits sans aucune appréciation : en 1990, le budget de l'armée représentait près de 16 pour cent des dépenses globales de la Confédération. Aujourd'hui, il atteint à peine les 6 pour cent, soit une diminution de 60 pour cent, alors que c'est une tâche régalienne de la seule responsabilité de la Confédération.
+Pendant trois décennies, la défense nationale a été la variable d'ajustement préférée des budgets, pour financer certes légitimement la croissance d'autres domaines essentiels comme la prévoyance sociale - plus 30 pour cent - ou les transports, dont les montants ont été multipliés par 3, en même temps que le budget de la Confédération était lui aussi multiplié par 3, passant de 31 milliards de francs en 1990 à 90 milliards en 2026.
+Mais le dividende de la paix a expiré. La guerre est de retour sur notre continent. Les menaces hybrides, cybernétiques, et le durcissement du contexte géopolitique ne sont plus des hypothèses d'exercices d'état-major, ce sont des réalités quotidiennes. Les rapports du Conseil fédéral et les analyses de nos propres commissions sont sans concession : en cas de conflit majeur, les deux tiers de nos troupes ne disposeraient pas d'un équipement complet et nos stocks de munitions suffiraient à peine pour quelques semaines. Notre pays n'a quasiment aucune couverture moderne face aux attaques aériennes et sol-air à basse et moyenne portées.
+Selon le Conseil fédéral, l'armée a un besoin urgent de 24 milliards de francs : 15 milliards d'investissements et 9 milliards pour parer aux augmentations inévitables sur le marché de l'armement. Ce n'est pas un chèque en blanc, mais un crédit-cadre dont l'utilisation sera soumise au Parlement lors de chaque budget, dans le respect des outils légaux à disposition. C'est vrai qu'il est plus facile de lister les titres des journaux que de donner les moyens au Conseil fédéral de remplir une de ses missions régaliennes : assurer la défense du pays pour protéger sa population.
+Dire que le budget militaire explose est un contresens statistique, je l'ai démontré. Ce que nous votons, c'est un plan de rattrapage structurel pour amener ensuite durablement nos dépenses de défense à 1 pour cent du PIB. C'est le strict minimum pour un État souverain et neutre. Comment justifier notre neutralité, dont le sens fait débat actuellement, si nous sommes incapables d'assurer de manière autonome la protection de notre espace aérien et de nos infrastructures critiques ? La neutralité n'est pas un bouclier magique, c'est une responsabilité opérationnelle. Elle doit être appuyée par une volonté et des moyens de défense crédibles qui s'insèrent dans un puzzle de la défense du continent européen.
+Le Conseil fédéral nous propose de recourir uniquement à l'augmentation de la TVA - pour rappel : 0,5 point pour le taux de TVA de base, 0,5 point pour le taux spécial - sans toucher au taux applicable aux produits de première nécessité, épargnant ainsi en grande partie le porte-monnaie des ménages et des familles. Il propose aussi la création d'un fonds pouvant s'endetter, destiné à obtenir davantage de souplesse dans la gestion des commandes d'armement.
+La Commission des finances nous a proposé un compromis avec un relèvement de la TVA de 0,2 point pour le taux de base et de 0,1 point pour le taux spécial, ainsi que l'utilisation de 50 pour cent des restes de crédit, comme pour la création d'un fonds. C'est une trajectoire financière responsable, pragmatique et surtout respectueuse du frein à l'endettement qui fait la force de notre gestion publique. Je remercie la Commission des finances des réflexions qu'elle a menées et de la proposition qu'elle a formulée. La Commission de la politique de sécurité a repris cette proposition sous forme de concept qu'elle a un peu amendé, notamment quant à la durée du fonds et à sa capacité d'endettement.
+Rappelons que sans sécurité, il n'y a ni prospérité économique, ni stabilité sociale, ni formation de qualité. La sécurité est le socle sur lequel reposent toutes nos autres politiques publiques. Investir dans l'armée, ce n'est pas préparer la guerre ; c'est garantir que notre population puisse continuer à vivre en sécurité et en liberté, à l'abri des chantages internationaux. Il est donc assez naturel de recourir notamment à cette modeste augmentation temporaire de la TVA. Certes, ce n'est pas une solution facile, mais c'est notre travail de définir des solutions et, si nécessaire, de les proposer et de les défendre devant le peuple souverain.
+Quant aux autres propositions figurant sur le dépliant, permettez-moi d'apporter à ce stade une appréciation sur les principaux concepts, étant entendu que je n'y reviendrai pas dans la discussion par article. Je constate d'abord que toutes ces propositions retiennent la création d'un fonds pour la défense et la sécurité, et c'est une bonne chose.
+La première variante sans TVA, que propose la minorité II (Dittli), prévoit de recourir seulement à la caisse fédérale en sus des restes de crédit. Elle n'est pas très réaliste, car elle implique de prévoir des programmes d'économie. Or, après être sorti de l'un d'entre eux, on sait à quel point un tel programme est difficile et long à mener.
+Je vous invite donc à rejeter ce concept.
+L'autre concept sans la TVA est défendu par la minorité IV (Salzmann). Le fait de demander le versement d'un dividende de substance de la BNS est très compliqué, peu réaliste, voire impraticable. Qui dit dividende de substance implique en effet le fait d'être actionnaire de la BNS. Or, je vous l'apprendrai peut-être - les membres de la Commission des finances le savent sûrement -, la Confédération n'est pas actionnaire de la BNS, comme le sont les cantons, les banques cantonales et quelques privés. La Confédération n'est pas actionnaire de la BNS et on ne peut pas exiger un dividende de substance lorsqu'on n'est pas propriétaire de cette substance. De plus, en vertu de l'indépendance de la BNS, il serait peu opportun d'y toucher alors que nous l'avons toujours défendue quand il s'agissait de financer l'AVS ou un fonds pour le climat. Je vous invite également à rejeter ce concept.
+La création temporaire d'un nouvel impôt sur les fortunes particulièrement importantes a quant à elle également peu de chance d'aboutir, car elle empiète sur les compétences fiscales des cantons. De plus, qu'est-ce qu'une fortune particulièrement importante ? Il est clair qu'un problème temporel de mise en oeuvre s'installerait également.
+L'armée suisse a besoin de visibilité à long terme pour se moderniser et faire face aux menaces les plus pertinentes et les plus immédiates, ce qui ne veut pas dire qu'il faut oublier le reste de l'armée, notamment l'armée de terre.
+Pour notre souveraineté et pour la protection de nos concitoyennes et concitoyens, je vous invite instamment à entrer en matière, à soutenir l'augmentation proposée dans le concept de la majorité de votre Commission de la politique de sécurité. Je vous invite également à refuser le renvoi au Conseil fédéral, qui porte sur des objets sur lesquels le Parlement s'est déjà prononcé.
 </t>
   </si>
 </sst>
@@ -309,8 +388,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I13" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I17" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I17"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -947,7 +1026,7 @@
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H12" t="s">
         <v>54</v>
@@ -983,6 +1062,122 @@
       </c>
       <c r="I13" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" t="s">
+        <v>62</v>
+      </c>
+      <c r="I14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -334,6 +334,43 @@
 La création temporaire d'un nouvel impôt sur les fortunes particulièrement importantes a quant à elle également peu de chance d'aboutir, car elle empiète sur les compétences fiscales des cantons. De plus, qu'est-ce qu'une fortune particulièrement importante ? Il est clair qu'un problème temporel de mise en oeuvre s'installerait également.
 L'armée suisse a besoin de visibilité à long terme pour se moderniser et faire face aux menaces les plus pertinentes et les plus immédiates, ce qui ne veut pas dire qu'il faut oublier le reste de l'armée, notamment l'armée de terre.
 Pour notre souveraineté et pour la protection de nos concitoyennes et concitoyens, je vous invite instamment à entrer en matière, à soutenir l'augmentation proposée dans le concept de la majorité de votre Commission de la politique de sécurité. Je vous invite également à refuser le renvoi au Conseil fédéral, qui porte sur des objets sur lesquels le Parlement s'est déjà prononcé.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steinemann Barbara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Titel dieses Geschäfts täuscht etwas, wir haben hier nur noch einen Punkt zu klären; dahinter steht eine etwas längere Geschichte.
+Am 18. Juni 2023 fanden in mehreren Kantonen Volksabstimmungen statt. In Bern wurde eine Schuldenbremse, in der Waadt ein Klimaartikel und im Kanton Jura ein Amtsenthebungsverfahren für kantonale und kommunale Behördenmitglieder eingeführt. In Genf kamen drei Vorlagen zur Abstimmung; erstens wurde ein Integritätsartikel für die digitale Welt, zweitens ein Recht a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Titel dieses Geschäfts täuscht etwas, wir haben hier nur noch einen Punkt zu klären; dahinter steht eine etwas längere Geschichte.
+Am 18. Juni 2023 fanden in mehreren Kantonen Volksabstimmungen statt. In Bern wurde eine Schuldenbremse, in der Waadt ein Klimaartikel und im Kanton Jura ein Amtsenthebungsverfahren für kantonale und kommunale Behördenmitglieder eingeführt. In Genf kamen drei Vorlagen zur Abstimmung; erstens wurde ein Integritätsartikel für die digitale Welt, zweitens ein Recht auf Ernährung und drittens ein neuer Verfassungsartikel eingeführt. Abgesehen von letzterem waren alle diese Punkte unbestritten, und das Parlament hat sie bereits genehmigt, der Ständerat am 10. September 2024 und der Nationalrat am 18. September 2024.
+Die dritte Genfer Vorlage war der neu verfasste Artikel 205 der Genfer Kantonsverfassung. Dieser sieht im neuen Absatz 3 vor, dass der Kanton Genf in Ergänzung zur Bundesgesetzgebung eine durch paritätische Beiträge der Arbeitgeber und Arbeitnehmer finanzierte Mutterschaftsversicherung von mindestens sechzehn Wochen und einen bezahlten Urlaub von mindestens acht Wochen für den anderen Elternteil gewährleistet. Dies soll gemäss Absatz 4 bei Adoptionen und bei der Aufnahme zur dauerhaften Unterbringung, auf Französisch "accueil avec hébergement à caractère permanent", analog gelten. Was die Erweiterung auf sechzehn Wochen Mutterschaftsversicherung betrifft, war die Revision von Beginn weg mit Bundesrecht konform und gemäss Artikel 51 Absatz 2 der Bundesverfassung zu gewährleisten, der Rest jedoch nicht bzw. damals noch nicht.
+Der Nationalrat hat in der Herbstsession 2024 beschlossen, mit der Gewährleistung zuzuwarten, bis das sich damals in Revision befindliche Erwerbsersatzgesetz (EOG) in Kraft ist. Auf der Basis von Artikel 116 Absatz 3 der Bundesverfassung und des EOG wurden einst nicht nur die Mutterschaftsversicherung, sondern in den letzten Jahren auch die Vaterschaftsentschädigung und die Adoptionsentschädigung eingerichtet. Ein Vorbehalt zugunsten der Kantone für eine weitergehende Regelung enthielt das EOG zum Zeitpunkt der Abstimmung in Genf nur im Bereich der Mutterschafts- und der Adoptionsentschädigung, nicht aber im Bereich des Vaterschaftsurlaubs.
+Folglich war der Teil über den achtwöchigen Vaterschaftsurlaub bundesrechtswidrig und durfte zum damaligen Zeitpunkt von uns nicht genehmigt werden. 
+Die Vorlage wurde im Herbst 2024 auf Antrag der Staatspolitischen Kommission des Ständerates gesplittet: Jener Teil, der höchstens teilweise hätte gewährleistet werden können, wurde aus dem Bundesbeschluss gestrichen und in eine Vorlage 2 verschoben, die heute und jetzt Beratungsgegenstand ist. 
+Der Vaterschaftsurlaub wurde 2021 auf Bundesebene eingeführt. Ab 2023 lief eine Vernehmlassung zu einer Änderung des EOG, die es den Kantonen erlaubt, einen längeren Vaterschaftsurlaub zu gewähren und diesen beispielsweise mit einem kantonalen Zuschlag auf die EO-Beiträge zu finanzieren. 
+Mit Beschlüssen vom 19. Dezember 2025 haben die beiden Räte das Bundesgesetz über den Erwerbsersatz revidiert. Die Referendumsfrist lief am 17. April 2026 ungenutzt ab. Artikel 16mbis sieht nun explizit vor, dass Kantone bei der Versicherung für den anderen Elternteil weiter gehen können als der Bund. Diese Regelung gilt gemäss Artikel 16x auch bei Adoptionen. Folglich wurde nur dieser Punkt bundesrechtskonform. 
+Artikel 205 Absatz 4 der Genfer Kantonsverfassung sieht des Weiteren vor, dass auch für Pflegemütter eine Entschädigungsleistung für mindestens sechzehn Wochen und für Pflegeväter von mindestens acht Wochen auszurichten sei. Für diesen Teil in Artikel 205 der Genfer KV fehlt weiterhin die entsprechende Grundlage im Bundesrecht. 
+Wir sind Zweitrat. Der Ständerat hat diese Änderung am 15. Juni 2026 genehmigt bzw. eben nicht genehmigt. Ihre Staatspolitische Kommission hat sich am 13. August 2026 mit der Angelegenheit befasst. Sie beantragt einstimmig, Artikel 205 Absätze 3 und 4 der in der Volksabstimmung vom 18. Juni 2023 revidierten Genfer KV in den Punkten über die kantonale Versicherung für den anderen Elternteil zu gewährleisten; dies auch bei Adoptionen, nicht aber bei der Aufnahme zur dauerhaften Unterbringung von Pflegekindern. Die Textelemente "ou d'accueil avec hébergement à caractère permanent" und "ou accueillant" dürfen folglich nicht genehmigt werden. 
+Ich bitte Sie, dem Antrag Ihrer SPK zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme l'a dit le rapporteur, le soutien à l'initiative populaire dépend un peu de la teneur du contre-projet qui sortira finalement des conseils, dans la mesure où le Conseil national s'est rallié à notre avis s'agissant du programme de certification. C'est un point réellement primordial du contre-projet que les certifications qui sont apportées aux fourrures importées soient établies selon des standards solides et internationaux reconnus. Dans la mesure où les deux points restants ont été rempl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme l'a dit le rapporteur, le soutien à l'initiative populaire dépend un peu de la teneur du contre-projet qui sortira finalement des conseils, dans la mesure où le Conseil national s'est rallié à notre avis s'agissant du programme de certification. C'est un point réellement primordial du contre-projet que les certifications qui sont apportées aux fourrures importées soient établies selon des standards solides et internationaux reconnus. Dans la mesure où les deux points restants ont été remplis, je retire la proposition de la minorité que je représente. Il n'y a donc plus de divergence sur ce point.
 </t>
   </si>
 </sst>
@@ -388,8 +425,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I17" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I19" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I19"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1180,6 +1217,64 @@
         <v>72</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -371,6 +371,90 @@
   </si>
   <si>
     <t xml:space="preserve">Comme l'a dit le rapporteur, le soutien à l'initiative populaire dépend un peu de la teneur du contre-projet qui sortira finalement des conseils, dans la mesure où le Conseil national s'est rallié à notre avis s'agissant du programme de certification. C'est un point réellement primordial du contre-projet que les certifications qui sont apportées aux fourrures importées soient établies selon des standards solides et internationaux reconnus. Dans la mesure où les deux points restants ont été remplis, je retire la proposition de la minorité que je représente. Il n'y a donc plus de divergence sur ce point.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guggisberg Lars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im Namen der Kommissionsmehrheit beantrage ich Ihnen, die Motion 25.4416, "Unterstützungsleistungen des Bundes in Naturkatastrophenfällen", abzulehnen. Die Motion wurde in der Kommission in der modifizierten Fassung gemäss Antrag Clivaz Christophe mit 13 zu 11 Stimmen abgelehnt.
+Der Antrag Clivaz Christophe zielte darauf ab, die ursprüngliche Motion zu modifizieren, um dem Bundesrat und der Verwaltung mehr Flexibilität bei der Finanzierung zu ermöglichen. Konkret wollte der Antrag die Formulieru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im Namen der Kommissionsmehrheit beantrage ich Ihnen, die Motion 25.4416, "Unterstützungsleistungen des Bundes in Naturkatastrophenfällen", abzulehnen. Die Motion wurde in der Kommission in der modifizierten Fassung gemäss Antrag Clivaz Christophe mit 13 zu 11 Stimmen abgelehnt.
+Der Antrag Clivaz Christophe zielte darauf ab, die ursprüngliche Motion zu modifizieren, um dem Bundesrat und der Verwaltung mehr Flexibilität bei der Finanzierung zu ermöglichen. Konkret wollte der Antrag die Formulierung "aus dem allgemeinen Bundeshaushalt" aus dem Motionstext streichen. Die Befürworter der Motion argumentierten, dass die bestehenden Grundlagen nicht ausreichen und die aktuelle Praxis zu aufwendig und unsicher sei. Es sei essenziell, gesetzliche Grundlagen in ruhigen Zeiten zu schaffen, um im Ernstfall nicht im Affekt oder ad hoc legiferieren zu müssen. Als positives Beispiel für eine solche präventive Regelung wurde das Epidemiengesetz angeführt.
+Die Kommissionsmehrheit lehnte die Motion aus folgenden Erwägungen ab:
+1. Die Zuständigkeit für die Vorsorge und den Wiederaufbau nach Naturereignissen liegt grundsätzlich bei den Kantonen. Wir haben in der Schweiz eine klare föderalistische Zuständigkeitsordnung, an der wir festhalten müssen. Die Schaffung einer bundesgesetzlichen Grundlage für die Finanzierung von Sofortmassnahmen würde diese Kantonshoheit schwächen. Es besteht die Gefahr, dass Kantone und Gemeinden ihre eigenen Pflichten in der Gefahrenprävention vernachlässigen, wenn sie sich primär auf die Verfügbarkeit von Bundesmitteln verlassen können.
+2. Den Kantonen stehen bereits erhebliche finanzielle Instrumente zur Verfügung. Über den nationalen Finanzausgleich fliessen jährlich Milliardenbeiträge vom Bund an die Kantone, ergänzt durch die Weiterleitung der direkten Bundessteuer. Diese Mechanismen sind dazu da, regionale finanzielle Disparitäten auszugleichen und die Handlungsfähigkeit der Kantone auch in schwierigen Situationen sicherzustellen.
+3. Die Praxis zeigt, dass der Bund in extremen Ausnahmefällen wie etwa bei der Katastrophe in Blatten auch ohne spezifische Gesetzesgrundlage rasch und effektiv helfen kann. Ein allgemeines Gesetz kann die Unvorhersehbarkeit und die Individualität von Katastrophen nicht vollständig abbilden. Zudem ist die Überprüfung der gesetzlichen Grundlagen im Rahmen des Postulates 25.3669 bereits im Gange. Es ist daher sachgerechter, den Bericht zu diesem Postulat abzuwarten und die Lage nüchtern zu analysieren, anstatt auf Basis von Einzelereignissen emotional zu legiferieren.
+Aus diesen Gründen bitte ich Sie namens der Kommissionsmehrheit, die Motion abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bläsi Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J'ai l'impression que, dans ce débat, on est en train de se perdre : c'est plus d'État à gauche, moins d'État à droite, saupoudré d'un mercantilisme absolu. Cependant, ce n'est pas le problème : le problème est qu'on a besoin des substances de base, des principes actifs de base, pour pouvoir éviter que les enfants qui tombent malades meurent, parce que l'on ne peut pas les soigner.
+Ces principes actifs sont impérissables. Ils ne posent donc aucun problème à stocker. Ils ne coûtent absolument rie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J'ai l'impression que, dans ce débat, on est en train de se perdre : c'est plus d'État à gauche, moins d'État à droite, saupoudré d'un mercantilisme absolu. Cependant, ce n'est pas le problème : le problème est qu'on a besoin des substances de base, des principes actifs de base, pour pouvoir éviter que les enfants qui tombent malades meurent, parce que l'on ne peut pas les soigner.
+Ces principes actifs sont impérissables. Ils ne posent donc aucun problème à stocker. Ils ne coûtent absolument rien. Les antibiotiques, c'est un petit peu compliqué ; c'est à part. Ne pensez-vous pas, Monsieur Loïc Dobler, que le mieux serait d'avoir ce stock de produits qui ne périront jamais et ainsi, si on en a besoin un jour, on est sûrs de pouvoir en fournir à nos enfants ? Les officines pourront recomposer des médicaments. Il n'y aura pas de problème de ce point de vue.
+Tandis que là, on ne parle que d'argent, de plus d'État, de moins d'État : on n'est pas du tout efficaces !
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les pénuries de médicaments ne sont plus des incidents isolés. Elles sont devenues structurelles et elles menacent parfois directement la continuité des soins. Elles ne touchent d'ailleurs pas les traitements innovants et coûteux, mais des médicaments anciens, bon marché et pourtant indispensables : antibiotiques, traitements contre l'épilepsie, la maladie de Parkinson, les maladies psychiques ou d'autres affections chroniques. Cette situation n'est pas un hasard. Elle découle d'une production p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les pénuries de médicaments ne sont plus des incidents isolés. Elles sont devenues structurelles et elles menacent parfois directement la continuité des soins. Elles ne touchent d'ailleurs pas les traitements innovants et coûteux, mais des médicaments anciens, bon marché et pourtant indispensables : antibiotiques, traitements contre l'épilepsie, la maladie de Parkinson, les maladies psychiques ou d'autres affections chroniques. Cette situation n'est pas un hasard. Elle découle d'une production pharmaceutique concentrée entre un nombre toujours plus restreint de fournisseurs, souvent situés dans quelques régions du monde. Les stocks ont été réduits et les chaînes de production optimisées selon la seule rentabilité. Lorsque le brevet d'un médicament ancien expire, il arrive qu'il soit tout simplement retiré du marché, parce qu'il ne rapporte plus assez. Il faut le dire clairement : la santé publique ne peut pas dépendre uniquement de la rentabilité attendue d'un produit.
+L'initiative populaire part de cette préoccupation légitime, mais elle est trop large et mélange des enjeux différents. Les initiants demandent à la Confédération d'intervenir sur toute la chaîne de valeur, y compris la recherche et le développement. Or, le problème ne se situe pas là. Les pénuries concernent des produits de base, éprouvés, souvent hors brevet, mais pas les médicaments innovants. Donner à la Confédération une compétence générale pour promouvoir encore davantage la recherche ne résoudrait donc pas le coeur du problème. C'est pourquoi recommander le rejet de l'initiative s'impose.
+Le contre-projet direct plus ciblé mérite en revanche d'être soutenu. Il donne à la Confédération les compétences nécessaires pour surveiller l'approvisionnement et détecter précocement les risques, mieux informer les professionnels de santé, soutenir ou garantir certaines capacités de production, acheter, faire fabriquer ou, et c'est important, en dernier recours, produire elle-même des biens essentiels et renforcer la coopération internationale. La ligne est claire. Lorsque le marché échoue, l'État doit pouvoir intervenir, mais toute aide publique à une entreprise devrait s'accompagner de contreparties en matière de transparence, de production et de livraison. Il faut éviter que les bénéfices restent privés pendant que les productions devenues moins rentables sont socialisées dès qu'elles posent problème. Le contre-projet ne réglera pas tout. Il constitue néanmoins une amélioration substantielle par rapport au statu quo et une réponse plus proportionnée que l'initiative au problème réel qu'il s'agit de résoudre.
+Il convient donc de recommander le rejet de l'initiative populaire et d'entrer en matière sur le contre-projet direct.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je vous remercie pour votre question relativement précise. Je serais tenté de vous dire que c'est au sein de votre groupe parlementaire qu'il faudrait chercher à convaincre. En effet, je crois que ce n'est pas au sein du groupe socialiste qu'il faut essayer de convaincre de l'importance du rôle de l'État dans le domaine de la santé. On peut effectivement partager votre appréciation, même si, en l'occurrence, il s'agit d'avoir un contre-projet qui puisse trouver une majorité. Et pour trouver une </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je vous remercie pour votre question relativement précise. Je serais tenté de vous dire que c'est au sein de votre groupe parlementaire qu'il faudrait chercher à convaincre. En effet, je crois que ce n'est pas au sein du groupe socialiste qu'il faut essayer de convaincre de l'importance du rôle de l'État dans le domaine de la santé. On peut effectivement partager votre appréciation, même si, en l'occurrence, il s'agit d'avoir un contre-projet qui puisse trouver une majorité. Et pour trouver une majorité, par définition, il faut être soutenu par la majorité de cette chambre ainsi que par la majorité du Conseil des États.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germann Hannes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mit dieser Motion soll der Bundesrat beauftragt werden, die gesetzlichen Grundlagen so anzupassen, dass die durch die Einführung der 13. AHV-Rente in Zukunft entstehenden Steuermehreinnahmen bei Kantonen und Gemeinden vollständig dem Bund zufliessen sollen; immerhin würden diese Mittel dann direkt an die AHV weitergeleitet. Die Motionäre begründen ihre Forderung damit bzw. machen geltend, dass aufgrund der Einführung der 13. AHV-Rente künftig ein System der Asymmetrie entstehe, bei dem der Bund </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mit dieser Motion soll der Bundesrat beauftragt werden, die gesetzlichen Grundlagen so anzupassen, dass die durch die Einführung der 13. AHV-Rente in Zukunft entstehenden Steuermehreinnahmen bei Kantonen und Gemeinden vollständig dem Bund zufliessen sollen; immerhin würden diese Mittel dann direkt an die AHV weitergeleitet. Die Motionäre begründen ihre Forderung damit bzw. machen geltend, dass aufgrund der Einführung der 13. AHV-Rente künftig ein System der Asymmetrie entstehe, bei dem der Bund die Mehrausgaben trage, während Kantone und Gemeinden von Steuermehreinnahmen profitierten, ohne einen entsprechenden Beitrag zu leisten. Als mögliche Lösung für diese Lastenverschiebung wollen sie den Kantonsanteil an der direkten Bundessteuer im Umfang der geschätzten Steuermehreinnahmen aus der 13. AHV-Rente reduzieren. 
+Der Bundesrat verweist darauf, dass das rechtlich grundsätzlich möglich wäre. Der Anteil der Kantone liegt derzeit bei 21,2 Prozent. Der Bund hat ausgerechnet, dass sich diese Mehreinnahmen für das Jahr 2026, in dem ja die 13. AHV-Rente im Dezember erstmals ausbezahlt wird, auf 650 Millionen Franken belaufen würden. Diese 650 Millionen würden rechnerisch eine Reduktion von 2 Prozentpunkten ausmachen, sprich der Anteil der Kantone und Gemeinden an der direkten Bundessteuer würde von 21,2 Prozent auf 19,2 Prozent reduziert. Nun verweisen der Bundesrat und die Kommission darauf, dass Gesetzesänderungen auf Bundesstufe bei den Kantonen ohnehin regelmässig positiv oder negativ zu Buche schlagen. Es geht dabei nicht nur um Einnahmen; oft beschliessen wir ja auch Gesetze, die bei Kantonen und Gemeinden direkt Ausgaben auslösen. Der Bundesrat will auf eine Feinsteuerung durch die Rechtsetzung in diesem Bereich verzichten und dies nur bei gross angelegten Reformen tun, wie wir das eigentlich immer gemacht haben. Hierbei ist namentlich auf die Neugestaltung des Finanzausgleichs und der Aufgabenteilung (NFA) von 2008 zu verweisen sowie - mit Blick auf die jüngere Vergangenheit - auf die Steuerreform und die AHV-Finanzierung (STAF) von 2020.
+Die Kommission hat sich am 1. September mit dem Geschäft befasst. Wir haben Kenntnis davon genommen, dass der Nationalrat mit 96 zu 90 Stimmen bei 5 Enthaltungen einen relativ knappen Entscheid gefällt hat. Wir haben uns in der Kommission den Ausführungen des Bundesrates angeschlossen. Es spricht nämlich einiges gegen eine Abschöpfung dieser zusätzlichen Steuereinnahmen, die den Kantonen und Gemeinden zugutekommen. Unter anderem finden wir, dass der administrative Aufwand zu hoch wäre. Zudem würde eine solche Anpassung zu ständigen Veränderungen bei der Verteilung führen - einmal nach oben, dann wieder nach unten. Das ist nicht zielgerichtet, es wäre dann auch keine Rechtssicherheit vorhanden. Wenn schon, müsste man eine solche Änderung im Zusammenhang mit der NFA vornehmen. Das, finden wir, sind eigentlich die guten Gründe, die für eine Ablehnung sprechen. Eine fixe und einmalige Reduktion des Kantonsanteils an der Bundessteuer würde der bestehenden Einnahmen- und Ausgaben-Dynamik - mit mal mehr, mal weniger Einnahmen bzw. Ausgaben - nicht gerecht werden. 
+Darum beantragt Ihnen Ihre vorberatende Kommission, die SGK-S, mit 6 zu 0 Stimmen bei immerhin 5 Enthaltungen, dem Bundesrat zu folgen und diese Motion abzulehnen.
 </t>
   </si>
 </sst>
@@ -425,8 +509,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I19" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I24" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I24"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1275,6 +1359,151 @@
         <v>80</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" t="s">
+        <v>89</v>
+      </c>
+      <c r="I21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" t="s">
+        <v>92</v>
+      </c>
+      <c r="I22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" t="s">
+        <v>95</v>
+      </c>
+      <c r="I23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -54,18 +54,18 @@
   </si>
   <si>
     <t xml:space="preserve">De ces trois motions, je vous invite à suivre la position de la commission concernant la motion Rechsteiner Thomas 25.3906 et à rejeter la motion Michel Matthias 25.3866 pour la simple raison technique qu'il s'agit de la même que la motion Vincenz 25.3902, que ma minorité propose d'adopter.
-Le rapporteur l'a dit : la majorité de la commission juge que les travaux en cours relatifs aux PFAS justifient de rejeter l'ensemble des motions qui ont été déposées en bloc. J'opposerai à cela l'argument se</t>
+Le rapporteur l'a dit, la majorité de la commission juge que les travaux en cours relatifs aux PFAS justifient de rejeter l'ensemble des motions qui ont été déposées en bloc. J'opposerai à cela l'argument sel</t>
   </si>
   <si>
     <t xml:space="preserve">De ces trois motions, je vous invite à suivre la position de la commission concernant la motion Rechsteiner Thomas 25.3906 et à rejeter la motion Michel Matthias 25.3866 pour la simple raison technique qu'il s'agit de la même que la motion Vincenz 25.3902, que ma minorité propose d'adopter.
-Le rapporteur l'a dit : la majorité de la commission juge que les travaux en cours relatifs aux PFAS justifient de rejeter l'ensemble des motions qui ont été déposées en bloc. J'opposerai à cela l'argument selon lequel la commission n'adopte cette position que de manière très partiale. Nous avons encore tous à l'esprit la kyrielle de motions concernant le loup auxquelles la commission a donné sa bénédiction, souvent contre l'avis du Conseil fédéral, alors même que les travaux étaient déjà en cours - mais passons.
-La deuxième raison pour laquelle il est nécessaire d'examiner en détail chacune de ces motions et de les accepter, c'est précisément parce que nous avons adopté la motion 25.3421, "Fixer des valeurs limites pertinentes pour les PFAS en tenant compte des conséquences pour l'agriculture et les distributeurs d'eau et introduire des mesures de soutien à l'agriculture", qui vise à modifier les valeurs limites fixées pour les PFAS en fonction des intérêts économiques. Cela s'inscrit dans le contexte de la thématique des PFAS, qui repose sur de solides connaissances scientifiques étayées par des décennies de recherche. On connaît leur dangerosité pour la santé humaine et environnementale, leur persistance dans le temps et leur omniprésence dans l'eau, les sols, dans une multitude d'objets du quotidien, dans les aliments d'origine animale ou végétale, et jusque dans le sang humain. C'est en étant un peu imperméables à ces alertes que nous avons transmis au Conseil fédéral la motion 25.3421 qui, à la suite du scandale de la viande contaminée aux PFAS, visait à assouplir les valeurs limites de manière à ce que ces produits alimentaires puissent continuer à être écoulés dans le commerce.
-C'est précisément dans ce contexte que la motion Vincenz 25.3902, reprise par notre collègue Matthias Michel dans sa motion 25.3866, est particulièrement intéressante. En effet, l'auteure de la motion constate que malgré les risques, la Suisse manque actuellement d'une base d'information systématique à destination des consommateurs et des consommatrices de produits qui contiennent des PFAS. Elle charge donc le Conseil fédéral de créer les bases légales qui permettraient d'instaurer une obligation de déclaration.
-Dans le contexte actuel, une obligation de déclaration comporte plusieurs avantages. D'une part, elle tient compte du fait que les PFAS sont partout, qu'on ne peut pas toujours les éviter, et que toute trajectoire de diminution doit s'inscrire dans le temps. Dans l'intervalle, elle table sur la transparence, sur l'information, afin de permettre aux consommateurs et consommatrices de faire un choix éclairé au moment de leurs achats. Sans édicter d'interdiction, l'obligation de déclaration joue un rôle de sensibilisation et, possiblement, d'incitation auprès des producteurs et productrices en faveur d'alternatives sans PFAS. Enfin, dans le contexte de l'augmentation des valeurs limites des PFAS, cette obligation de déclaration permettrait de renforcer la confiance dans les produits commercialisés, alors que le rehaussement des valeurs limites suscite au mieux l'inquiétude, au pire le mécontentement auprès des commerces ainsi que des consommateurs et des consommatrices.
+Le rapporteur l'a dit, la majorité de la commission juge que les travaux en cours relatifs aux PFAS justifient de rejeter l'ensemble des motions qui ont été déposées en bloc. J'opposerai à cela l'argument selon lequel la commission n'adopte cette position que de manière très partiale. Nous avons encore tous à l'esprit la kyrielle de motions concernant le loup auxquelles la commission a donné sa bénédiction, souvent contre l'avis du Conseil fédéral, alors même que les travaux étaient déjà en cours, mais passons.
+La deuxième raison pour laquelle il est nécessaire d'examiner en détail chacune de ces motions et de les accepter, c'est précisément parce que nous avons adopté la motion 25.3421, "Fixer des valeurs limites pertinentes pour les PFAS en tenant compte des conséquences pour l'agriculture et les distributeurs d'eau et introduire des mesures de soutien à l'agriculture", qui vise à modifier les valeurs limites fixées pour les PFAS en fonction des intérêts économiques. Cela s'inscrit dans le contexte de la thématique des PFAS, qui repose sur de solides connaissances scientifiques étayées par des décennies de recherche. On connaît leur dangerosité pour la santé humaine et environnementale, leur persistance dans le temps et leur omniprésence dans l'eau, les sols, dans une multitude d'objets du quotidien, dans les aliments d'origine animale ou végétale et jusque dans le sang humain. C'est en étant un peu imperméables à ces alertes que nous avons transmis au Conseil fédéral la motion 25.3421 qui, à la suite du scandale de la viande contaminée aux PFAS, visait à assouplir les valeurs limites de manière à ce que ces produits alimentaires puissent continuer à être écoulés dans le commerce.
+C'est précisément dans ce contexte que la motion Vincenz 25.3902, reprise par notre collègue Matthias Michel dans sa motion 25.3866, est particulièrement intéressante. En effet, l'auteure de la motion constate que, malgré les risques, la Suisse manque actuellement d'une base d'information systématique à destination des consommateurs et des consommatrices de produits qui contiennent des PFAS. Elle charge donc le Conseil fédéral de créer les bases légales qui permettraient d'instaurer une obligation de déclaration.
+Dans le contexte actuel, une obligation de déclaration comporte plusieurs avantages. D'une part, elle tient compte du fait que les PFAS sont partout, qu'on ne peut pas toujours les éviter et que toute trajectoire de diminution doit s'inscrire dans le temps. Dans l'intervalle, elle table sur la transparence, sur l'information, afin de permettre aux consommateurs et consommatrices de faire un choix éclairé au moment de leurs achats. Sans édicter d'interdiction, l'obligation de déclaration joue un rôle de sensibilisation et, possiblement, d'incitation auprès des producteurs et productrices en faveur d'alternatives sans PFAS. Enfin, dans le contexte de l'augmentation des valeurs limites des PFAS, cette obligation de déclaration permettrait de renforcer la confiance dans les produits commercialisés, alors que le rehaussement des valeurs limites suscite au mieux l'inquiétude, au pire le mécontentement, auprès des commerces ainsi que des consommateurs et des consommatrices.
 Je rappelle que la motion prévoit également des cautèles pour ne pas nuire aux intérêts du pays. Elle précise qu'il faut veiller à ce que les obligations soient clairement définies, conformes au droit international, applicables, et que leur mise en oeuvre soit proportionnée.
 Le Conseil fédéral, dans son avis qui propose le rejet de cette motion, invoque les possibles obstacles techniques au commerce qu'impliquerait une déclaration obligatoire. Or, si on lit le mandat que donne la motion, elle ne vise qu'à mettre sur les rails les travaux préparatoires, à savoir la création des bases légales pour une déclaration obligatoire. Le Conseil fédéral aurait, dans le cadre de ses travaux préliminaires, toute latitude pour examiner le cadre législatif et trouver une solution pragmatique et praticable.
-Regardons du côté de nos voisins : il est à noter que l'Union européenne mène actuellement de vastes travaux relatifs à la régulation des PFAS. Les deux commissions de l'Agence européenne des produits chimiques ont récemment émis, pour ce qui concerne le comité d'évaluation des risques, son avis final, et, pour ce qui concerne le comité d'analyses socioéconomiques, qui évalue les risques pour la compétitivité économique des PFAS, son projet d'avis. Ces deux commissions arrivent à la conclusion que les restrictions des PFAS à l'échelle de l'Union européenne sont justifiées, étant attendu que des dérogations spécifiques soient possibles, notamment pour les produits. Ces comités recommandent également que toute restriction soit complétée de mesures efficaces pour minimiser les émissions.
-Le rapport final qui sera transmis à la Commission européenne est attendu pour fin 2026, mais il est à noter que si l'Union européenne devait introduire des obligations de déclaration supplémentaires, la Suisse les examinerait dans le cadre de la reprise autonome. Une adoption de la motion Vincenz et la mise en route correspondante des travaux législatifs permettraient de faciliter, le cas échéant, la reprise des directives européennes de manière à ne pas pénaliser non plus le marché d'exportation suisse.
+Regardons du côté de nos voisins[NB]: il est à noter que l'Union européenne mène actuellement de vastes travaux relatifs à la régulation des PFAS. Les deux commissions de l'Agence européenne des produits chimiques ont récemment émis, pour ce qui concerne le comité d'évaluation des risques, son avis final et, pour ce qui concerne le comité d'analyses socioéconomiques, qui évalue les risques pour la compétitivité économique des PFAS, son projet d'avis. Ces deux commissions arrivent à la conclusion que les restrictions des PFAS à l'échelle de l'Union européenne sont justifiées, étant attendu que des dérogations spécifiques soient possibles, notamment pour les produits. Ces comités recommandent également que toute restriction soit complétée de mesures efficaces pour minimiser les émissions.
+Le rapport final qui sera transmis à la Commission européenne est attendu pour fin 2026, mais il est à noter que, si l'Union européenne devait introduire des obligations de déclaration supplémentaires, la Suisse les examinerait dans le cadre de la reprise autonome. Une adoption de la motion Vincenz et la mise en route correspondante des travaux législatifs permettraient de faciliter, le cas échéant, la reprise des directives européennes de manière à ne pas pénaliser non plus le marché d'exportation suisse.
 La motion Vincenz 25.3902 offre une solution raisonnable et pragmatique. Je vous invite, dès lors, à suivre la décision du Conseil national, qui l'a déjà adoptée, et à l'adopter à votre tour en acceptant ma proposition de minorité.
 </t>
   </si>
@@ -77,11 +77,11 @@
   </si>
   <si>
     <t xml:space="preserve">La prémisse de cette motion Würth s'appuie sur un sous-entendu qui est à mon sens problématique, y compris au niveau institutionnel, à savoir que les valeurs limites édictées par le Conseil fédéral en matière de PFAS l'ont été jusqu'à présent en l'absence de base légale. Or, l'ordonnance sur les contaminants, qui fixe les valeurs limites des PFAS dans son annexe 8, repose sur l'ordonnance sur les denrées alimentaires et les objets usuels, elle-même fondée sur la loi fédérale sur les denrées alimentaires, la loi sur la protection de l'environnement, la loi sur le génie génétique et la loi sur la sécurité des produits. En matière de bases légales, nous avons donc quand même l'arsenal nécessaire. Je rappelle aussi que, concernant les PFAS, nous avons adopté en 2022 la motion Maret Marianne 22.3929, "Définition dans les ordonnances de valeurs spécifiques aux PFAS". Par conséquent, prétendre maintenant que la base légale fait défaut est factuellement faux.
-La directive de l'OSAV 2026/1, que la présente motion entend supprimer, ne fait donc que reprendre la situation réglementaire qui prévaut actuellement. Sous l'intitulé "Application des teneurs maximales fixées pour les substances per- et polyfluoroalkylées (PFAS)", elle a simplement pour objectif de garantir une application uniforme des teneurs maximales fixées dans les denrées alimentaires, quelles que soient ces teneurs. Elle précise également les compétences et les responsabilités des autorités cantonales chargées de l'exécution de la législation sur les denrées alimentaires. La loi spéciale à laquelle fait référence la présente motion fait suite à la motion 25.3421 que nous avons acceptée, et qui, sous un intitulé relativement lénifiant, à savoir "Fixer des valeurs limites pertinentes pour les PFAS en tenant compte des conséquences pour l'agriculture et les distributeurs d'eau et introduire des mesures de soutien à l'agriculture", cache une réalité passablement crue : elle vise à augmenter les plafonds afin que les producteurs de viande contaminée notamment puissent continuer à écouler leurs marchandises. C'est une solution que j'avais comparée dans le débat d'alors au fait d'augmenter la limitation de vitesse dans le but de diminuer le nombre d'excès de vitesse.
+La directive de l'OSAV 2026/1, que la présente motion entend supprimer, ne fait donc que reprendre la situation réglementaire qui prévaut actuellement. Sous l'intitulé "Application des teneurs maximales fixées pour les substances per- et polyfluoroalkylées (PFAS)", elle a simplement pour objectif de garantir une application uniforme des teneurs maximales fixées dans les denrées alimentaires, quelles que soient ces teneurs. Elle précise également les compétences et les responsabilités des autorités cantonales chargées de l'exécution de la législation sur les denrées alimentaires. La loi spéciale à laquelle fait référence la présente motion fait suite à la motion 25.3421 que nous avons acceptée, et qui, sous un intitulé relativement lénifiant, à savoir "Fixer des valeurs limites pertinentes pour les PFAS en tenant compte des conséquences pour l'agriculture et les distributeurs d'eau et introduire des mesures de soutien à l'agriculture", cache une réalité passablement crue[NB]: elle vise à augmenter les plafonds afin que les producteurs de viande contaminée, notamment, puissent continuer à écouler leurs marchandises. C'est une solution que j'avais comparée dans le débat d'alors au fait d'augmenter la limitation de vitesse dans le but de diminuer le nombre d'excès de vitesse.
 C'est donc bien cette loi spéciale qui vise à changer la pratique actuelle conformément à la procédure ordinaire. Ce projet de loi spéciale est maintenant en consultation et devra ensuite suivre le cours de la procédure normale.
-Monsieur Würth, vous avez dit hier dans le débat sur le Mercosur : 
-"Insofern glaube ich als Ständerat, dass wir nicht Dinge, die in der Vernehmlassung sind, quasi im Expresstempo in einen Bundesbeschluss schreiben sollten."
-Je suis d'accord avec vous sur le fait qu'un objet en consultation doit suivre son cours normal et que nous ne devrions pas anticiper des résultats pas encore issus de la procédure ordinaire. Dès lors, si à l'issue de la procédure de consultation sur la modification des valeurs limites, le Conseil fédéral modifie cette dernière, l'OSAV procédera évidemment à l'adaptation de ces directives. Ce n'est pas à nous, ce n'est pas au Parlement, d'anticiper le résultat d'une consultation et l'adoption de la loi spéciale par le Conseil fédéral, au contraire, ce serait un signal extrêmement singulier.
+Monsieur Würth, vous avez dit hier dans le débat sur le Mercosur[NB]: 
+"Insofern glaube ich, dass wir als Ständerat nicht Dinge, die in der Vernehmlassung sind, quasi im Expresstempo in einen Bundesbeschluss schreiben sollten."
+Je suis d'accord avec vous sur le fait qu'un objet en consultation doit suivre son cours normal et que nous ne devrions pas anticiper des résultats pas encore issus de la procédure ordinaire. Dès lors, si, à l'issue de la procédure de consultation sur la modification des valeurs limites, le Conseil fédéral modifie cette dernière, l'OSAV procédera évidemment à l'adaptation de ces directives. Ce n'est pas à nous, ce n'est pas au Parlement, d'anticiper le résultat d'une consultation et l'adoption de la loi spéciale par le Conseil fédéral. Au contraire, ce serait un signal extrêmement singulier.
 Dès lors, je vous invite à ne pas anticiper les résultats de la consultation de cette loi spéciale, à laisser le processus démocratique se dérouler et à rejeter la motion Würth. Si les valeurs limites des PFAS doivent être changées, elles le seront dans le temps ordinaire de la procédure législative.
 </t>
   </si>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Stettler Thomas</t>
   </si>
   <si>
-    <t xml:space="preserve">Monsieur le président de la Confédération, les importations actuelles de viande sont inférieures aux quantités concédées dans l'accord, si bien que l'équilibre ne devrait pas être ébranlé et que les prix aux producteurs devraient être maintenus. Cela m'encourage plutôt à soutenir cet accord. Qu'en serait-il si la consommation indigène devait s'effondrer, comme cela a été le cas au moment de la crise de la vache folle ? Pouvez-vous me rassurer sur cet élément ?
+    <t xml:space="preserve">Monsieur le président de la Confédération, les importations actuelles de viande sont inférieures aux quantités concédées dans l'accord, si bien que l'équilibre ne devrait pas être ébranlé et que les prix aux producteurs devraient être maintenus. Cela m'encourage plutôt à soutenir cet accord. Qu'en serait-il si la consommation indigène devait s'effondrer, comme cela a été le cas au moment de la crise de la vache folle[NB]? Pouvez-vous me rassurer sur cet élément[NB]?
 </t>
   </si>
   <si>
@@ -156,16 +156,16 @@
     <t xml:space="preserve">VD</t>
   </si>
   <si>
-    <t xml:space="preserve">Nous traitons aujourd'hui un dossier qui touche à la sécurité de notre pays. Cette première modification de la loi sur le renseignement (LRens) va dans la bonne direction. Deux autres paquets de modifications sont encore prévus. Ils seront présentés prochainement. L'un d'entre eux est en consultation et le suivant traitera de ce qui touche au Tribunal administratif fédéral, avec des modifications légales.
-Cette modification n'est pas trop rapide, car la géopolitique a changé. Les blocs politique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nous traitons aujourd'hui un dossier qui touche à la sécurité de notre pays. Cette première modification de la loi sur le renseignement (LRens) va dans la bonne direction. Deux autres paquets de modifications sont encore prévus. Ils seront présentés prochainement. L'un d'entre eux est en consultation et le suivant traitera de ce qui touche au Tribunal administratif fédéral, avec des modifications légales.
-Cette modification n'est pas trop rapide, car la géopolitique a changé. Les blocs politiques sont en train d'évoluer. Les outils de renseignement, d'écoute, d'espionnage, ainsi que l'avènement et le renforcement de l'utilisation de l'IA nous obligent à réagir. Nous avons une responsabilité vis-à-vis de notre population. On le voit avec certaines informations ou renseignements mal utilisés ou pas utilisés du tout, comme avec l'attentat du 7 octobre en Israël. Ils sont en pleine campagne électorale. Est-ce vrai ou pas ? Le gouvernement israélien était-il au courant des attentats qui se préparaient ? Acte potentiel de terrorisme : on sait qu'à l'échelle internationale, d'autres pays nous renseignent. Il nous semble important de pouvoir se coordonner et d'anticiper ces différents aspects.
-Le renforcement du Service de renseignement de la Confédération (SRC) est fondamental pour détecter précocement les menaces. Il en va de notre devoir d'anticiper. Comme on dit : mieux vaut prévenir que guérir. Nous devrons veiller à mettre en place des garde-fous supplémentaires et des voies de droit. Le projet va dans ce sens. En cas de besoin, la loi pourra toujours être adaptée et corrigée.
-Je ne vais pas commenter tout le projet de loi, qui me convient globalement, mais me concentrer, dans ce débat d'entrée en matière, sur quelques éléments qui concernent les cantons. La capacité opérationnelle des autorités cantonales d'exécution reste insuffisante dans le projet du Conseil fédéral. Dans un contexte sécuritaire qui se dégrade, les services de renseignement cantonaux constituent un maillage essentiel du renseignement en Suisse. À ce propos, pour ceux qui s'en souviennent, en ce qui concerne l'attentat qui a conduit à un meurtre à Morges, on ne sait toujours pas si le canton était au courant ou pas. L'échelon fédéral a-t-il correctement informé les cantons ? Des enquêtes sont toujours en cours. On voit que le maillage cantons-Confédération est important, surtout pour les cantons qui ont des services organisés principalement en lien avec la police.
-Dans un contexte sécuritaire qui se dégrade, les services de renseignement cantonaux constituent donc un maillage essentiel à l'échelle suisse. Il est ainsi nécessaire que les acteurs cantonaux disposent de moyens suffisants pour effectuer leur travail. Les services cantonaux fournissent le gros du travail de surveillance et assurent la recherche d'informations sur le territoire suisse ; informations qui profitent au SRC.
-C'est pourquoi j'ai déposé en commission des propositions visant à maintenir la capacité opérationnelle des services de renseignement cantonaux. Le principe de ces propositions est soutenu par de nombreux cantons, dont les cantons de Vaud, du Jura, du Valais, de Berne, d'Argovie, de Thurgovie, du Tessin, de Genève, voire de Fribourg. La première proposition - j'y reviendrai dans le cadre de la discussion par article - permet de prévoir une exploitation technique réaliste des appareils de localisation lors d'observations, y compris pour les services de renseignement cantonaux. La deuxième proposition permet de garantir le traitement des données personnelles et le profilage par les autorités cantonales d'exécution. En commission, on m'a dit que c'était implicite, mais, dans le domaine du renseignement, il est parfois mieux de l'indiquer dans la loi.
+    <t xml:space="preserve">Nous traitons aujourd'hui un dossier qui touche à la sécurité de notre pays. Cette première modification de la loi sur le renseignement (LRens) va dans la bonne direction. Deux autres paquets de modifications sont encore prévus. Ils seront présentés prochainement. L'un d'entre eux est en consultation, et le suivant traitera de ce qui touche au Tribunal administratif fédéral, avec des modifications légales.
+Cette modification n'est pas trop rapide, car la géopolitique a changé. Les blocs politiqu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nous traitons aujourd'hui un dossier qui touche à la sécurité de notre pays. Cette première modification de la loi sur le renseignement (LRens) va dans la bonne direction. Deux autres paquets de modifications sont encore prévus. Ils seront présentés prochainement. L'un d'entre eux est en consultation, et le suivant traitera de ce qui touche au Tribunal administratif fédéral, avec des modifications légales.
+Cette modification n'est pas trop rapide, car la géopolitique a changé. Les blocs politiques sont en train d'évoluer. Les outils de renseignement, d'écoute, d'espionnage, ainsi que l'avènement et le renforcement de l'utilisation de l'IA nous obligent à réagir. Nous avons une responsabilité vis-à-vis de notre population. On le voit avec certaines informations ou renseignements mal utilisés ou pas utilisés du tout, comme avec l'attentat du 7 octobre en Israël. Ils sont en pleine campagne électorale. Est-ce vrai ou pas[NB]? Le gouvernement israélien était-il au courant des attentats qui se préparaient[NB]? Acte potentiel de terrorisme[NB]: on sait qu'à l'échelle internationale, d'autres pays nous renseignent. Il nous semble important de pouvoir se coordonner et d'anticiper ces différents aspects.
+Le renforcement du Service de renseignement de la Confédération (SRC) est fondamental pour détecter précocement les menaces. Il en va de notre devoir d'anticiper. Comme on dit[NB]: mieux vaut prévenir que guérir. Nous devrons veiller à mettre en place des garde-fous supplémentaires et des voies de droit. Le projet va dans ce sens. En cas de besoin, la loi pourra toujours être adaptée et corrigée.
+Je ne vais pas commenter tout le projet de loi, qui me convient globalement, mais me concentrer, dans ce débat d'entrée en matière, sur quelques éléments qui concernent les cantons. La capacité opérationnelle des autorités cantonales d'exécution reste insuffisante dans le projet du Conseil fédéral. Dans un contexte sécuritaire qui se dégrade, les services de renseignement cantonaux constituent un maillage essentiel du renseignement en Suisse. À ce propos, pour ceux qui s'en souviennent, en ce qui concerne l'attentat qui a conduit à un meurtre à Morges, on ne sait toujours pas si le canton était au courant ou pas. L'échelon fédéral a-t-il correctement informé les cantons[NB]? Des enquêtes sont toujours en cours. On voit que le maillage cantons-Confédération est important, surtout pour les cantons qui ont des services organisés principalement en lien avec la police.
+Dans un contexte sécuritaire qui se dégrade, les services de renseignement cantonaux constituent donc un maillage essentiel à l'échelle suisse. Il est ainsi nécessaire que les acteurs cantonaux disposent de moyens suffisants pour effectuer leur travail. Les services cantonaux fournissent le gros du travail de surveillance et assurent la recherche d'informations sur le territoire suisse[NB]; ces informations profitent au SRC.
+C'est pourquoi j'ai déposé en commission des propositions visant à maintenir la capacité opérationnelle des services de renseignement cantonaux. Le principe de ces propositions est soutenu par de nombreux cantons, notamment les cantons de Vaud, du Jura, du Valais, de Berne, d'Argovie, de Thurgovie, du Tessin, de Genève, voire de Fribourg. La première proposition - j'y reviendrai dans le cadre de la discussion par article - permet de prévoir une exploitation technique réaliste des appareils de localisation lors d'observations, y compris pour les services de renseignement cantonaux. La deuxième proposition permet de garantir le traitement des données personnelles et le profilage par les autorités cantonales d'exécution. En commission, on m'a dit que c'était implicite, mais, dans le domaine du renseignement, il est parfois mieux de l'indiquer dans la loi.
 Je vous encourage à entrer en matière, à soutenir le Conseil fédéral et ensuite à adopter mes deux propositions de minorité.
 </t>
   </si>
@@ -174,14 +174,14 @@
   </si>
   <si>
     <t xml:space="preserve">Notre Commission des affaires juridiques a examiné le protocole d'amendement à la Convention d'établissement conclue entre la Suisse et l'Iran lors de sa séance du 26 juin dernier et l'a approuvé.
-La Suisse a conclu la présente convention d'établissement avec l'Iran, alors l'Empire de Perse, en 1934. Cette convention prévoyait, pour ce qui concerne le droit des personnes et de la famille, ainsi que le droit successoral, que ce soit le droit iranien qui s'applique aux ressortissants en Suisse. El</t>
+La Suisse a conclu la présente convention d'établissement avec l'Iran, alors encore Empire perse, en 1934. Cette convention prévoyait, pour ce qui concerne le droit des personnes et de la famille, ainsi que le droit successoral, que ce soit le droit iranien qui s'applique aux ressortissants établis en </t>
   </si>
   <si>
     <t xml:space="preserve">Notre Commission des affaires juridiques a examiné le protocole d'amendement à la Convention d'établissement conclue entre la Suisse et l'Iran lors de sa séance du 26 juin dernier et l'a approuvé.
-La Suisse a conclu la présente convention d'établissement avec l'Iran, alors l'Empire de Perse, en 1934. Cette convention prévoyait, pour ce qui concerne le droit des personnes et de la famille, ainsi que le droit successoral, que ce soit le droit iranien qui s'applique aux ressortissants en Suisse. Elle contient en outre des mesures de protection pour les ressortissants et ressortissantes de chacun des deux États et règle, entre autres, la liberté de voyager et le droit d'exercer un travail. Or, l'application du droit de la famille iranien dans notre pays est problématique pour la justice suisse, ainsi qu'en regard des droits fondamentaux. Certaines des dispositions du droit iranien de la famille sont incompatibles avec l'ordre public et donc inapplicables, ce qui entraîne une insécurité juridique. Il engendre également une inégalité de traitement par rapport au reste de la population résidente, a priori soumise au droit de l'État de domicile.
-Signé à Téhéran le 18 décembre 2024 et adopté par le Conseil fédéral le 19 décembre 2025, le protocole d'amendement qui nous est soumis aujourd'hui supprime les dispositions relatives au droit applicable contenues à l'article 8 de la convention. Dès lors, les ressortissants et ressortissantes de nationalité iranienne en Suisse seront soumis aux règles du droit international privé et aux conventions de La Haye en matière de protection de l'enfant et de l'adulte, ainsi que notamment sur les obligations alimentaires. Les règles internationales renvoient au droit en vigueur au lieu de domicile et de résidence et c'est donc le droit suisse qui s'appliquera dorénavant. L'amendement à la convention concernera potentiellement plusieurs milliers de personnes de nationalité iranienne en Suisse. Jusqu'à présent, les dispositions de la convention renvoyaient au droit iranien, par exemple pour ce qui concerne les conditions de divorce ou encore la garde et l'entretien des enfants, lorsque l'ensemble des personnes concernées étaient iraniennes. D'une part, cela soulevait des questions légitimes en matière de droit des personnes. D'autre part, dans la pratique, les tribunaux suisses renonçaient fréquemment à appliquer ce droit au motif de la réserve de l'ordre public. À l'inverse, très peu de personnes de nationalité suisse sont actuellement établies en Iran : moins de 10 selon les informations reçues par la commission, hormis le personnel diplomatique. Pour ces personnes, il est toutefois à relever que l'Iran applique déjà à l'heure actuelle le droit de l'État d'origine dans les cas relevant de la famille et des successions.
-Lors de la consultation, le protocole d'amendement a été approuvé à l'unanimité, quelques participants déplorant toutefois le temps qui a été nécessaire pour aboutir à ce résultat. À noter également que la Convention d'établissement conclue entre la Suisse et l'Iran a donné lieu à plusieurs interventions parlementaires par le passé, qui dénonçaient l'applicabilité d'un droit national peu compatible avec les valeurs de la Suisse. Le présent amendement résout ce problème tout en maintenant les acquis de la convention dans d'autres domaines qui contribuent à la stabilité des relations entre la Suisse et l'Iran.
-En un mot commençant, le protocole d'amendement à la Convention d'établissement conclue entre la Suisse et l'Iran améliore notablement la sécurité juridique et les droits fondamentaux des personnes concernées. La Commission des affaires juridiques a salué ces améliorations, relevant qu'au regard de la dégradation des droits fondamentaux depuis la signature de la convention en 1934, en particulier des droits des femmes, il était plus que temps de placer les ressortissants et ressortissantes iraniens établis en Suisse sous la protection du droit suisse des personnes, de la famille et des successions. La commission salue également les négociations menées par la Suisse pour parvenir à ce résultat.
+La Suisse a conclu la présente convention d'établissement avec l'Iran, alors encore Empire perse, en 1934. Cette convention prévoyait, pour ce qui concerne le droit des personnes et de la famille, ainsi que le droit successoral, que ce soit le droit iranien qui s'applique aux ressortissants établis en Suisse. Elle contient en outre des mesures de protection pour les ressortissants et ressortissantes de chacun des deux États et règle, entre autres, la liberté de voyager et le droit d'exercer un travail. Or, l'application du droit de la famille iranien dans notre pays est problématique pour la justice suisse, ainsi qu'en regard des droits fondamentaux. Certaines des dispositions du droit iranien de la famille sont incompatibles avec l'ordre public et donc inapplicables, ce qui entraîne une insécurité juridique. Il engendre également une inégalité de traitement par rapport au reste de la population résidente, a priori soumise au droit de l'État de domicile.
+Signé à Téhéran le 18 décembre 2024 et adopté par le Conseil fédéral le 19 décembre 2025, le protocole d'amendement qui nous est soumis aujourd'hui supprime les dispositions relatives au droit applicable contenues à l'article 8 de la convention. Dès lors, les ressortissants et ressortissantes de nationalité iranienne établis en Suisse seront soumis aux règles du droit international privé et aux conventions de La Haye en matière de protection de l'enfant et de l'adulte, ainsi que notamment sur les obligations alimentaires. Les règles internationales renvoient au droit en vigueur au lieu de domicile et de résidence, et c'est donc le droit suisse qui s'appliquera dorénavant. L'amendement à la convention concernera potentiellement plusieurs milliers de personnes de nationalité iranienne en Suisse. Jusqu'à présent, les dispositions de la convention renvoyaient au droit iranien, par exemple pour ce qui concerne les conditions de divorce ou encore la garde et l'entretien des enfants, lorsque l'ensemble des personnes concernées étaient iraniennes. D'une part, cela soulevait des questions légitimes en matière de droit des personnes. D'autre part, dans la pratique, les tribunaux suisses renonçaient fréquemment à appliquer ce droit au motif de la réserve de l'ordre public. À l'inverse, très peu de personnes de nationalité suisse sont actuellement établies en Iran[NB]: moins de 10 selon les informations reçues par la commission, hormis le personnel diplomatique. Pour ces personnes, il est toutefois à relever que l'Iran applique déjà à l'heure actuelle le droit de l'État d'origine dans les cas relevant de la famille et des successions.
+Lors de la consultation, le protocole d'amendement a été approuvé à l'unanimité, quelques participants déplorant toutefois le temps qui a été nécessaire pour aboutir à ce résultat. À noter également que la Convention d'établissement conclue entre la Suisse et l'Iran a par le passé donné lieu à plusieurs interventions parlementaires qui dénonçaient l'applicabilité d'un droit national peu compatible avec les valeurs de la Suisse. Le présent amendement résout ce problème tout en maintenant les acquis de la convention dans d'autres domaines qui contribuent à la stabilité des relations entre la Suisse et l'Iran.
+En un mot comme en cent, le protocole d'amendement à la Convention d'établissement conclue entre la Suisse et l'Iran améliore notablement la sécurité juridique et les droits fondamentaux des personnes concernées. La Commission des affaires juridiques a salué ces améliorations, relevant qu'au regard de la dégradation des droits fondamentaux, en particulier les droits des femmes, depuis la signature de la convention en 1934, il était plus que temps de placer les ressortissants et ressortissantes iraniens établis en Suisse sous la protection du droit suisse des personnes, de la famille et des successions. La commission salue également les négociations menées par la Suisse pour parvenir à ce résultat.
 Elle est donc entrée en matière sans opposition et a approuvé à l'unanimité l'arrêté fédéral portant approbation du protocole d'amendement et vous invite à en faire de même.
 </t>
   </si>
@@ -195,10 +195,10 @@
     <t xml:space="preserve">M-E</t>
   </si>
   <si>
-    <t xml:space="preserve">Je prendrai exactement le même exemple que notre collègue présidente de la Délégation des Commissions de gestion (DélCdG), mais pour vous dire de soutenir la proposition de la minorité de la commission. Faisons de la politique fiction ; imaginons qu'un parti gouvernemental de notre pays soit tout à coup infiltré par des éléments extrémistes provenant de l'étranger qui seraient susceptibles de prendre à contre-pied la politique menée par notre pays ou par ce parti même au sein du Conseil fédéral,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je prendrai exactement le même exemple que notre collègue présidente de la Délégation des Commissions de gestion (DélCdG), mais pour vous dire de soutenir la proposition de la minorité de la commission. Faisons de la politique fiction ; imaginons qu'un parti gouvernemental de notre pays soit tout à coup infiltré par des éléments extrémistes provenant de l'étranger qui seraient susceptibles de prendre à contre-pied la politique menée par notre pays ou par ce parti même au sein du Conseil fédéral, et qui seraient susceptibles de mettre en danger l'ordre politique et juridique suisses. En tant que responsable de ce parti, je serais très content que le Service de renseignement de la Confédération (SRC) s'y intéresse et puisse nous prévenir en nous informant que nous avons un problème, un risque, qu'il y a une suspicion qui pourrait nous mettre en danger et nous mettre en porte-à-faux avec la Constitution de ce pays. C'est la raison pour laquelle je soutiens la proposition de la minorité Gmür-Schönenberger à l'article 5 alinéa 6 lettre c, qui permettrait précisément au SRC de protéger cette organisation contre son avis, peut-être, ou en l'absence de son avis, parce qu'elle n'est pas consciente du risque qu'elle encourt. Par le biais de cette disposition, avec toutes les restrictions qui sont contenues dans la loi et qui sont justifiées dans un État de droit, je serais content, en tant que responsable de cette organisation, que quelqu'un m'avertisse qu'un risque est encouru par mon organisation.
+    <t xml:space="preserve">Je prendrai exactement le même exemple que notre collègue présidente de la Délégation des Commissions de gestion (DélCdG), mais pour vous dire de soutenir la proposition de la minorité de la commission. Faisons de la politique fiction[NB]; imaginons qu'un parti gouvernemental de notre pays soit tout à coup infiltré par des éléments extrémistes provenant de l'étranger qui seraient susceptibles de prendre à contre-pied la politique menée par notre pays ou par ce parti même au sein du Conseil fédér</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je prendrai exactement le même exemple que notre collègue présidente de la Délégation des Commissions de gestion (DélCdG), mais pour vous dire de soutenir la proposition de la minorité de la commission. Faisons de la politique fiction[NB]; imaginons qu'un parti gouvernemental de notre pays soit tout à coup infiltré par des éléments extrémistes provenant de l'étranger qui seraient susceptibles de prendre à contre-pied la politique menée par notre pays ou par ce parti même au sein du Conseil fédéral, et qui seraient susceptibles de mettre en danger l'ordre politique et juridique suisses. En tant que responsable de ce parti, je serais très content que le Service de renseignement de la Confédération (SRC) s'y intéresse et puisse nous prévenir en nous informant que nous avons un problème, un risque, qu'il y a une suspicion qui pourrait nous mettre en danger et nous mettre en porte-à-faux avec la Constitution de ce pays. C'est la raison pour laquelle je soutiens la proposition de la minorité Gmür-Schönenberger à l'article 5 alinéa 6 lettre c, qui permettrait précisément au SRC de protéger cette organisation contre son avis, peut-être, ou en l'absence de son avis, parce qu'elle n'est pas consciente du risque qu'elle encourt. Par le biais de cette disposition, avec toutes les restrictions qui sont contenues dans la loi et qui sont justifiées dans un État de droit, je serais content, en tant que responsable de cette organisation, que quelqu'un m'avertisse qu'un risque est encouru par mon organisation.
 C'est la raison pour laquelle je vous invite vraiment à soutenir la proposition de la minorité Gmür-Schönenberger, selon le projet du Conseil fédéral.
 </t>
   </si>
@@ -206,21 +206,21 @@
     <t xml:space="preserve">419288</t>
   </si>
   <si>
-    <t xml:space="preserve">Ma motion porte sur un sujet encore trop peu visible, à mon avis, dans le débat public, mais qui concerne directement la sécurité de notre pays, de notre économie et de nos infrastructures. Nous parlons aujourd'hui de cryptographie post-quantique. Cela peut sembler très technique, mais en réalité, derrière ce terme se cache une question très simple : comment garantir que les données et les communications que nous protégeons aujourd'hui resteront protégées demain.
-Notre société repose sur la cryp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ma motion porte sur un sujet encore trop peu visible, à mon avis, dans le débat public, mais qui concerne directement la sécurité de notre pays, de notre économie et de nos infrastructures. Nous parlons aujourd'hui de cryptographie post-quantique. Cela peut sembler très technique, mais en réalité, derrière ce terme se cache une question très simple : comment garantir que les données et les communications que nous protégeons aujourd'hui resteront protégées demain.
+    <t xml:space="preserve">Ma motion porte sur un sujet encore trop peu visible, à mon avis, dans le débat public, mais qui concerne directement la sécurité de notre pays, de notre économie et de nos infrastructures. Nous parlons aujourd'hui de cryptographie post-quantique. Cela peut sembler très technique, mais en réalité, derrière ce terme se cache une question très simple[NB]: comment garantir que les données et les communications que nous protégeons aujourd'hui resteront protégées demain.
+Notre société repose sur la c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma motion porte sur un sujet encore trop peu visible, à mon avis, dans le débat public, mais qui concerne directement la sécurité de notre pays, de notre économie et de nos infrastructures. Nous parlons aujourd'hui de cryptographie post-quantique. Cela peut sembler très technique, mais en réalité, derrière ce terme se cache une question très simple[NB]: comment garantir que les données et les communications que nous protégeons aujourd'hui resteront protégées demain.
 Notre société repose sur la cryptographie. Les paiements électroniques, les communications de l'administration, les dossiers médicaux, les identités numériques, les signatures électroniques, les systèmes industriels ou encore les infrastructures critiques dépendent tous, à des degrés divers, de mécanismes cryptographiques. Or, certains des algorithmes de cryptographie à clé publique que nous utilisons actuellement pourraient être rendus vulnérables par des ordinateurs quantiques suffisamment puissants.
-Le problème est que nous ne pouvons pas attendre le jour où un ordinateur quantique capable de casser ses protections sera disponible pour commencer à agir. Pourquoi cela ? Parce que la migration cryptographique est un processus long, complexe et coûteux. Il faut identifier les systèmes concernés, comprendre leurs dépendances, vérifier les logiciels et les équipements, travailler avec les fournisseurs, tester les nouveaux mécanismes, garantir l'interopérabilité et, dans certains cas, remplacer des systèmes qui ont une durée de vie de dix, vingt ou trente ans. Autrement dit, le moment d'agir est avant que la menace ne devienne opérationnelle.
+Le problème est que nous ne pouvons pas attendre le jour où un ordinateur quantique capable de casser ses protections sera disponible pour commencer à agir. Pourquoi cela[NB]? Parce que la migration cryptographique est un processus long, complexe et coûteux. Il faut identifier les systèmes concernés, comprendre leurs dépendances, vérifier les logiciels et les équipements, travailler avec les fournisseurs, tester les nouveaux mécanismes, garantir l'interopérabilité et, dans certains cas, remplacer des systèmes qui ont une durée de vie de dix, vingt ou trente ans. Autrement dit, il faut agir avant que la menace ne devienne opérationnelle.
 Il existe également un risque, déjà présent aujourd'hui, de "moissonner maintenant pour déchiffrer plus tard". Des données peuvent être capturées aujourd'hui alors qu'elles sont encore correctement protégées. Si leurs valeurs ou leur caractère confidentiel perdurent pendant dix, vingt ou trente ans, elles pourraient être déchiffrées à l'avenir lorsque les capacités technologiques le permettront. Cela concerne notamment les informations de l'État, les données médicales, les données de recherche, les secrets industriels ou certaines informations liées à la sécurité nationale. Nous devons donc raisonner non seulement en fonction de la menace actuelle, mais aussi de la durée pendant laquelle une information doit rester confidentielle.
-C'est précisément ce que vise ma motion : ne pas céder à la panique et ne pas imposer une technologie particulière, mais planifier la transition de manière progressive, coordonnée et fondée sur les risques. C'est un élément essentiel. Sans inventaire, nous ne pouvons pas piloter correctement une migration. C'est pourquoi la notion de crypto-agilité est particulièrement importante. Nos systèmes doivent être conçus de manière à pouvoir faire évoluer leurs mécanismes cryptographiques sans devoir tout reconstruire à chaque changement de standard.
-C'est une question de cybersécurité, mais également une question de bonne gestion des deniers publics. Si une migration anticipée peut être planifiée, une migration imposée dans l'urgence risque quant à elle d'être beaucoup plus coûteuse, plus complexe et beaucoup plus risquée. La Suisse ne part heureusement pas de zéro. La Confédération a déjà identifié cette problématique et dispose de compétences importantes dans le domaine de la cybersécurité et de l'informatique. Ce qui manque encore, c'est précisément une vision nationale, commune, avec des responsabilités, des priorités et des échéances clairement définies.
-Nos partenaires internationaux avancent : l'Union européenne travaille sur la transition vers la cryptographie post-quantique, et les États-Unis, le Royaume-Uni, la France et l'Allemagne ont également engagé des démarches. La motion prévoit à juste titre des échéances différenciées, une priorité aux cas à haut risque d'ici 2030, puis une transition progressive des autres systèmes critiques ou sensibles d'ici 2035 en fonction de la maturité des standards et de l'interopérabilité. Cette approche permet d'éviter deux erreurs. La première serait de ne rien faire en attendant que la menace soit certaine. La seconde serait d'imposer aujourd'hui des investissements massifs dans des technologies qui pourraient encore évoluer. La bonne réponse se situe entre les deux : préparer maintenant, migrer progressivement et adapter les exigences sur le plan des risques.
-Permettez-moi de revenir encore quelques instants sur l'avis du Conseil fédéral. Il reconnait l'importance du sujet et je l'en remercie, mais il rejette le point relatif au soutien aux cantons, aux PME, aux entreprises et aux hautes écoles au motif que certaines mesures dépasseraient les compétences actuelles de la Confédération. Je me rallie à sa proposition et ne conteste pas le rejet de la lettre i. Je souhaite néanmoins, pour la clarté des délibérations et la mise en oeuvre à venir, préciser l'esprit de cette lettre i. Mon intention n'a jamais été de créer une compétence fédérale nouvelle ni de transférer à la Confédération une responsabilité qui incombe aux cantons, aux entreprises et aux hautes écoles en matière de cybersécurité, car la responsabilité individuelle de chaque acteur demeure entière. Sur ce point, je partage entièrement l'analyse du Conseil fédéral.
+C'est précisément ce que vise ma motion[NB]: ne pas céder à la panique et ne pas imposer une technologie particulière, mais planifier la transition de manière progressive, coordonnée et fondée sur les risques. C'est un élément essentiel. Sans inventaire, nous ne pouvons pas piloter correctement une migration. C'est pourquoi la notion de cryptoagilité est particulièrement importante. Nos systèmes doivent être conçus de manière à pouvoir faire évoluer leurs mécanismes cryptographiques sans devoir tout reconstruire à chaque changement de standard.
+C'est une question de cybersécurité, mais également de bonne gestion des deniers publics. Si une migration anticipée peut être planifiée, une migration imposée dans l'urgence risque quant à elle d'être beaucoup plus coûteuse, plus complexe et plus risquée. La Suisse ne part heureusement pas de zéro. La Confédération a déjà identifié cette problématique et dispose de compétences importantes dans le domaine de la cybersécurité et de l'informatique. Ce qui manque encore, c'est précisément une vision nationale, commune, avec des responsabilités, des priorités et des échéances clairement définies.
+Nos partenaires internationaux avancent[NB]: l'Union européenne travaille sur la transition vers la cryptographie post-quantique, et les États-Unis, le Royaume-Uni, la France et l'Allemagne ont également engagé des démarches. La motion prévoit à juste titre des échéances différenciées, une priorité aux cas à haut risque d'ici 2030, puis une transition progressive des autres systèmes critiques ou sensibles d'ici 2035, en fonction de la maturité des standards et de l'interopérabilité. Cette approche permet d'éviter deux erreurs. La première serait de ne rien faire en attendant que la menace soit certaine. La seconde serait d'imposer aujourd'hui des investissements massifs dans des technologies qui pourraient encore évoluer. La bonne réponse se situe entre les deux[NB]: préparer maintenant, migrer progressivement et adapter les exigences sur le plan des risques.
+Permettez-moi de revenir encore quelques instants sur l'avis du Conseil fédéral. Il reconnaît l'importance du sujet et je l'en remercie, mais il rejette le point relatif au soutien aux cantons, aux PME, aux entreprises et aux hautes écoles au motif que certaines mesures dépasseraient les compétences actuelles de la Confédération. Je me rallie à sa proposition et ne conteste pas le rejet de la lettre i. Je souhaite néanmoins, pour la clarté des délibérations et la mise en oeuvre à venir, préciser l'esprit de cette lettre i. Mon intention n'a jamais été de créer une compétence fédérale nouvelle ni de transférer à la Confédération une responsabilité qui incombe aux cantons, aux entreprises et aux hautes écoles en matière de cybersécurité, car la responsabilité individuelle de chaque acteur demeure entière. Sur ce point, je partage entièrement l'analyse du Conseil fédéral.
 Ce que visait la lettre i, c'est la coordination et non le soutien financier. Une transition vers la cryptographie post-quantique, conduite en ordre dispersé, sans référentiel commun ni interopérabilité, coûterait beaucoup plus cher à tous et affaiblirait la sécurité de l'ensemble. Je prends donc acte du fait que le Conseil fédéral, dans le cadre de ses compétences, assurera cette coordination, avec la mise à disposition de lignes directrices, de modèles d'inventaire, de tests d'interopérabilité et de retours d'expériences utiles aux cantons et à l'économie. Je forme le voeu que le rapport biennal, prévu à la lettre c, rende compte de la manière dont cette coordination est assurée afin que le Parlement puisse en suivre les effets.
-En résumé et pour conclure, la cryptographie post-quantique n'est peut-être pas encore une urgence visible pour la population. Mais précisément parce que la transition prendra du temps, il est nécessaire d'agir aujourd'hui avant que cela ne devienne une urgence.
-Je vous invite donc à soutenir ma motion sans la lettre i, comme demandé par le Conseil fédéral, et je vous en remercie.
+En résumé et pour conclure, la cryptographie post-quantique n'est peut-être pas encore une urgence visible pour la population. Mais, précisément parce que la transition prendra du temps, il est nécessaire d'agir aujourd'hui avant que cela ne devienne une urgence.
+Je vous invite donc à soutenir ma motion sans la lettre i, comme le demande le Conseil fédéral, et je vous en remercie.
 </t>
   </si>
   <si>
@@ -455,6 +455,41 @@
 Der Bundesrat verweist darauf, dass das rechtlich grundsätzlich möglich wäre. Der Anteil der Kantone liegt derzeit bei 21,2 Prozent. Der Bund hat ausgerechnet, dass sich diese Mehreinnahmen für das Jahr 2026, in dem ja die 13. AHV-Rente im Dezember erstmals ausbezahlt wird, auf 650 Millionen Franken belaufen würden. Diese 650 Millionen würden rechnerisch eine Reduktion von 2 Prozentpunkten ausmachen, sprich der Anteil der Kantone und Gemeinden an der direkten Bundessteuer würde von 21,2 Prozent auf 19,2 Prozent reduziert. Nun verweisen der Bundesrat und die Kommission darauf, dass Gesetzesänderungen auf Bundesstufe bei den Kantonen ohnehin regelmässig positiv oder negativ zu Buche schlagen. Es geht dabei nicht nur um Einnahmen; oft beschliessen wir ja auch Gesetze, die bei Kantonen und Gemeinden direkt Ausgaben auslösen. Der Bundesrat will auf eine Feinsteuerung durch die Rechtsetzung in diesem Bereich verzichten und dies nur bei gross angelegten Reformen tun, wie wir das eigentlich immer gemacht haben. Hierbei ist namentlich auf die Neugestaltung des Finanzausgleichs und der Aufgabenteilung (NFA) von 2008 zu verweisen sowie - mit Blick auf die jüngere Vergangenheit - auf die Steuerreform und die AHV-Finanzierung (STAF) von 2020.
 Die Kommission hat sich am 1. September mit dem Geschäft befasst. Wir haben Kenntnis davon genommen, dass der Nationalrat mit 96 zu 90 Stimmen bei 5 Enthaltungen einen relativ knappen Entscheid gefällt hat. Wir haben uns in der Kommission den Ausführungen des Bundesrates angeschlossen. Es spricht nämlich einiges gegen eine Abschöpfung dieser zusätzlichen Steuereinnahmen, die den Kantonen und Gemeinden zugutekommen. Unter anderem finden wir, dass der administrative Aufwand zu hoch wäre. Zudem würde eine solche Anpassung zu ständigen Veränderungen bei der Verteilung führen - einmal nach oben, dann wieder nach unten. Das ist nicht zielgerichtet, es wäre dann auch keine Rechtssicherheit vorhanden. Wenn schon, müsste man eine solche Änderung im Zusammenhang mit der NFA vornehmen. Das, finden wir, sind eigentlich die guten Gründe, die für eine Ablehnung sprechen. Eine fixe und einmalige Reduktion des Kantonsanteils an der Bundessteuer würde der bestehenden Einnahmen- und Ausgaben-Dynamik - mit mal mehr, mal weniger Einnahmen bzw. Ausgaben - nicht gerecht werden. 
 Darum beantragt Ihnen Ihre vorberatende Kommission, die SGK-S, mit 6 zu 0 Stimmen bei immerhin 5 Enthaltungen, dem Bundesrat zu folgen und diese Motion abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'intention du Conseil fédéral, dès le départ, on peut le lire dans son message sur la loi sur l'égalité, était d'inclure tous les types de discrimination, y compris celle liée à l'orientation sexuelle. C'était l'intention dès le départ de la loi sur l'égalité. Or, l'arrêt du Tribunal fédéral de 2019 - ATF 145 II 153 - a explicitement exclu l'orientation sexuelle des motifs de discrimination dans la loi sur l'égalité. C'est donc pour cela qu'il existe aujourd'hui cette lacune juridique.
+Vous m'e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'intention du Conseil fédéral, dès le départ, on peut le lire dans son message sur la loi sur l'égalité, était d'inclure tous les types de discrimination, y compris celle liée à l'orientation sexuelle. C'était l'intention dès le départ de la loi sur l'égalité. Or, l'arrêt du Tribunal fédéral de 2019 - ATF 145 II 153 - a explicitement exclu l'orientation sexuelle des motifs de discrimination dans la loi sur l'égalité. C'est donc pour cela qu'il existe aujourd'hui cette lacune juridique.
+Vous m'excuserez de faire une entorse au fait de ne pas répéter, au nom du plurilinguisme.
+Nel suo rapporto in adempimento del postulato 23.3501, il Consiglio federale ha mostrato disponibilità riguardo all'esplicita inclusione dell'orientamento sessuale tra i motivi di discriminazione. Secondo il rapporto, è possibile, senza mettere in discussione il carattere binario della legge sull'uguaglianza, estendere alcune delle sue disposizioni anche alle discriminazioni fondate sull'orientamento sessuale.
+C'est donc sur cette base que nous devons nous reposer. On se réjouit également du message que nous livrera le Conseil fédéral par rapport à cet élément.
+Les discriminations pour les personnes LGBTIQ sont réelles. J'aimerais rappeler à ce sujet deux rapports, de l'administration et du Conseil fédéral. Il s'agit d'une part du plan d'action national contre les crimes de haine envers les personnes LGBTIQ. Dans ce plan d'action, il est remarqué que malgré des progrès légaux, l'égalité de fait des personnes dans notre pays n'est pas encore atteinte.
+Im Alltag sind LGBTIQ-Personen nach wie vor mit tiefgreifenden Ungleichbehandlungen sowie mit Diskriminierungserfahrungen und verbaler, physischer, sexueller oder psychologischer Gewalt konfrontiert, was die Gesundheit der Betroffenen beeinträchtigt. Gleichzeitig besteht eine erhöhte Gefahr der Verharmlosung von Hassreden. Der Arbeitsbereich ist einer der betroffenen Bereiche, wenn es um Diskriminierung von LGBTIQ-Personen geht, in diesem Sinn ist das Gleichstellungsgesetz das richtige Gefäss, um die Situation in diesem Bereich zu verbessern. 
+Ich möchte mich gegen die Ausführungen meines Vorredners wehren. Es geht nicht um eine materielle Erweiterung des Gesetzes, sondern um eine Präzisierung, wen es betrifft. Das Gleichstellungsgesetz betrifft zwar die Gleichstellung von Frau und Mann. Aber wenn keine Gleichstellung von Frauen und Männern untereinander besteht, also von heterosexuellen Männern oder Frauen und homosexuellen Männern oder Frauen, dann kann sich auch keine Gleichstellung von Frauen und Männern ergeben. In diesem Sinn ist es richtig, eine solche Präzisierung vorzunehmen.
+Die Beweislasterleichterung ist ein klarer Teil des Diskriminierungsverbots, und es geht eben auch um die Beweislasterleichterung bei Diskriminierung oder Benachteiligung einer Frau am Arbeitsplatz - ich hoffe, wir sind uns alle einig, dass das einfach nicht geht. Es kann zwar ein bisschen kompliziert sein, die Tatsachen zu beweisen, aber es ist so: Diskriminierung und Belästigung haben am Arbeitsplatz keinen Platz.
+J'ajoute un mot sur la santé des personnes LGBTIQ. Le Conseil fédéral a publié en 2022 un rapport de postulat qui concernait la santé des personnes homosexuelles et bisexuelles qui a été établi sur la base d'une étude de la Haute école de Lucerne. Ce rapport montre que la santé psychique en Suisse - mais ceci fait écho à la situation internationale - des personnes concernées est considérablement pire que celle du reste de la population.
+J'aimerais ajouter encore un mot sur la version modifiée. Comme le rapporteur l'a dit, la commission a adopté une version modifiée. Elle était unanime sur le fait qu'il était pertinent de maintenir l'orientation sexuelle, mais d'enlever l'identité de genre. Il s'agit, d'une part, d'une considération pragmatique sur le fait que les travaux sur l'identité de genre sont encore relativement débutants en ce qui concerne la précision de cette identité dans les textes légaux. D'autre part, l'article 8 alinéa 2 de la Constitution précise que nul ne peut être discriminé du fait de son sexe et la doctrine a admis que l'identité de genre était comprise dans cet article 8 alinéa 2 qui interdit la discrimination en raison du sexe.
+Dès lors, je vous demande de suivre la commission et d'adopter la motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nous avons effectivement déjà eu ce débat il n'y a pas si longtemps sur une motion dont le texte était identique, que notre conseil avait adoptée avec raison. Permettez-moi de ramener quelques éléments du débat que nous avons eu à l'époque, puisque j'étais l'auteur de cette motion.
+Il s'agit de créer une base légale fédérale qui permette de déroger à un principe important de notre Constitution : le droit de manifester et le droit de se réunir. Or, pour tout droit fondamental, si l'on veut que so</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nous avons effectivement déjà eu ce débat il n'y a pas si longtemps sur une motion dont le texte était identique, que notre conseil avait adoptée avec raison. Permettez-moi de ramener quelques éléments du débat que nous avons eu à l'époque, puisque j'étais l'auteur de cette motion.
+Il s'agit de créer une base légale fédérale qui permette de déroger à un principe important de notre Constitution : le droit de manifester et le droit de se réunir. Or, pour tout droit fondamental, si l'on veut que son exercice soit parfois limité, ce que vise la motion, il faut une base légale explicite. Cette motion vise la création d'une base légale explicite qui permette de limiter un tout petit peu l'exercice d'un droit fondamental, qui est celui de la liberté de se réunir et de la liberté de manifester.
+Il ne s'agit donc pas de restreindre, mais, au contraire, de donner la possibilité aux collectivités publiques - vous avez rappelé précédemment, cher collègue Zopfi, que vous étiez le président de l'Association des communes suisses ; moi j'ai de nombreux représentants de communes qui sont venus vers moi en me félicitant d'avoir réussi à faire passer cette motion devant le Conseil des États, parce que cela leur donne une base légale - de pouvoir justement justifier une facturation par rapport aux dégâts provoqués lors de ces manifestations. Il s'agirait donc simplement de créer une base légale - comme je l'ai dit - qui permette la facturation, mais qui fixe également un cadre dans lequel la facturation est possible ou n'est pas possible.
+Je crois que cette base légale est indispensable et je vous invite vraiment à soutenir la proposition de la majorité de la commission et d'accepter cette motion.
 </t>
   </si>
 </sst>
@@ -509,8 +544,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I24" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I26" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I26"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1504,6 +1539,64 @@
         <v>101</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" t="s">
+        <v>103</v>
+      </c>
+      <c r="I25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" t="s">
+        <v>106</v>
+      </c>
+      <c r="I26" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -130,17 +130,17 @@
     <t xml:space="preserve">Dobler Loïc</t>
   </si>
   <si>
-    <t xml:space="preserve">Imaginez : vous voudriez vivre dans votre propre appartement avec le soutien dont vous avez besoin au quotidien, mais ce soutien n'existe pas, ou pas assez. Alors, c'est dans un foyer ou une institution que vous devez vivre, pas parce que vous l'avez choisi, mais parce que personne ne vous a donné le choix. Ce ne sont pas des cas isolés ; c'est le quotidien de milliers de personnes en Suisse aujourd'hui. Douze ans après avoir ratifié la Convention de l'ONU relative aux droits des personnes handi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imaginez : vous voudriez vivre dans votre propre appartement avec le soutien dont vous avez besoin au quotidien, mais ce soutien n'existe pas, ou pas assez. Alors, c'est dans un foyer ou une institution que vous devez vivre, pas parce que vous l'avez choisi, mais parce que personne ne vous a donné le choix. Ce ne sont pas des cas isolés ; c'est le quotidien de milliers de personnes en Suisse aujourd'hui. Douze ans après avoir ratifié la Convention de l'ONU relative aux droits des personnes handicapées, nous en sommes encore là.
-Alors, la question qui nous est posée aujourd'hui tient en un mot : l'autodétermination. Décider soi-même où l'on vit. Décider soi-même comment on vit. Décider soi-même où l'on travaille, où l'on se cultive, où l'on se divertit. Ce n'est pas un supplément d'âme qu'on accorde quand le budget le permet. C'est un droit fondamental. Or, un droit fondamental, cela ne se négocie pas.
-C'est pourquoi nous soutenons l'initiative pour l'inclusion. Parce qu'elle inscrit dans notre Constitution ce que la loi seule ne garantit pas : une égalité effective, un droit au soutien nécessaire, et la liberté de choisir sa vie. Une loi, une majorité peut la défaire ; un droit constitutionnel, on le protège. Nous soutenons tout autant le contre-projet indirect du Conseil fédéral. La commission a choisi de le renforcer encore sur plusieurs points essentiels. C'est ce travail qu'il faut défendre aujourd'hui devant notre conseil.
-Regardons ce qui est sur la table, dans les domaines du travail et de la formation d'abord. Aujourd'hui encore, trop de personnes en situation de handicap n'accèdent pas à un emploi qui correspond à leurs compétences, parce que la transition depuis une institution se heurte à des obstacles administratifs, à un manque d'accompagnement, à des mesures de soutien insuffisantes. Le texte propose des structures plus souples, moins de bureaucratie, des conditions-cadres plus fiables autant pour les salariés que pour les employeurs, jusqu'à 90 heures d'assistance par mois pour garder un emploi, et une protection contre la discrimination qui couvre enfin tous les aspects des rapports de travail, de l'embauche au salaire en passant par la formation continue. Pour que le parcours ne s'arrête plus faute de possibilités adaptées, le texte encourage aussi des formations ciblées et une meilleure représentation des personnes concernées au sein des commissions qui préparent nos décisions.
+    <t xml:space="preserve">Imaginez[NB]: vous voudriez vivre dans votre propre appartement avec le soutien dont vous avez besoin au quotidien, mais ce soutien n'existe pas, ou pas assez. Alors, c'est dans un foyer ou une institution que vous devez vivre, pas parce que vous l'avez choisi, mais parce que personne ne vous a donné le choix. Ce ne sont pas des cas isolés[NB]; c'est le quotidien de milliers de personnes en Suisse aujourd'hui. Douze ans après avoir ratifié la Convention de l'ONU relative aux droits des personnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imaginez[NB]: vous voudriez vivre dans votre propre appartement avec le soutien dont vous avez besoin au quotidien, mais ce soutien n'existe pas, ou pas assez. Alors, c'est dans un foyer ou une institution que vous devez vivre, pas parce que vous l'avez choisi, mais parce que personne ne vous a donné le choix. Ce ne sont pas des cas isolés[NB]; c'est le quotidien de milliers de personnes en Suisse aujourd'hui. Douze ans après avoir ratifié la Convention de l'ONU relative aux droits des personnes handicapées, nous en sommes encore là.
+Alors, la question qui nous est posée aujourd'hui tient en un mot[NB]: l'autodétermination. Décider soi-même où l'on vit. Décider soi-même comment on vit. Décider soi-même où l'on travaille, où l'on se cultive, où l'on se divertit. Ce n'est pas un supplément d'âme qu'on accorde quand le budget le permet. C'est un droit fondamental. Or, un droit fondamental, cela ne se négocie pas.
+C'est pourquoi nous soutenons l'initiative pour l'inclusion. Parce qu'elle inscrit dans notre Constitution ce que la loi seule ne garantit pas[NB]: une égalité effective, un droit au soutien nécessaire, et la liberté de choisir sa vie. Une loi, une majorité peut la défaire[NB]; un droit constitutionnel, on le protège. Nous soutenons tout autant le contre-projet indirect du Conseil fédéral. La commission a choisi de le renforcer encore sur plusieurs points essentiels. C'est ce travail qu'il faut défendre aujourd'hui devant notre conseil.
+Regardons ce qui est sur la table, dans les domaines du travail et de la formation d'abord. Aujourd'hui encore, trop de personnes en situation de handicap n'accèdent pas à un emploi qui correspond à leurs compétences, parce que la transition depuis une institution se heurte à des obstacles administratifs, à un manque d'accompagnement, à des mesures de soutien insuffisantes. Le texte propose des structures plus souples, moins de bureaucratie, des conditions-cadres plus fiables, autant pour les salariés que pour les employeurs, jusqu'à 90 heures d'assistance par mois pour garder un emploi, et une protection contre la discrimination qui couvre enfin tous les aspects des rapports de travail, de l'embauche au salaire en passant par la formation continue. Pour que le parcours ne s'arrête plus faute de possibilités adaptées, le texte encourage aussi des formations ciblées et une meilleure représentation des personnes concernées au sein des commissions qui préparent nos décisions.
 Dans le domaine du logement, ensuite, les personnes en situation de handicap doivent pouvoir décider elles-mêmes où, comment et avec qui elles vivent. Le texte encourage le logement autonome et revalorise l'assistance qui rend cette vie autonome possible au quotidien.
 Dans le domaine de l'accès aux services et à la vie sociale, enfin, les entreprises privées et les services numériques devront être conçus pour être accessibles à toutes et tous. Le sport, la culture, les loisirs ne doivent plus rester des privilèges réservés à celles et ceux qui n'ont pas de handicap. Pour que personne ne renonce à un appareillage faute de moyens, l'assurance-invalidité obtient enfin les leviers pour peser sur les prix des moyens auxiliaires techniques.
-Ce ne sont pas des lignes budgétaires ; ce sont des vies qui changent. On ne devrait jamais avoir à demander la permission de vivre sa propre vie. Décider où l'on habite, avec qui, comment on travaille : ce n'est pas un privilège qu'on accorde, c'est un droit que l'on doit garantir. Tant qu'il ne l'est pas pour tout le monde, il ne l'est vraiment pour personne.
-Oui, des minorités voudront renier ces avancées, une par une, sous prétexte de coûts ou de complexité. À chacune de ces minorités, notre réponse sera la même : non à l'affaiblissement de la protection contre la discrimination, non à la réduction des prestations d'assistance, non aux restrictions sur le libre choix du logement. Il y a un principe que nous ne devons jamais perdre de vue dans ce débat : ce ne sont pas les autorités ni les institutions qui doivent décider à la place des personnes en situation de handicap. C'est à elles de décider pour elles-mêmes. Défendons le travail accompli par la commission, et votons en fin de course en faveur de l'initiative comme de ce contre-projet renforcé. Il est temps que l'autodétermination que l'on promet depuis douze ans devienne une réalité.
+Ce ne sont pas des lignes budgétaires[NB]; ce sont des vies qui changent. On ne devrait jamais avoir à demander la permission de vivre sa propre vie. Décider où l'on habite, avec qui, comment on travaille[NB]: ce n'est pas un privilège qu'on accorde, c'est un droit que l'on doit garantir. Tant qu'il ne l'est pas pour tout le monde, il ne l'est vraiment pour personne.
+Oui, des minorités voudront renier ces avancées, une par une, sous prétexte de coûts ou de complexité. À chacune de ces minorités, notre réponse sera la même[NB]: non à l'affaiblissement de la protection contre la discrimination, non à la réduction des prestations d'assistance, non aux restrictions sur le libre choix du logement. Il y a un principe que nous ne devons jamais perdre de vue dans ce débat[NB]: ce ne sont pas les autorités ni les institutions qui doivent décider à la place des personnes en situation de handicap. C'est à elles de décider pour elles-mêmes. Défendons le travail accompli par la commission, et votons en fin de course en faveur de l'initiative comme de ce contre-projet renforcé. Il est temps que l'autodétermination que l'on promet depuis douze ans devienne une réalité.
 </t>
   </si>
   <si>
@@ -227,33 +227,33 @@
     <t xml:space="preserve">419433</t>
   </si>
   <si>
-    <t xml:space="preserve">Sans trop rallonger, je voudrais vous dire que si vous soutenez la minorité Hurni, vous aurez une première solution qui pourra être débattue soit par la commission du Conseil national soit par notre Commission des affaires juridiques, qui pourrait entretemps y réfléchir. Si nous refusons cette proposition de minorité, nous n'aurons rien pour régler ce problème qui est pourtant clair, évident, qui a été soulevé ici et où il y a vraiment une nécessité d'agir. La résolution du problème sera donc re</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sans trop rallonger, je voudrais vous dire que si vous soutenez la minorité Hurni, vous aurez une première solution qui pourra être débattue soit par la commission du Conseil national soit par notre Commission des affaires juridiques, qui pourrait entretemps y réfléchir. Si nous refusons cette proposition de minorité, nous n'aurons rien pour régler ce problème qui est pourtant clair, évident, qui a été soulevé ici et où il y a vraiment une nécessité d'agir. La résolution du problème sera donc reportée aux calendes grecques. Excusez l'expression !
-Donc, je crois qu'il faut prendre ce que l'on a. Comme un bon tiens vaut mieux que deux tu l'auras, je vous invite aujourd'hui, parce qu'il y a un vrai problème, à soutenir ce que vous propose la minorité de la commission, quitte à peut-être améliorer cette solution à un autre moment. Mais au moins, on aura déjà fait un pas dans la bonne direction.
-Il s'agit d'une situation qui est quand même particulière. Comme on l'a dit, c'est dans un avion et pas dans un restaurant, ou sur la route où l'on peut s'arrêter pour faire venir les agents de la force publique. Il y a une question de protection des passagers mais, plus globalement, de sécurité dans l'avion, qu'il faut pouvoir régler. C'est pour cela que, à mon avis, il faut offrir cette protection au personnel qui travaille dans les avions et soutenir la minorité Hurni.
+    <t xml:space="preserve">Sans trop rallonger, je voudrais vous dire que si vous soutenez la minorité Hurni, vous aurez une première solution qui pourra être débattue soit par la commission du Conseil national, soit par notre Commission des affaires juridiques, qui pourrait entretemps y réfléchir. Si nous refusons cette proposition de minorité, nous n'aurons rien pour régler ce problème qui est pourtant clair, évident, qui a été soulevé ici et où il y a vraiment une nécessité d'agir. La résolution du problème sera donc r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sans trop rallonger, je voudrais vous dire que si vous soutenez la minorité Hurni, vous aurez une première solution qui pourra être débattue soit par la commission du Conseil national, soit par notre Commission des affaires juridiques, qui pourrait entretemps y réfléchir. Si nous refusons cette proposition de minorité, nous n'aurons rien pour régler ce problème qui est pourtant clair, évident, qui a été soulevé ici et où il y a vraiment une nécessité d'agir. La résolution du problème sera donc reportée aux calendes grecques. Excusez l'expression[NB]!
+Donc, je crois qu'il faut prendre ce que l'on a. Comme un bon tiens vaut mieux que deux tu l'auras, je vous invite aujourd'hui, parce qu'il y a un vrai problème, à soutenir ce que vous propose la minorité de la commission, quitte à peut-être améliorer cette solution à un autre moment. Mais, au moins, on aura déjà fait un pas dans la bonne direction.
+Il s'agit d'une situation qui est quand même particulière. Comme on l'a dit, c'est dans un avion et pas dans un restaurant ou sur la route, où l'on peut s'arrêter pour faire venir les agents de la force publique. Il y a une question de protection des passagers, mais, plus globalement, de sécurité dans l'avion, qu'il faut pouvoir régler. C'est pour cela que, à mon avis, il faut offrir cette protection au personnel qui travaille dans les avions et soutenir la minorité Hurni.
 </t>
   </si>
   <si>
     <t xml:space="preserve">419593</t>
   </si>
   <si>
-    <t xml:space="preserve">Madame Amaudruz, vous évoquez à juste titre l'aspect de cette réforme relatif à l'indemnisation de l'assurance-chômage. Je ne vous ai pas entendu par exemple vous insurger du fait que, pour l'AVS également, les frontaliers sont indemnisés de la même manière que les résidents suisses puisqu'ils ont cotisé en Suisse. Ce combat semble un peu perdu d'avance, parce qu'il n'est pas lié à l'Union européenne, mais à l'OCDE, qui a des principes par rapport à cela. (Remarque intermédiaire du président : A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madame Amaudruz, vous évoquez à juste titre l'aspect de cette réforme relatif à l'indemnisation de l'assurance-chômage. Je ne vous ai pas entendu par exemple vous insurger du fait que, pour l'AVS également, les frontaliers sont indemnisés de la même manière que les résidents suisses puisqu'ils ont cotisé en Suisse. Ce combat semble un peu perdu d'avance, parce qu'il n'est pas lié à l'Union européenne, mais à l'OCDE, qui a des principes par rapport à cela. (Remarque intermédiaire du président : Avez-vous une question, Monsieur Dobler ?) Ma question est donc : l'enjeu qui se pose n'est-il pas plutôt l'imposition des frontaliers aussi en Suisse, plutôt que l'indemnisation par le biais du chômage en France ? Ne vous trompez-vous pas de combat avec cette motion ?
+    <t xml:space="preserve">Madame Amaudruz, vous évoquez à juste titre l'aspect de cette réforme relatif à l'indemnisation de l'assurance-chômage. Je ne vous ai pas entendue par exemple vous insurger contre le fait que, pour l'AVS également, les frontaliers sont indemnisés de la même manière que les résidents suisses puisqu'ils ont cotisé en Suisse. Ce combat semble un peu perdu d'avance, parce qu'il n'est pas lié à l'Union européenne, mais à l'OCDE, qui a des principes par rapport à cela. (Remarque intermédiaire du prési</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madame Amaudruz, vous évoquez à juste titre l'aspect de cette réforme relatif à l'indemnisation de l'assurance-chômage. Je ne vous ai pas entendue par exemple vous insurger contre le fait que, pour l'AVS également, les frontaliers sont indemnisés de la même manière que les résidents suisses puisqu'ils ont cotisé en Suisse. Ce combat semble un peu perdu d'avance, parce qu'il n'est pas lié à l'Union européenne, mais à l'OCDE, qui a des principes par rapport à cela. (Remarque intermédiaire du président[NB]: Avez-vous une question, Monsieur Dobler[NB]?) Ma question est donc[NB]: l'enjeu qui se pose n'est-il pas plutôt l'imposition des frontaliers aussi en Suisse, plutôt que l'indemnisation par le biais du chômage en France[NB]? Ne vous trompez-vous pas de combat avec cette motion[NB]?
 </t>
   </si>
   <si>
     <t xml:space="preserve">419672</t>
   </si>
   <si>
-    <t xml:space="preserve">Nous avons aujourd'hui le plaisir d'accueillir une délégation du canton du Jura et je remercie le président de m'avoir fait l'amitié de la saluer officiellement à la tribune de notre conseil. La délégation est conduite par M. Fabrice Macquat, président du Parlement jurassien, et c'est pour moi, évidemment, une joie et un honneur de pouvoir vous souhaiter la bienvenue dans la salle du Conseil des États. Pour y accéder, vous êtes passés sous la magnifique verrière de la coupole et avez pu admirer </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nous avons aujourd'hui le plaisir d'accueillir une délégation du canton du Jura et je remercie le président de m'avoir fait l'amitié de la saluer officiellement à la tribune de notre conseil. La délégation est conduite par M. Fabrice Macquat, président du Parlement jurassien, et c'est pour moi, évidemment, une joie et un honneur de pouvoir vous souhaiter la bienvenue dans la salle du Conseil des États. Pour y accéder, vous êtes passés sous la magnifique verrière de la coupole et avez pu admirer les armoiries des cantons disposées autour de la croix suisse.
-Les guides s'amusent souvent à demander aux visiteuses et visiteurs où se trouvent les armoiries du Jura, car ces dernières ne trônent pas sous la coupole, puisqu'elles ont été ajoutées bien après la construction du Palais du Parlement. Pour cause, son inauguration en 1902 est intervenue 77 ans avant l'entrée en souveraineté du canton. Ainsi, absente de la coupole en 1902, la région jurassienne a néanmoins posé, cette année-là, un jalon important pour rallier un jour la Berne fédérale. Elle a en effet largement approuvé en votation populaire un projet de construction de nouvelle ligne de chemin de fer qui allait préfigurer le percement de la ligne ferroviaire Moutier-Bienne. Lorsqu'en 1979, le canton du Jura est entré en souveraineté au terme d'une histoire que l'on sait mouvementée, ces armoiries ont trouvé une place de choix au-dessus des trois Confédérés.
+    <t xml:space="preserve">Nous avons aujourd'hui le plaisir d'accueillir une délégation du canton du Jura et je remercie le président de m'avoir fait l'amitié de la saluer officiellement à la tribune de notre conseil. La délégation est conduite par M.[NB]Fabrice Macquat, président du Parlement jurassien, et c'est pour moi, évidemment, une joie et un honneur de pouvoir vous souhaiter la bienvenue dans la salle du Conseil des États. Pour y accéder, vous êtes passés sous la magnifique verrière de la coupole et avez pu admir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nous avons aujourd'hui le plaisir d'accueillir une délégation du canton du Jura et je remercie le président de m'avoir fait l'amitié de la saluer officiellement à la tribune de notre conseil. La délégation est conduite par M.[NB]Fabrice Macquat, président du Parlement jurassien, et c'est pour moi, évidemment, une joie et un honneur de pouvoir vous souhaiter la bienvenue dans la salle du Conseil des États. Pour y accéder, vous êtes passés sous la magnifique verrière de la coupole et avez pu admirer les armoiries des cantons disposées autour de la croix suisse.
+Les guides s'amusent souvent à demander aux visiteuses et visiteurs où se trouvent les armoiries du Jura, car ces dernières ne trônent pas sous la coupole, puisqu'elles ont été ajoutées bien après la construction du Palais du Parlement. Pour cause, son inauguration en 1902 est intervenue 77 ans avant l'entrée en souveraineté du canton. Ainsi, absente de la coupole en 1902, la région jurassienne a néanmoins posé, cette année-là, un jalon important pour rallier un jour la Berne fédérale. Elle a en effet largement approuvé en votation populaire un projet de construction de nouvelle ligne de chemin de fer qui allait préfigurer le percement de la ligne ferroviaire Moutier-Bienne. Lorsqu'en 1979 le canton du Jura est entré en souveraineté, au terme d'une histoire que l'on sait mouvementée, ces armoiries ont trouvé une place de choix au-dessus des trois Confédérés.
 La Confédération que nous représentons aujourd'hui n'est pas celle qui s'est unie sous cette coupole en 1902. Elle a changé, elle s'est agrandie, elle a évolué avec les générations et les territoires qui la composent. Unies sous un même toit, les armoiries sous la coupole sont le témoin de cette histoire. Elles nous rappellent, à l'instar du canton du Jura, que le fédéralisme sur lequel la Suisse s'est construite depuis ses origines porte les graines des changements dont la population se fait le moteur. Je vous souhaite une très cordiale bienvenue au Palais fédéral ainsi qu'une excellente visite. (Applaudissements)
 </t>
   </si>
@@ -490,6 +490,157 @@
 Il s'agit de créer une base légale fédérale qui permette de déroger à un principe important de notre Constitution : le droit de manifester et le droit de se réunir. Or, pour tout droit fondamental, si l'on veut que son exercice soit parfois limité, ce que vise la motion, il faut une base légale explicite. Cette motion vise la création d'une base légale explicite qui permette de limiter un tout petit peu l'exercice d'un droit fondamental, qui est celui de la liberté de se réunir et de la liberté de manifester.
 Il ne s'agit donc pas de restreindre, mais, au contraire, de donner la possibilité aux collectivités publiques - vous avez rappelé précédemment, cher collègue Zopfi, que vous étiez le président de l'Association des communes suisses ; moi j'ai de nombreux représentants de communes qui sont venus vers moi en me félicitant d'avoir réussi à faire passer cette motion devant le Conseil des États, parce que cela leur donne une base légale - de pouvoir justement justifier une facturation par rapport aux dégâts provoqués lors de ces manifestations. Il s'agirait donc simplement de créer une base légale - comme je l'ai dit - qui permette la facturation, mais qui fixe également un cadre dans lequel la facturation est possible ou n'est pas possible.
 Je crois que cette base légale est indispensable et je vous invite vraiment à soutenir la proposition de la majorité de la commission et d'accepter cette motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuosto Brenda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce postulat s'inscrit pleinement dans notre politique des agglomérations transfrontalières, dont l'importance est aujourd'hui d'autant plus soulignée par la votation du canton de Genève sur le financement des P+R de l'autre côté de la frontière. Nos agglomérations transfrontalières, qu'il s'agisse de Genève, Bâle, Lugano ou du Chablais, sont les moteurs de notre économie. Mais aujourd'hui, le coût de cette activité est un engorgement quotidien de nos réseaux routiers. Chaque matin, ce sont des c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce postulat s'inscrit pleinement dans notre politique des agglomérations transfrontalières, dont l'importance est aujourd'hui d'autant plus soulignée par la votation du canton de Genève sur le financement des P+R de l'autre côté de la frontière. Nos agglomérations transfrontalières, qu'il s'agisse de Genève, Bâle, Lugano ou du Chablais, sont les moteurs de notre économie. Mais aujourd'hui, le coût de cette activité est un engorgement quotidien de nos réseaux routiers. Chaque matin, ce sont des colonnes ininterrompues de véhicules individuels qui traversent nos communes.
+Selon l'Office fédéral de la statistique (OFS), plus de 80 pour cent de la totalité des frontaliers actifs en Suisse travaillent dans des cantons limitrophes de la France comme Genève, Vaud, Neuchâtel et le Jura, et au Tessin. En 2021, la grande majorité d'entre eux utilisaient la voiture individuelle pour leurs déplacements quotidiens, représentant le coeur du trafic aux frontières. L'Office fédéral des routes (OFROU) recense plus de 68 000 heures d'embouteillage sur nos autoroutes, ce qui provoque un report massif du trafic sur nos routes secondaires. L'Office fédéral du développement territorial (ARE) évalue les coûts externes totaux de la mobilité individuelle en Suisse à près de 10 milliards de francs par an. Les habitantes et habitants de nos communes frontalières, de nos agglomérations, en payent directement le prix : bruit permanent, dégradation de l'air, risque pour la sécurité routière, usure permanente des routes locales - à la charge des communes - et péjoration de la qualité de vie.
+Dans son avis, le Conseil fédéral nous dit que tout va bien, que les instruments actuels comme l'OPTA ou la loi sur les chemins de fer suffisent et que le principe de territorialité doit prévaloir. Il nous rappelle les 850 millions de francs investis par le passé dans des projets emblématiques comme le CEVA ou Mendrisio-Varese.
+Mais cela n'est pas suffisant pour garantir un développement territorial harmonieux et cohérent. Face à cela, les solutions concrètes existent pourtant et passent par un report modal efficace : créer et renforcer des lignes de transports publics transfrontalières - bus à haute fréquence, trams, liaisons ferroviaires ou lignes express. Lorsque nous offrons une alternative rapide et directe de l'autre côté de la frontière, nous stoppons les voitures avant qu'elles ne viennent s'engorger dans nos villages. Regardez l'exemple du Léman Express et ses plus de 80 000 voyageurs par jour. La preuve est faite : dès qu'une alternative crédible existe, le report modal fonctionne.
+Avec ce postulat, je demande d'adapter nos outils financiers pour accélérer ces mesures de transports publics ciblées et rendre aux usagères et usagers de la route la fluidité dont ils ont besoin. Pour le bien-être, le bien-vivre ensemble dans nos communes et le dynamisme de nos régions frontalières, je vous invite donc à soutenir ce postulat.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burkart Thierry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir befinden uns in der Differenzbereinigung zur Weiterentwicklung der LSVA. Offen ist noch eine einzige Differenz: die Frage, ob die bewährte Praxis, Abklassierungen in eine neue LSVA-Kategorie frühzeitig bekannt zu geben, auf Gesetzesstufe verankert wird. 
+Bei unserer letzten Beratung am 21. September haben wir von den drei verbleibenden Differenzen zwei im Sinne des Nationalrates ausgeräumt und sind ihm damit deutlich entgegengekommen. Einzig bei der Planungssicherheit haben wir an unserem Be</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir befinden uns in der Differenzbereinigung zur Weiterentwicklung der LSVA. Offen ist noch eine einzige Differenz: die Frage, ob die bewährte Praxis, Abklassierungen in eine neue LSVA-Kategorie frühzeitig bekannt zu geben, auf Gesetzesstufe verankert wird. 
+Bei unserer letzten Beratung am 21. September haben wir von den drei verbleibenden Differenzen zwei im Sinne des Nationalrates ausgeräumt und sind ihm damit deutlich entgegengekommen. Einzig bei der Planungssicherheit haben wir an unserem Beschluss festgehalten. Der Nationalrat hat diese letzte Differenz am 23. September beraten und mit 101 zu 95 Stimmen bei 1 Enthaltung an seiner Fassung festgehalten. Das Resultat war allerdings noch deutlich knapper als in der ersten Runde der Differenzbereinigung. Die Minderheit, die dem Ständerat folgen wollte, ist nur um 6 Stimmen unterlegen. 
+Ich habe mich in der letzten Runde der Differenzbereinigung, wie es sich normalerweise gehört, sehr kurz gehalten. Ich muss aber hier etwas ausholen. Bitte verzeihen Sie mir das angesichts der knappen Ergebnisse und der politischen Bedeutung des Themas. 
+Ihre Kommission hat das Geschäft am vergangenen Donnerstag erneut beraten. Das Resultat hätte knapper nicht sein können: Mit 6 zu 6 Stimmen und Stichentscheid der Präsidentin beantragt sie Ihnen, an der Verankerung der Planungssicherheit festzuhalten, aber in einer präzisierten Fassung. Neu soll Artikel 8 Absatz 2 SVAG wie folgt ergänzt werden: Der Bundesrat berücksichtigt die völkerrechtlichen Verträge und das Erfordernis der Planungssicherheit der Unternehmen. Er teilt jede Änderung an der Einstufung der Fahrzeugkategorien mit einer Vorlaufzeit von mindestens sieben Jahren mit.
+Weshalb erfolgt diese Präzisierung? Die Beratungen in beiden Räten haben gezeigt, dass die Vorlaufzeit von sieben Jahren grundsätzlich auf Zustimmung stösst. Geäussert wurde aber die Sorge, die bisherige Formulierung des Ständerates sei zu starr, und es müsse jede Änderung an der LSVA, auch eine Teuerungsanpassung, sieben Jahre im Voraus angekündigt werden.
+Diesem Einwand trägt der neue Antrag Rechnung. Die Vorlaufzeit gilt ausschliesslich für Änderungen an der Einstufung der Fahrzeugkategorien, also für Abklassierungen. Die Teuerungsanpassung und die übrige Tarifgestaltung bleiben in der Kompetenz des Bundesrates, so wie heute. Damit schaffen wir dort Planungssicherheit, wo sie für die Investitionsentscheide der Betriebe entscheidend ist, ohne den Bundesrat übermässig einzuschränken. Wir halten zudem an unserem Beschluss zu Ziffer II fest, den unser Rat am 21. September gefällt hat.
+Worum geht es in der Sache? Für ein kleineres oder mittleres Transportunternehmen, etwa einen Betrieb mit 5 bis 10 Lastwagen im Entlebuch, im Wallis, im Glarnerland oder sonst wo in der Schweiz, ist ein LKW keine Routineanschaffung. Ein Fahrzeug kostet schnell 200 000 bis 300 000 Franken. Ich habe darauf hingewiesen, dass sich die Kosten bei Spezialaufbauten oder Kranfahrzeugen auf deutlich über eine halbe Million belaufen. Ich gehe hier nicht noch einmal auf die Argumente ein, die bereits in der vormaligen Beratung aufgeführt worden sind. Nichtsdestotrotz weise ich darauf hin, dass eine Abklassierung die LSVA für ein Fahrzeug von einem Tag auf den anderen um rund 15 Prozent verteuern kann. Ein Grossbetrieb kann das über seine Flotte abfedern, ein Betrieb mit 5 oder 10 Lastwagen nicht. Die Planbarkeit ist für die Investition und die Investitionssicherheit von grosser Bedeutung.
+Die Minderheit wird ihre Position im Anschluss selbst vertreten.
+Erlauben Sie mir vorab, zwei Aussagen zu korrigieren, die in der Kommission von der jetzigen Minderheit gemacht worden sind. Erstens ist argumentiert worden, dass die vorgeschlagene Regelung das Verlagerungsziel gefährde. Das trifft nicht zu. Artikel 84 Absatz 2 BV beschlägt den alpenquerenden Gütertransitverkehr von Grenze zu Grenze. Das Verlagerungsziel betrifft also den alpenquerenden Transitverkehr und nicht den Binnenverkehr. Der Baustellenverkehr im Kanton Aargau, das Kehrichtfahrzeug im Emmental oder der Holztransporter im Jura haben mit dem Verfassungsauftrag der Verlagerung nichts zu tun. Diese Fahrzeuge lassen sich auch nicht auf die Schiene verlagern. Genau sie sind aber von Abklassierungen am stärksten betroffen.
+Zweitens wurde gesagt, der Gesetzgeber würde sich die Hände binden und könnte das Gesetz künftig nicht mehr anpassen. Auch das ist nicht der Fall. Mit der präzisierten Fassung ist nun auch ausdrücklich klargestellt, dass die Vorlaufzeit nur für Abklassierungen gilt und nicht für Teuerungsanpassungen. Das Parlament kann das Gesetz jederzeit ändern, und der Bundesrat kann unabhängig von einer Gesetzesänderung jederzeit Abklassierungen vornehmen. Es geht einzig darum, dass Abklassierungen frühzeitig bekannt gegeben werden, damit die Betriebe ihre Investitionen darauf ausrichten können. Das ist nichts Neues. Diese Praxis wurde unter Bundesrätin Leuthard eingeführt und seither angewendet. Sie war bisher von allen Seiten unbestritten. Wenn sie unbestritten ist, spricht nichts dagegen, sie im Gesetz festzuschreiben. 
+Im Namen der Kommissionsmehrheit beantrage ich Ihnen, der abgeänderten Fassung zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gmür-Schönenberger Andrea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich mache eine grundsätzliche Bemerkung zur LSVA-Revision: Es war und ist unser Anliegen, einen Ausgleich zu finden zwischen den Interessen der Branche im Entlebuch, im Wallis, im Jura und in der ganzen Schweiz - und den ökologischen Anliegen, die wir in diesem Land auch haben. Was wir bisher beraten respektive entschieden haben, ist ein Stück weit auch eine Schwächung des BIF. Das bedaure ich einerseits, andererseits habe ich die Änderungen aber auch klar mitgetragen.
+Die Planungssicherheit, di</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich mache eine grundsätzliche Bemerkung zur LSVA-Revision: Es war und ist unser Anliegen, einen Ausgleich zu finden zwischen den Interessen der Branche im Entlebuch, im Wallis, im Jura und in der ganzen Schweiz - und den ökologischen Anliegen, die wir in diesem Land auch haben. Was wir bisher beraten respektive entschieden haben, ist ein Stück weit auch eine Schwächung des BIF. Das bedaure ich einerseits, andererseits habe ich die Änderungen aber auch klar mitgetragen.
+Die Planungssicherheit, die der Mehrheitssprecher wiederholt angesprochen hat, ist bereits jetzt gegeben, weil der Bundesrat in der Verordnung die sieben Jahre Vorlaufzeit sowieso festhalten will. Die Fahrzeughalter erhalten damit ganz klar die gewünschte Planungssicherheit. Eine zusätzliche gesetzliche Regelung braucht es nicht. Die Regelung schwächt zudem die LSVA als Lenkungsinstrument. Das neue Schwerverkehrsabgabegesetz wurde bewusst so ausgestaltet, dass es eben an technische Entwicklungen angepasst werden kann. Eine gesetzliche, siebenjährige Sperrfrist würde künftige Weiterentwicklungen der LSVA erschweren oder gar blockieren. Gerade wegen der Elektrifizierung des Schwerverkehrs ist heute nicht absehbar, welche Kriterien in 10 oder 15 Jahren relevant sein werden. Eine derart starre Regelung macht aus einem anpassungsfähigen Lenkungsinstrument ein schwerfälliges System. Der wichtigste Punkt ist aber eigentlich der folgende: Kennen Sie ein einziges Gesetz, in dem festgehalten ist, dass dieses während 7 Jahren nicht geändert werden darf? Warum 7 Jahre, warum nicht 10 oder 15 Jahre? Wenn Sie dem Antrag der Mehrheit zustimmen, schaffen wir hier ein Präjudiz.
+Die Rechtsgleichheit wäre meines Erachtens auch nicht gewährleistet. Wir brauchen eine gesetzliche Regulierung, die Sinn macht. Wir wollen die Branche schützen. Es braucht diese Anpassung der Verordnung, aber eine gesetzliche Regelung, die eine ganz bestimmte Vorlaufzeit im Gesetz festhält, wäre schädlich.
+Ich bitte Sie, der Minderheit zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On a entendu parler de fierté. Alors oui, parce que je suis fier de notre liberté, de notre souveraineté, de notre prospérité, mais aussi soucieux d'un avenir serein pour notre pays, je vous invite à approuver sans ambiguïté l'entrée en matière sur le paquet "Stabilisation et développement des relations Suisses-UE (Bilatérales III)".
+Refuser le débat aujourd'hui serait irresponsable. Cela reviendrait à tourner le dos à la voie bilatérale, un modèle pragmatique qui garantit notre stabilité économ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On a entendu parler de fierté. Alors oui, parce que je suis fier de notre liberté, de notre souveraineté, de notre prospérité, mais aussi soucieux d'un avenir serein pour notre pays, je vous invite à approuver sans ambiguïté l'entrée en matière sur le paquet "Stabilisation et développement des relations Suisses-UE (Bilatérales III)".
+Refuser le débat aujourd'hui serait irresponsable. Cela reviendrait à tourner le dos à la voie bilatérale, un modèle pragmatique qui garantit notre stabilité économique depuis plus de 25 ans. L'accès réglementé et sans heurts au marché intérieur européen n'est pas un luxe ; c'est une nécessité vitale pour l'emploi, l'innovation et la force industrielle de notre pays. C'est une question stratégique pour l'avenir de notre pays.
+Nous ne sommes pas une île au milieu de nulle part, et nos voisins restent à n'en pas douter des acteurs fondamentaux de notre prospérité. Ils sont aussi globalement nos principaux alliés, même si nous rencontrons parfois des divergences avec eux. Vu la situation géopolitique actuelle, il serait dommageable de leur tourner le dos.
+Il y a lieu de relever ici la qualité du résultat des négociations menées par nos négociateurs et par les diplomates suisses. En effet, bon nombre d'États membres de l'UE ne cachent pas qu'ils seraient heureux de bénéficier des avantages accordés à la Suisse. Parce que c'est bel et bien ici qu'il y a du bilatéralisme, comme on a cru entendre que ce n'était pas le cas. C'est bilatéral parce que sur les plus de 600 pages que contiennent ces accords, la plupart sont consacrées à des exceptions en faveur de notre pays.
+Les arguments politiques ne manquent pas et les arguments économiques en faveur de ces textes sont indiscutables.
+Tout d'abord, le poids massif de l'UE dans notre commerce. L'Union européenne reste de très loin notre principal partenaire commercial. Cela a été dit : plus de 50 pour cent des exportations de marchandises suisses, soit plus de 147 milliards de francs par an, sont destinés au marché européen. En sens inverse, environ 70 pour cent de nos importations en proviennent.
+Ensuite, il y a un impact direct sur l'emploi suisse. Notre économie dépend de conditions-cadres fiables. En moyenne, une entreprise suisse sur deux emploie de la main-d'oeuvre qualifiée issue de l'UE. Bloquer ce paquet, c'est mettre en péril la compétitivité de nos entreprises et la sécurité de milliers d'emplois helvétiques.
+Ces chiffres sont impressionnants à l'échelle nationale. Ils deviennent une question de survie économique pour les cantons de l'Arc jurassien. Je veux parler des cantons de Neuchâtel, du Jura, de la région du Jura bernois et du Nord vaudois, qui sont des régions frontalières. Une économie ultra exportatrice, l'Arc jurassien, abrite les fleurons de l'horlogerie, des microtechniques, des machines et des technologies médicales. C'est une région dont la richesse repose presque exclusivement sur sa capacité à exporter. Deux francs sur trois sont gagnés à l'étranger. 
+Sans la mise à jour des accords, notamment sur la suppression des obstacles techniques au commerce, l'industrie de l'Arc jurassien fera face à des barrières administratives majeures qui détruiront sa compétitivité face à la concurrence mondiale. Voilà un exemple qui était souhaité par notre collègue Salzmann. Ce n'est pas une projection, mais nous l'avons vécu récemment. 
+La réalité transfrontalière : l'Arc jurassien vit et respire au rythme de la coopération transfrontalière. Près de 72 000 frontaliers - 12 000 pour le seul canton du Jura - viennent chaque jour y apporter leurs compétences essentielles. Stabiliser la libre circulation des personnes et sécuriser l'accès au marché du travail est une condition sine qua non pour que le tissu industriel de l'Arc jurassien puisse continuer à produire et à innover. 
+Étant donné qu'on a parlé des effets du Brexit - on a parlé de l'évolution de son PIB -, j'ai profité de ce long débat pour vérifier sur les réseaux, respectivement au travers de l'intelligence artificielle, quelle était la situation. Les chiffres sont clairs. Le PIB du Royaume-Uni a progressé moins vite que celui de l'Union européenne, entre 6 et 8 pour cent. Quant à la productivité de ce pays, il a baissé de 3 pour cent et l'emploi a baissé de 4 pour cent à cause des frictions administratives et des coûts des échanges depuis le Brexit. 
+Quant à l'aspect institutionnel, qui a souvent monopolisé le débat au détriment du contenu des accords, il serait regrettable, comme l'a dit notre collègue Chassot, que ce soit l'arbre qui cache la forêt. Nous y reviendrons, mais je vous invite déjà à appliquer la Constitution que nous avons promis de respecter au début de notre mandat. Elle règle complètement la question des compétences et notamment de l'application du référendum facultatif. Pourquoi faudrait-il la triturer et la torturer pour lui faire dire autre chose que ce qu'elle contient ? 
+Vous l'aurez compris : à l'instar des cantons romands, je soutiens le référendum facultatif. Ces cantons estiment en effet avoir été suffisamment associés aux préparations des actes législatifs dont nous allons parler et que leurs remarques et demandes ont été suffisamment prises en compte par le Conseil fédéral.
+Il est d'ailleurs curieux d'entendre les tenants de la souveraineté de notre pays citer à l'envi des professeurs étrangers et ignorer les avis de la quasi-totalité des professeurs de droit constitutionnel de notre pays.
+En conclusion, les cantons de Suisse occidentale, les entreprises et les associations professionnelles sont unis pour réclamer cette sécurité juridique indispensable à la bonne marge de leurs affaires. L'isolement n'est pas une option viable, il en va de la prospérité de notre pays et, par voie de conséquence, du pouvoir d'achat et du bien-être de nos concitoyennes et concitoyens. Nous avons besoin de coconstruire ensemble la voie bilatérale qui a largement contribué à la prospérité et la souveraineté de notre pays.
+Je vous invite à entrer en matière sur ce projet, à mener un débat constructif tourné vers l'avenir et finalement à accepter les projets qui nous sont soumis.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans la mode, on classifie les habits entre S et XL. Aujourd'hui, on a aussi inventé le XXL. Le débat d'aujourd'hui, c'est un débat XXL. Je ne vais pas répéter ce qui a été dit, mais je vais quand même apporter quelques arguments qui concernent mon canton, puisque l'on a beaucoup entendu ce jour la voix des cantons.
+Tout d'abord, pourquoi un débat XXL ? Des auditions publiques - c'est quasiment une première -, 32 séances de commissions, des plénières importantes, des commissions avec chaque fois</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans la mode, on classifie les habits entre S et XL. Aujourd'hui, on a aussi inventé le XXL. Le débat d'aujourd'hui, c'est un débat XXL. Je ne vais pas répéter ce qui a été dit, mais je vais quand même apporter quelques arguments qui concernent mon canton, puisque l'on a beaucoup entendu ce jour la voix des cantons.
+Tout d'abord, pourquoi un débat XXL ? Des auditions publiques - c'est quasiment une première -, 32 séances de commissions, des plénières importantes, des commissions avec chaque fois des leaders, trois conseillers fédéraux présents - c'est très rare de voir une délégation aussi importante devant notre chambre -, la présence de la presse - c'est rare aussi de voir les tribunes de la presse si fournies. Cela veut dire que c'est un débat qui est important. Certains ont qualifié le débat comme "la mère de toutes les batailles". À titre personnel, ce n'est pas la mère de toutes les batailles. C'est un dossier parmi d'autres. Mais c'est un dossier qui est important.
+Nous sommes responsables de notre vote. Nous sommes 46. Notre vote correspond également à notre diversité cantonale. À vous entendre, certains considèrent que l'Europe est un ennemi. Non, l'Europe, c'est un partenaire économique, de fait, les chiffres ont été rappelés. De temps en temps, nous sommes en concurrence avec l'Europe. Nos industries, de temps en temps, sont en concurrence avec l'Europe. Et notre devoir, c'est de trouver un chemin pour que notre économie puisse prospérer, se développer et créer de la richesse qui est utile à la cohésion sociale.
+J'ai entendu ce mot qui devient de plus en plus magique : la souveraineté. La souveraineté peut être unique quand vous êtes sur une île, mais quand vous êtes au milieu de l'Europe, la souveraineté, c'est aussi trouver des partenariats qui consolident le pays. Certes, c'est un mot magique pour nous, les Suisses, mais en même temps, la souveraineté se partage, que ce soit dans le domaine militaire, de la sécurité ou de l'approvisionnement. D'ailleurs, on vient d'avoir une votation le week-end dernier sur la souveraineté alimentaire. Et on constate que, dans tous les cas de figure, il n'y aura pas de souveraineté alimentaire au niveau suisse. Même durant le plan Wahlen, il n'y a pas eu de souveraineté alimentaire au niveau suisse. Nous devons compter également avec d'autres pays. Nous devons construire des stratégies avec d'autres pays.
+Ensuite, j'en suis très heureux, quand on donne la parole au peuple, le peuple s'exprime. Notre chambre a longuement débattu de l'initiative populaire "Pas de Suisse à 10 millions ! (initiative pour la durabilité)". Pour certains, il fallait faire un contre-projet ; pour d'autres, et j'étais de ceux-là, un contre-projet, non, mais par contre, affronter le peuple, expliquer que quand nous avons une pyramide des âges avec un vieillissement majeur, nous avons intérêt à trouver des solutions pour garantir un équilibre de la pyramide des âges, garantir les emplois. Je rappelle que dans le cadre du débat que nous avons eu concernant l'initiative "Pas de Suisse à 10 millions ! (initiative pour la durabilité)", nous avons mis en place des garde-fous. La Suisse, en permanence, peut se fermer ou se réouvrir. Ce qui a été négocié par le Conseil fédéral permet d'avoir une clause de sauvegarde ; en tout temps, on peut la dénoncer. Non pas comme l'ont fait les Anglais avec le Brexit, mais dénoncer une clause. 
+Ensuite, la neutralité. Là aussi, nous avons eu un débat très large, intense. 75 pour cent du peuple suisse a dit non à l'initiative populaire "Sauvegarder la neutralité suisse (initiative sur la neutralité)", et j'en suis très heureux. 
+Flexibilité, stabilité, prévisibilité, sécurité juridique : c'est cela que nous amène ce dossier qui a été négocié par le Conseil fédéral. Stabilité, pour continuer à travailler par la voie bilatérale. Prévisibilité, pour nos entreprises : un entrepreneur a besoin de savoir, en lien avec son cahier de commandes, ce qu'il va se passer ces prochaines années. Et sécurité juridique : quand il y a un accord, il y a deux parties. Il y a des arbitres qui traiteront de l'accord. Cela permet d'avoir une sécurité juridique dans un monde en pleine évolution. 
+Cela me fait beaucoup sourire : il y a quelques mois - et là je remercie le président de la Confédération, M. Parmelin, qui essaie de travailler sur les taxes américaines -, on pensait que l'Europe, c'était l'ennemi, et qu'on avait trouvé des marchés assez simples. Les États-Unis sont devenus un marché, mais les règles ont beaucoup changé avec nos amis américains. Nous aurons à débattre, et suivant le chemin que nous choisirons dans le domaine des accords internationaux, avec le Mercosur, je me réjouis déjà qu'il faille avoir une double majorité concernant l'accord avec le Mercosur. Je me réjouis déjà. 
+Un autre dossier qui va venir prochainement, c'est celui de la Chine. Il n'y a pas un jour où l'on ne lit pas que, demain, la Chine sera la plus grande puissance économique mondiale. Je me réjouis d'avoir un débat, et si une nouvelle fois, nous devons soumettre ce texte à une double majorité, cela sera compliqué, parce que la Chine est loin, elle n'est pas si proche de notre marché. Notre marché, c'est l'Europe, l'Europe des 27.
+Ce que je n'ai pas beaucoup entendu dans le débat d'aujourd'hui c'est des remerciements. Je pense que c'est important de savoir remercier les gens qui ont fait un travail très important. J'ai présidé à la destinée des 26 cantons avec mon collègue Würth, au sein de cette chambre. On a commencé le débat sur les Bilatérales `III il y a à peu près 15 ans. Le conseiller fédéral Burkhalter a travaillé sur ce dossier, a mis en place le dialogue Europe. Il a quitté le Conseil fédéral, et le conseiller fédéral Cassis, vice-président du Conseil fédéral, a repris le flambeau. Il y a bientôt dix ans qu'il travaille sur ce dossier, et ce n'est pas simple. Personnellement, je souhaitais vous remercier, Messieurs, pour l'engagement que vous avez manifesté pour la Suisse. Tous les jours, c'était un dossier sensible, complexe, avec votre administration et les ambassadeurs, vous avez trouvé un chemin qui est utile à la cohésion de ce pays.
+J'aimerais également remercier les cantons. J'ai entendu aujourd'hui la voix des cantons. Chaque canton, c'est la force de notre pays, qui est plurielle. Quand on est à Schwytz, on n'est pas à Lausanne, c'est clair. Et quand on est à Lausanne, on n'est pas dans le Jura ni en Valais ou dans le canton d'Uri. Chaque canton a ses spécificités. En vous écoutant, j'ai entendu que vous avez amené aujourd'hui, dans le cadre de ce débat, ces spécificités régionales. Ce que je sais, c'est que quand nous sommes unis, nous créons la Suisse. Et la Suisse crée de la richesse, de la cohésion, de l'ouverture et de l'intelligence.
+Le débat que nous avons aujourd'hui - et c'est pour cela que je vous encourage à entrer en matière -, c'est un débat important, qui permettra d'avoir de la prospective, et créer justement cette Suisse qu'on aime.
+J'aimerais remercier également les partenaires sociaux. Parce que pour moi, l'Europe, c'est avant tout économique, puisqu'on contrôle notre marché du travail. Les partenaires sociaux dans ce dossier ont travaillé - c'était difficile, je le sais : notre collègue Maillard a travaillé, au nom de l'USS, avec d'autres partenaires. La partie adverse, l'économie, a trouvé un chemin : 14 mesures, que je soutiendrai, car je pense qu'elles s'inscrivent dans une logique très claire. Il s'agit de garantir le pouvoir d'achat, les salaires, la cohésion et de nouveau, la stabilité et les équilibres, la prévisibilité. C'est dans cet esprit que j'ai compris ce dossier.
+Je ne souhaitais pas intervenir, mais comme chaque canton s'est exprimé en apportant son éclairage, je vais parler encore quelques minutes de mon canton de Vaud. C'est le troisième canton suisse, bientôt à un million d'habitants, et j'en suis très fier. Cela ne me pose aucun problème que nous ayons un million d'habitants, parce que nous avons une pyramide des âges équilibrée, entre les personnes qui vieillissent, les jeunes qui doivent trouver une destinée et ceux qui sont dans le monde du travail.
+ Ensuite, nous avons les hautes écoles. Nous traiterons tout à l'heure ou demain d'Erasmus plus. Là aussi il faut de la prévisibilité. Quand nous n'avons pas signé les accords avec le milieu académique et autres, on a pleuré et il a fallu trouver des solutions. On doit stabiliser ce dossier pour le bien de nos enfants. On n'a pas de pétrole, mais par contre on a des hautes écoles et nos hautes écoles doivent avoir des partenariats équilibrés avec l'étranger. Là aussi il en va de la sécurité.
+Dernier point concernant mon canton, c'est un canton ouvert qui, lors des votations, a des positions parmi les plus ouvertes au niveau suisse. L'ouverture, c'est tout le contraire de la fermeture. Quand un canton se ferme, quand un pays se ferme, pendant quelques années, il peut peut-être vivre sur cette notion de souveraineté, quoique aujourd'hui on est dépendant des uns des autres, on le voit avec les taxes américaines. C'est pour ça que le canton de Vaud a dit à la députation vaudoise dans cette chambre de soutenir le travail du Conseil fédéral que nous remercions sincèrement pour avoir atteint les objectifs et pour le projet qui est sur la table. Je vous encourage à en faire de même, à entrer en matière, à améliorer si on peut le faire deux ou trois points de l'accord général puis à l'envoyer au Conseil national pour qu'il puisse l'examiner et ainsi trouver une destinée pour notre pays, de la stabilité, de la prévisibilité et de la sécurité juridique dans un monde en pleine évolution et insécuritaire.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graf Maya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich möchte gerne etwas Persönliches voranstellen, das mich in unserer heutigen Debatte aber sehr wichtig dünkt.
+Heute Morgen sprach mich beim Einkaufen eine ältere Bekannte auf unsere Debatte an - heute schauen uns ja hoffentlich sehr viele Leute zu -: Sie selbst könne sich nicht mit diesem grossen Paket, mit diesem Dokument mit so vielen Seiten auseinandersetzen, sagte sie mir. Sie müsse darauf vertrauen, dass wir das für die Bevölkerung sorgfältig tun, und zwar in Bezug auf die Zukunft ihrer G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich möchte gerne etwas Persönliches voranstellen, das mich in unserer heutigen Debatte aber sehr wichtig dünkt.
+Heute Morgen sprach mich beim Einkaufen eine ältere Bekannte auf unsere Debatte an - heute schauen uns ja hoffentlich sehr viele Leute zu -: Sie selbst könne sich nicht mit diesem grossen Paket, mit diesem Dokument mit so vielen Seiten auseinandersetzen, sagte sie mir. Sie müsse darauf vertrauen, dass wir das für die Bevölkerung sorgfältig tun, und zwar in Bezug auf die Zukunft ihrer Grosskinder. Sie selbst habe nämlich in goldenen Zeiten gelebt.
+Zu Hause erhielt ich die Mailnachricht eines jungen Mannes, der mich bat, heute "für eine nächste Generation zu entscheiden, die versteht, dass wir solidarisch und über nationale Grenzen hinaus handeln müssen, um eine bessere Welt zu schaffen".
+Wir kennen die Umfragen und wissen, dass sich breite Bevölkerungskreise der Tatsache bewusst sind, dass wir eine Weiterentwicklung unserer erfolgreichen Bilateralen brauchen. Ja, es ist eine grosse Verantwortung, welche wir heute mit der Beratung dieses umfassenden EU-Pakets für die nächsten Generationen, für unsere Kinder und Grosskinder tragen.
+Geschätzte Kollegin Z'graggen, 15 Jahre lang wurde an diesem Vertragspaket mit der EU gewerkelt - sehr umsichtig, sehr lange, sehr sorgfältig. Es wurde vom Bundesrat unter Mitwirkung der Kantone, der Sozialpartner und aller Betroffenen erarbeitet. Was wir in diesen Tagen, Wochen und Monaten hier im Parlament beraten und dann der Bevölkerung zur Entscheidung vorlegen, wird massgeblich unsere Nachkommen beschäftigen - sie werden damit leben müssen.
+Das bringt mich zum Gedanken, den ich mit Ihnen teilen will und den zu beachten ich Sie bitte. Denn die meisten von uns werden von den Folgen dieses wichtigen Vertragswerks mit unseren europäischen Verbündeten nicht mehr selbst betroffen sein, und wir werden auch nicht von den Folgen betroffen sein, wenn wir das Vertragspaket nicht verabschieden. Die meisten von uns - nicht alle - gehören zu den glücklichen Boomern, zur goldenen Generation des dauernden Wohlstandswachstums und des Friedens in Europa. Daher tragen wir eine ganz besondere Verantwortung für das Wohlergehen der zukünftigen Generationen.
+Wir müssen sorgfältig abwägen, was wir heute tun. Es ist der wichtigste strategische Entscheid unseres Landes für die nächsten Jahrzehnte, ja, für die nächsten Generationen. Wir sollten nicht zaudern. Die Verträge geben uns das Instrumentarium für eine selbstbewusste Umsetzung, die unseren Interessen Rechnung trägt. Diesen Spielraum müssen wir selbstbewusst nutzen. Ich bin davon überzeugt, dass wir das tun und mit unseren Beratungen auch zeigen werden.
+Die Antwort - Sie merken es - ist daher für mich klar: Eintreten auf das Stabilisierungspaket mit der EU und Ja zur Weiterentwicklung unserer heute schon erfolgreichen Beziehungen, statt noch mehr zu verzögern. Und Ja zum fakultativen Staatsvertragsreferendum, damit die betroffenen Stimmbürgerinnen und Stimmbürger allein entscheiden können, denn sie sind direkt betroffen - sie und ihre Nachkommen.
+Die Schweiz ist nicht trotz ihrer Verflechtung mit Europa erfolgreich. Sie ist vor allem aufgrund ihrer Verbundenheit mit Europa erfolgreich. Die Schweiz ist Europa - eigentlich komisch, dass man das immer wiederholen muss. Jetzt geht es darum, diese Verbindungen für die Zukunft zu sichern. Die Welt um uns herum ist nämlich unsicherer geworden. Gerade in solchen Zeiten wäre es töricht, die Beziehungen zu unseren wichtigsten und verlässlichsten Partnern unnötig zu schwächen.
+Der internationale Handel wird härter. Macht gilt vor Recht. Wollen Sie mit solchen Staaten weitere Verträge abschliessen, Freihandelsabkommen, und Staatsverträge aushandeln, und übermorgen ist wieder alles anders? Wir haben Herausforderungen mit der zukünftigen Energieversorgung. Fragen der Forschung, Gesundheit und Sicherheit müssen wir bewältigen, und nicht nur die Schweiz steht vor diesen Herausforderungen. Wir haben mit diesem Extremsommer einen Fingerzeig der Klimakrise erlebt. Das können wir als Schweiz nicht alleine lösen, mitten in Europa. Wir sollten das gemeinsam tun. Deshalb ist es wichtig, dass wir diese Weiterentwicklung unserer Beziehungen zur EU als unserem stabilsten Partner weiterverfolgen.
+Die Herren Schmid und Stark sagten vorhin, es könnten ja einfach die Bilateralen I und II weitergeführt werden. Das ist Selbstbetrug, geschätzte Kollegen, es tut mir leid. Denn wir wissen heute, und das können Ihnen alle bestätigen, und die Wirtschaft spürt bereits, dass das nicht stimmt. Unsere heutigen Abkommen erodieren, weil es in den 25 Jahren in der EU, in der Welt und auch in der Schweiz so viele Veränderungen gegeben hat. Stellen Sie sich vor, wie schnell sich alles verändert! Wir sind weder im Jahr 1291, die geschätzte Kollegin Z'graggen ist noch nicht da, und wir sind auch nicht im Jahre 2000, geschätzter Kollege Schmid.
+Ich gebe ein Beispiel. Unsere Pharma- und Medtech-Firmen sowie die Maschinenindustrie sind ganz direkt und unmittelbar betroffen, wenn die gegenseitige Anerkennung der technischen Standards nicht mehr aktualisiert wird. Zahlreiche Konzerne und KMU mit Sitz in der Nordwestschweiz sind auf einen diskriminierungsfreien Zugang zum europäischen Markt angewiesen. Ohne die Bilateralen werden Firmen ihre Investitionen eher im Ausland tätigen. Soll ich Ihnen sagen, was das Ausland bedeutet? Es bedeutet einfach: fünf Kilometer verschieben, über die Landesgrenze ins Elsass oder nach Südbaden oder in andere Regionen. 15 Kantone in unserem Land sind Grenzregionen. Das heisst, es ist eigentlich einfach. Dies hat direkte Auswirkungen auf Arbeitsplätze und die Volkswirtschaft, und auf unser Wissen. Wissen ist nämlich die wichtigste Ressource der Schweiz, und es definiert unsere Zukunft, besonders für den Innovations- und Life-Science-Standort Nordwestschweiz. Wissen braucht Vernetzung, weswegen der Zugang zu den EU-Programmen Horizon Europe und Erasmus plus für den Forschungsplatz Schweiz unverzichtbar ist.
+Noch ein Wort als Vertreterin der Nordwestschweiz und des Kantons Basel-Landschaft: In der Nordwestschweizer Regierungskonferenz sind die Kantone Solothurn, Aargau, Basel-Stadt, Jura und Basel-Landschaft vertreten. Sie haben gemeinsam bekräftigt, dass geregelte Beziehungen zur Europäischen Union unverzichtbar sind. Sie sind überzeugt, dass das Verhandlungsergebnis geregelte Beziehungen mit der EU ermöglicht und den bilateralen Weg absichert und weiterentwickelt. Sie wissen als Grenzregionen, wie eng verflochten die Beziehungen zu den benachbarten EU-Staaten sind. Sie sind für die Nordwestschweizer Kantone existenziell. Ich möchte hier auch noch darauf hinweisen, dass es darum geht, dass daher auch offene Grenzen in Verbindung mit der Absicherung des Schweizer Lohnschutzniveaus elementar für einen funktionierenden Arbeitsmarkt, gute wirtschaftliche Zusammenarbeit und den gesellschaftlichen Zusammenhalt in einer Grenzregion sind.
+Diese klare Haltung kommt nicht von ungefähr. Die Nordwestschweiz ist die exportstärkste Region der Schweiz. Fast die Hälfte aller Schweizer Exporte kommen aus der Nordwestschweiz, wovon wiederum die Hälfte in die EU als wichtigsten Handelspartner der Schweiz geht. Das kann niemand von heute auf morgen einfach ersetzen. Es ist nicht ersetzbar. Das sind unsere Nachbarn, die wichtigsten Handelspartner.
+Ich bin überzeugt, dass wir eine Schweiz wollen, die ihre Zukunft selbstbewusst gestaltet, keine Schweiz, die aus Angst vor Veränderungen Schritt für Schritt sich selbst ins Abseits stellt und sich auch noch ideologisch verschanzt. Die Bilateralen III sind kein Abschied von unserer nationalen Entscheidungsfreiheit. Wir werden hier als Parlament immer entscheiden und immer auch das letzte Wort haben. Das ist wichtig und muss gewährleistet sein, und das ist es auch. Die Bilateralen III sind die Fortsetzung eines Weges, den die Schweiz vor 25 Jahren eingeschlagen hat: eigenständig bleiben und trotzdem eng mit unseren europäischen Nachbarn zusammenarbeiten. Genau das wird mit dem Paket bezweckt, das nun vorliegt. 
+Ich will diese souveräne Schweiz, eine Schweiz, die ihren Kindern nicht nur Wohlstand hinterlässt, sondern eben auch gesunde Lebensgrundlagen und eine vielfältige Gesellschaft sowie Freiheit, Demokratie und Rechtsstaatlichkeit. Das können wir gemeinsam erreichen. Daran müssen wir gemeinsam arbeiten. Ich will eine Schweiz, die weiterhin mitredet und mitbestimmt, und zwar dort, wo sie ihre Zukunft beeinflussen kann. Ich will keine Schweiz, die nur reagiert und immer hinterherspringt und sich dann beugen muss, wenn Macht vor Recht gilt. Daher ist für mich klar: Ich trete ein und werde auch mit Überzeugung diesem EU-Vertragspaket zustimmen.
 </t>
   </si>
 </sst>
@@ -544,8 +695,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I26" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I32" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I32"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1597,6 +1748,180 @@
         <v>107</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" t="s">
+        <v>110</v>
+      </c>
+      <c r="I27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" t="s">
+        <v>114</v>
+      </c>
+      <c r="G28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" t="s">
+        <v>115</v>
+      </c>
+      <c r="I28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" t="s">
+        <v>119</v>
+      </c>
+      <c r="G29" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" t="s">
+        <v>120</v>
+      </c>
+      <c r="I29" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" t="s">
+        <v>123</v>
+      </c>
+      <c r="I30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31" t="s">
+        <v>36</v>
+      </c>
+      <c r="G31" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I31" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="s">
+        <v>129</v>
+      </c>
+      <c r="E32" t="s">
+        <v>130</v>
+      </c>
+      <c r="F32" t="s">
+        <v>131</v>
+      </c>
+      <c r="G32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" t="s">
+        <v>132</v>
+      </c>
+      <c r="I32" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -504,7 +504,7 @@
   <si>
     <t xml:space="preserve">Ce postulat s'inscrit pleinement dans notre politique des agglomérations transfrontalières, dont l'importance est aujourd'hui d'autant plus soulignée par la votation du canton de Genève sur le financement des P+R de l'autre côté de la frontière. Nos agglomérations transfrontalières, qu'il s'agisse de Genève, Bâle, Lugano ou du Chablais, sont les moteurs de notre économie. Mais aujourd'hui, le coût de cette activité est un engorgement quotidien de nos réseaux routiers. Chaque matin, ce sont des colonnes ininterrompues de véhicules individuels qui traversent nos communes.
 Selon l'Office fédéral de la statistique (OFS), plus de 80 pour cent de la totalité des frontaliers actifs en Suisse travaillent dans des cantons limitrophes de la France comme Genève, Vaud, Neuchâtel et le Jura, et au Tessin. En 2021, la grande majorité d'entre eux utilisaient la voiture individuelle pour leurs déplacements quotidiens, représentant le coeur du trafic aux frontières. L'Office fédéral des routes (OFROU) recense plus de 68 000 heures d'embouteillage sur nos autoroutes, ce qui provoque un report massif du trafic sur nos routes secondaires. L'Office fédéral du développement territorial (ARE) évalue les coûts externes totaux de la mobilité individuelle en Suisse à près de 10 milliards de francs par an. Les habitantes et habitants de nos communes frontalières, de nos agglomérations, en payent directement le prix : bruit permanent, dégradation de l'air, risque pour la sécurité routière, usure permanente des routes locales - à la charge des communes - et péjoration de la qualité de vie.
-Dans son avis, le Conseil fédéral nous dit que tout va bien, que les instruments actuels comme l'OPTA ou la loi sur les chemins de fer suffisent et que le principe de territorialité doit prévaloir. Il nous rappelle les 850 millions de francs investis par le passé dans des projets emblématiques comme le CEVA ou Mendrisio-Varese.
+Dans son avis, le Conseil fédéral nous dit que tout va bien, que les instruments actuels comme l'Ordonnance du DETEC concernant le programme en faveur du trafic d'agglomération (OPTA) ou la loi sur les chemins de fer suffisent et que le principe de territorialité doit prévaloir. Il nous rappelle les 850 millions de francs investis par le passé dans des projets emblématiques comme le CEVA ou Mendrisio-Varese.
 Mais cela n'est pas suffisant pour garantir un développement territorial harmonieux et cohérent. Face à cela, les solutions concrètes existent pourtant et passent par un report modal efficace : créer et renforcer des lignes de transports publics transfrontalières - bus à haute fréquence, trams, liaisons ferroviaires ou lignes express. Lorsque nous offrons une alternative rapide et directe de l'autre côté de la frontière, nous stoppons les voitures avant qu'elles ne viennent s'engorger dans nos villages. Regardez l'exemple du Léman Express et ses plus de 80 000 voyageurs par jour. La preuve est faite : dès qu'une alternative crédible existe, le report modal fonctionne.
 Avec ce postulat, je demande d'adapter nos outils financiers pour accélérer ces mesures de transports publics ciblées et rendre aux usagères et usagers de la route la fluidité dont ils ont besoin. Pour le bien-être, le bien-vivre ensemble dans nos communes et le dynamisme de nos régions frontalières, je vous invite donc à soutenir ce postulat.
 </t>
@@ -571,15 +571,15 @@
 Les arguments politiques ne manquent pas et les arguments économiques en faveur de ces textes sont indiscutables.
 Tout d'abord, le poids massif de l'UE dans notre commerce. L'Union européenne reste de très loin notre principal partenaire commercial. Cela a été dit : plus de 50 pour cent des exportations de marchandises suisses, soit plus de 147 milliards de francs par an, sont destinés au marché européen. En sens inverse, environ 70 pour cent de nos importations en proviennent.
 Ensuite, il y a un impact direct sur l'emploi suisse. Notre économie dépend de conditions-cadres fiables. En moyenne, une entreprise suisse sur deux emploie de la main-d'oeuvre qualifiée issue de l'UE. Bloquer ce paquet, c'est mettre en péril la compétitivité de nos entreprises et la sécurité de milliers d'emplois helvétiques.
-Ces chiffres sont impressionnants à l'échelle nationale. Ils deviennent une question de survie économique pour les cantons de l'Arc jurassien. Je veux parler des cantons de Neuchâtel, du Jura, de la région du Jura bernois et du Nord vaudois, qui sont des régions frontalières. Une économie ultra exportatrice, l'Arc jurassien, abrite les fleurons de l'horlogerie, des microtechniques, des machines et des technologies médicales. C'est une région dont la richesse repose presque exclusivement sur sa capacité à exporter. Deux francs sur trois sont gagnés à l'étranger. 
-Sans la mise à jour des accords, notamment sur la suppression des obstacles techniques au commerce, l'industrie de l'Arc jurassien fera face à des barrières administratives majeures qui détruiront sa compétitivité face à la concurrence mondiale. Voilà un exemple qui était souhaité par notre collègue Salzmann. Ce n'est pas une projection, mais nous l'avons vécu récemment. 
-La réalité transfrontalière : l'Arc jurassien vit et respire au rythme de la coopération transfrontalière. Près de 72 000 frontaliers - 12 000 pour le seul canton du Jura - viennent chaque jour y apporter leurs compétences essentielles. Stabiliser la libre circulation des personnes et sécuriser l'accès au marché du travail est une condition sine qua non pour que le tissu industriel de l'Arc jurassien puisse continuer à produire et à innover. 
-Étant donné qu'on a parlé des effets du Brexit - on a parlé de l'évolution de son PIB -, j'ai profité de ce long débat pour vérifier sur les réseaux, respectivement au travers de l'intelligence artificielle, quelle était la situation. Les chiffres sont clairs. Le PIB du Royaume-Uni a progressé moins vite que celui de l'Union européenne, entre 6 et 8 pour cent. Quant à la productivité de ce pays, il a baissé de 3 pour cent et l'emploi a baissé de 4 pour cent à cause des frictions administratives et des coûts des échanges depuis le Brexit. 
-Quant à l'aspect institutionnel, qui a souvent monopolisé le débat au détriment du contenu des accords, il serait regrettable, comme l'a dit notre collègue Chassot, que ce soit l'arbre qui cache la forêt. Nous y reviendrons, mais je vous invite déjà à appliquer la Constitution que nous avons promis de respecter au début de notre mandat. Elle règle complètement la question des compétences et notamment de l'application du référendum facultatif. Pourquoi faudrait-il la triturer et la torturer pour lui faire dire autre chose que ce qu'elle contient ? 
+Ces chiffres sont impressionnants à l'échelle nationale. Ils deviennent une question de survie économique pour les cantons de l'Arc jurassien. Je veux parler des cantons de Neuchâtel, du Jura, de la région du Jura bernois et du Nord vaudois, qui sont des régions frontalières avec une économie ultra exportatrice. L'Arc jurassien abrite les fleurons de l'horlogerie, des microtechniques, des machines et des technologies médicales. C'est une région dont la richesse repose presque exclusivement sur sa capacité à exporter. Deux francs sur trois sont gagnés à l'étranger.
+Sans la mise à jour des accords, notamment sur la suppression des obstacles techniques au commerce, l'industrie de l'Arc jurassien fera face à des barrières administratives majeures qui détruiront sa compétitivité face à la concurrence mondiale. Voilà un exemple, comme l'avait souhaité notre collègue Salzmann. Ce n'est pas une projection ; nous l'avons vécu récemment.
+La réalité transfrontalière : l'Arc jurassien vit et respire au rythme de la coopération transfrontalière. Près de 72 000 frontaliers - 12 000 pour le seul canton du Jura - viennent chaque jour y apporter leurs compétences essentielles. Stabiliser la libre circulation des personnes et sécuriser l'accès au marché du travail est une condition sine qua non pour que le tissu industriel de l'Arc jurassien puisse continuer à produire et à innover.
+Étant donné qu'on a parlé des effets du Brexit - on a parlé de l'évolution du PIB -, j'ai profité de ce long débat pour vérifier sur les réseaux, respectivement au travers de l'intelligence artificielle, quelle était la situation. Les chiffres sont clairs. Le PIB du Royaume-Uni a progressé moins vite que celui de l'Union européenne, entre 6 et 8 pour cent. Quant à la productivité de ce pays, elle a diminué de 3 pour cent et l'emploi a baissé de 4 pour cent à cause des frictions administratives et des coûts des échanges depuis le Brexit.
+Quant à l'aspect institutionnel, qui a souvent monopolisé le débat au détriment du contenu des accords, il serait regrettable, comme l'a dit notre collègue Chassot, que ce soit l'arbre qui cache la forêt. Nous y reviendrons, mais je vous invite déjà à appliquer la Constitution que nous avons promis de respecter au début de notre mandat. Elle règle complètement la question des compétences et notamment de l'application du référendum facultatif. Pourquoi faudrait-il la triturer et la torturer pour lui faire dire autre chose que ce qu'elle contient ?
 Vous l'aurez compris : à l'instar des cantons romands, je soutiens le référendum facultatif. Ces cantons estiment en effet avoir été suffisamment associés aux préparations des actes législatifs dont nous allons parler et que leurs remarques et demandes ont été suffisamment prises en compte par le Conseil fédéral.
 Il est d'ailleurs curieux d'entendre les tenants de la souveraineté de notre pays citer à l'envi des professeurs étrangers et ignorer les avis de la quasi-totalité des professeurs de droit constitutionnel de notre pays.
-En conclusion, les cantons de Suisse occidentale, les entreprises et les associations professionnelles sont unis pour réclamer cette sécurité juridique indispensable à la bonne marge de leurs affaires. L'isolement n'est pas une option viable, il en va de la prospérité de notre pays et, par voie de conséquence, du pouvoir d'achat et du bien-être de nos concitoyennes et concitoyens. Nous avons besoin de coconstruire ensemble la voie bilatérale qui a largement contribué à la prospérité et la souveraineté de notre pays.
-Je vous invite à entrer en matière sur ce projet, à mener un débat constructif tourné vers l'avenir et finalement à accepter les projets qui nous sont soumis.
+En conclusion, les cantons de Suisse occidentale, les entreprises et les associations professionnelles sont unis pour réclamer cette sécurité juridique indispensable à la bonne marche de leurs affaires. L'isolement n'est pas une option viable. Il en va de la prospérité de notre pays et, par voie de conséquence, du pouvoir d'achat et du bien-être de nos concitoyennes et concitoyens. Nous avons besoin de coconstruire ensemble la voie bilatérale, qui a largement contribué à la prospérité et la souveraineté de notre pays.
+Je vous invite à entrer en matière sur ce projet, à mener un débat constructif tourné vers l'avenir et, finalement, à accepter les projets qui nous sont soumis.
 </t>
   </si>
   <si>
@@ -587,25 +587,25 @@
   </si>
   <si>
     <t xml:space="preserve">Dans la mode, on classifie les habits entre S et XL. Aujourd'hui, on a aussi inventé le XXL. Le débat d'aujourd'hui, c'est un débat XXL. Je ne vais pas répéter ce qui a été dit, mais je vais quand même apporter quelques arguments qui concernent mon canton, puisque l'on a beaucoup entendu ce jour la voix des cantons.
-Tout d'abord, pourquoi un débat XXL ? Des auditions publiques - c'est quasiment une première -, 32 séances de commissions, des plénières importantes, des commissions avec chaque fois</t>
+Tout d'abord, pourquoi un débat XXL ? Des auditions publiques - c'est quasiment une première -, 32 séances de commissions, des séances plénières importantes, des commissions avec cha</t>
   </si>
   <si>
     <t xml:space="preserve">Dans la mode, on classifie les habits entre S et XL. Aujourd'hui, on a aussi inventé le XXL. Le débat d'aujourd'hui, c'est un débat XXL. Je ne vais pas répéter ce qui a été dit, mais je vais quand même apporter quelques arguments qui concernent mon canton, puisque l'on a beaucoup entendu ce jour la voix des cantons.
-Tout d'abord, pourquoi un débat XXL ? Des auditions publiques - c'est quasiment une première -, 32 séances de commissions, des plénières importantes, des commissions avec chaque fois des leaders, trois conseillers fédéraux présents - c'est très rare de voir une délégation aussi importante devant notre chambre -, la présence de la presse - c'est rare aussi de voir les tribunes de la presse si fournies. Cela veut dire que c'est un débat qui est important. Certains ont qualifié le débat comme "la mère de toutes les batailles". À titre personnel, ce n'est pas la mère de toutes les batailles. C'est un dossier parmi d'autres. Mais c'est un dossier qui est important.
-Nous sommes responsables de notre vote. Nous sommes 46. Notre vote correspond également à notre diversité cantonale. À vous entendre, certains considèrent que l'Europe est un ennemi. Non, l'Europe, c'est un partenaire économique, de fait, les chiffres ont été rappelés. De temps en temps, nous sommes en concurrence avec l'Europe. Nos industries, de temps en temps, sont en concurrence avec l'Europe. Et notre devoir, c'est de trouver un chemin pour que notre économie puisse prospérer, se développer et créer de la richesse qui est utile à la cohésion sociale.
-J'ai entendu ce mot qui devient de plus en plus magique : la souveraineté. La souveraineté peut être unique quand vous êtes sur une île, mais quand vous êtes au milieu de l'Europe, la souveraineté, c'est aussi trouver des partenariats qui consolident le pays. Certes, c'est un mot magique pour nous, les Suisses, mais en même temps, la souveraineté se partage, que ce soit dans le domaine militaire, de la sécurité ou de l'approvisionnement. D'ailleurs, on vient d'avoir une votation le week-end dernier sur la souveraineté alimentaire. Et on constate que, dans tous les cas de figure, il n'y aura pas de souveraineté alimentaire au niveau suisse. Même durant le plan Wahlen, il n'y a pas eu de souveraineté alimentaire au niveau suisse. Nous devons compter également avec d'autres pays. Nous devons construire des stratégies avec d'autres pays.
-Ensuite, j'en suis très heureux, quand on donne la parole au peuple, le peuple s'exprime. Notre chambre a longuement débattu de l'initiative populaire "Pas de Suisse à 10 millions ! (initiative pour la durabilité)". Pour certains, il fallait faire un contre-projet ; pour d'autres, et j'étais de ceux-là, un contre-projet, non, mais par contre, affronter le peuple, expliquer que quand nous avons une pyramide des âges avec un vieillissement majeur, nous avons intérêt à trouver des solutions pour garantir un équilibre de la pyramide des âges, garantir les emplois. Je rappelle que dans le cadre du débat que nous avons eu concernant l'initiative "Pas de Suisse à 10 millions ! (initiative pour la durabilité)", nous avons mis en place des garde-fous. La Suisse, en permanence, peut se fermer ou se réouvrir. Ce qui a été négocié par le Conseil fédéral permet d'avoir une clause de sauvegarde ; en tout temps, on peut la dénoncer. Non pas comme l'ont fait les Anglais avec le Brexit, mais dénoncer une clause. 
-Ensuite, la neutralité. Là aussi, nous avons eu un débat très large, intense. 75 pour cent du peuple suisse a dit non à l'initiative populaire "Sauvegarder la neutralité suisse (initiative sur la neutralité)", et j'en suis très heureux. 
-Flexibilité, stabilité, prévisibilité, sécurité juridique : c'est cela que nous amène ce dossier qui a été négocié par le Conseil fédéral. Stabilité, pour continuer à travailler par la voie bilatérale. Prévisibilité, pour nos entreprises : un entrepreneur a besoin de savoir, en lien avec son cahier de commandes, ce qu'il va se passer ces prochaines années. Et sécurité juridique : quand il y a un accord, il y a deux parties. Il y a des arbitres qui traiteront de l'accord. Cela permet d'avoir une sécurité juridique dans un monde en pleine évolution. 
-Cela me fait beaucoup sourire : il y a quelques mois - et là je remercie le président de la Confédération, M. Parmelin, qui essaie de travailler sur les taxes américaines -, on pensait que l'Europe, c'était l'ennemi, et qu'on avait trouvé des marchés assez simples. Les États-Unis sont devenus un marché, mais les règles ont beaucoup changé avec nos amis américains. Nous aurons à débattre, et suivant le chemin que nous choisirons dans le domaine des accords internationaux, avec le Mercosur, je me réjouis déjà qu'il faille avoir une double majorité concernant l'accord avec le Mercosur. Je me réjouis déjà. 
-Un autre dossier qui va venir prochainement, c'est celui de la Chine. Il n'y a pas un jour où l'on ne lit pas que, demain, la Chine sera la plus grande puissance économique mondiale. Je me réjouis d'avoir un débat, et si une nouvelle fois, nous devons soumettre ce texte à une double majorité, cela sera compliqué, parce que la Chine est loin, elle n'est pas si proche de notre marché. Notre marché, c'est l'Europe, l'Europe des 27.
-Ce que je n'ai pas beaucoup entendu dans le débat d'aujourd'hui c'est des remerciements. Je pense que c'est important de savoir remercier les gens qui ont fait un travail très important. J'ai présidé à la destinée des 26 cantons avec mon collègue Würth, au sein de cette chambre. On a commencé le débat sur les Bilatérales `III il y a à peu près 15 ans. Le conseiller fédéral Burkhalter a travaillé sur ce dossier, a mis en place le dialogue Europe. Il a quitté le Conseil fédéral, et le conseiller fédéral Cassis, vice-président du Conseil fédéral, a repris le flambeau. Il y a bientôt dix ans qu'il travaille sur ce dossier, et ce n'est pas simple. Personnellement, je souhaitais vous remercier, Messieurs, pour l'engagement que vous avez manifesté pour la Suisse. Tous les jours, c'était un dossier sensible, complexe, avec votre administration et les ambassadeurs, vous avez trouvé un chemin qui est utile à la cohésion de ce pays.
+Tout d'abord, pourquoi un débat XXL ? Des auditions publiques - c'est quasiment une première -, 32 séances de commissions, des séances plénières importantes, des commissions avec chaque fois des leaders, trois conseillers fédéraux présents - c'est très rare de voir une délégation aussi importante devant notre chambre -, la présence de la presse - c'est rare aussi de voir les tribunes de la presse si fournies. Cela veut dire que c'est un débat qui est important. Certains ont qualifié le débat comme étant "la mère de toutes les batailles". À titre personnel, ce n'est pas la mère de toutes les batailles. C'est un dossier parmi d'autres, mais c'est un dossier qui est important.
+Nous sommes responsables de notre vote. Nous sommes 46. Notre vote correspond également à notre diversité cantonale. À vous entendre, certains considèrent que l'Europe est un ennemi. Non, l'Europe, c'est un partenaire économique, les chiffres ont été rappelés. De temps en temps, nous sommes en concurrence avec l'Europe. Nos industries, de temps en temps, sont en concurrence avec l'Europe. Notre devoir est de trouver un chemin pour que notre économie puisse prospérer, se développer et créer de la richesse qui est utile à la cohésion sociale.
+J'ai entendu ce mot qui devient de plus en plus magique : la souveraineté. La souveraineté peut être unique quand vous êtes sur une île, mais quand vous êtes au milieu de l'Europe, la souveraineté, c'est aussi trouver des partenariats qui consolident le pays. Certes, c'est un mot magique pour nous, les Suisses, mais en même temps, la souveraineté se partage, que ce soit dans le domaine militaire, de la sécurité ou de l'approvisionnement. D'ailleurs, on vient d'avoir une votation le week-end dernier sur la souveraineté alimentaire. On constate que, dans tous les cas de figure, il n'y aura pas de souveraineté alimentaire au niveau suisse. Même durant le plan Wahlen, il n'y a pas eu de souveraineté alimentaire au niveau suisse. Nous devons compter également avec d'autres pays. Nous devons construire des stratégies avec d'autres pays.
+Ensuite, j'en suis très heureux, quand on donne la parole au peuple, le peuple s'exprime. Notre chambre a longuement débattu de l'initiative populaire "Pas de Suisse à 10 millions ! (initiative pour la durabilité)". Pour certains, il fallait faire un contre-projet ; pour d'autres - et j'étais de ceux-là - pas de contre-projet, mais par contre, il fallait affronter le peuple et expliquer que quand nous avons une pyramide des âges avec un vieillissement majeur, nous avons intérêt à trouver des solutions pour garantir un équilibre de la pyramide des âges et garantir les emplois. Je rappelle que dans le cadre du débat que nous avons eu concernant l'initiative "Pas de Suisse à 10 millions ! (initiative pour la durabilité)", nous avons mis en place des garde-fous. La Suisse peut en permanence se fermer ou se réouvrir. Ce qui a été négocié par le Conseil fédéral permet d'avoir une clause de sauvegarde ; en tout temps, on peut la dénoncer - non pas comme l'ont fait les Anglais avec le Brexit, mais dénoncer une clause.
+Ensuite, la neutralité. Là aussi, nous avons eu un débat très large et intense. 75 pour cent du peuple suisse a dit non à l'initiative populaire "Sauvegarder la neutralité suisse (initiative sur la neutralité)", et j'en suis très heureux.
+Flexibilité, stabilité, prévisibilité, sécurité juridique : c'est cela que nous amène ce dossier qui a été négocié par le Conseil fédéral. Stabilité, pour continuer à travailler par la voie bilatérale. Prévisibilité, pour nos entreprises : un entrepreneur a besoin de savoir, en lien avec son cahier de commandes, ce qu'il va se passer ces prochaines années. Et sécurité juridique : quand il y a un accord, il y a deux parties, mais il y a aussi des arbitres qui traiteront de l'accord, et cela permet d'avoir une sécurité juridique dans un monde en pleine évolution.
+Cela me fait beaucoup sourire : il y a quelques mois - et là, je remercie le président de la Confédération, M. Parmelin, qui essaie de travailler sur les taxes américaines -, on pensait que l'Europe était l'ennemi, et qu'on allait trouver des marchés assez simplement. Les États-Unis sont devenus un marché, mais les règles ont beaucoup changé avec nos amis américains. Nous aurons à débattre, suivant le chemin que nous choisirons dans le domaine des accords internationaux, du Mercosur. Je me réjouis déjà qu'il faille avoir une double majorité concernant l'accord avec le Mercosur - je me réjouis déjà.
+Un autre dossier qui va venir prochainement, c'est celui de la Chine. Il n'y a pas un jour où l'on ne lit pas que, demain, la Chine sera la plus grande puissance économique mondiale. Je me réjouis d'avoir un débat. Si une nouvelle fois, nous devons soumettre ce texte à une double majorité, cela sera compliqué, parce que la Chine est loin, elle n'est pas si proche de notre marché. Notre marché, c'est l'Europe : l'Europe des 27.
+Ce que je n'ai pas beaucoup entendu dans le débat d'aujourd'hui,ce sont des remerciements. Je pense que c'est important de savoir remercier les gens qui ont fait un travail très important. J'ai présidé à la destinée des 26 cantons avec mon collègue Würth, au sein de cette chambre. On a commencé le débat sur les Bilatérales III il y a à peu près 15 ans. Le conseiller fédéral Burkhalter a travaillé sur ce dossier, a mis en place le dialogue Europe. Il a quitté le Conseil fédéral et le conseiller fédéral Cassis, vice-président du Conseil fédéral, a repris le flambeau. Il y a bientôt dix ans qu'il travaille sur ce dossier et ce n'est pas simple. Personnellement, je souhaitais vous remercier, Messieurs, pour l'engagement que vous avez manifesté pour la Suisse, tous les jours. C'était un dossier sensible, complexe. Avec votre administration et les ambassadeurs, vous avez trouvé un chemin qui est utile à la cohésion de ce pays.
 J'aimerais également remercier les cantons. J'ai entendu aujourd'hui la voix des cantons. Chaque canton, c'est la force de notre pays, qui est plurielle. Quand on est à Schwytz, on n'est pas à Lausanne, c'est clair. Et quand on est à Lausanne, on n'est pas dans le Jura ni en Valais ou dans le canton d'Uri. Chaque canton a ses spécificités. En vous écoutant, j'ai entendu que vous avez amené aujourd'hui, dans le cadre de ce débat, ces spécificités régionales. Ce que je sais, c'est que quand nous sommes unis, nous créons la Suisse. Et la Suisse crée de la richesse, de la cohésion, de l'ouverture et de l'intelligence.
-Le débat que nous avons aujourd'hui - et c'est pour cela que je vous encourage à entrer en matière -, c'est un débat important, qui permettra d'avoir de la prospective, et créer justement cette Suisse qu'on aime.
-J'aimerais remercier également les partenaires sociaux. Parce que pour moi, l'Europe, c'est avant tout économique, puisqu'on contrôle notre marché du travail. Les partenaires sociaux dans ce dossier ont travaillé - c'était difficile, je le sais : notre collègue Maillard a travaillé, au nom de l'USS, avec d'autres partenaires. La partie adverse, l'économie, a trouvé un chemin : 14 mesures, que je soutiendrai, car je pense qu'elles s'inscrivent dans une logique très claire. Il s'agit de garantir le pouvoir d'achat, les salaires, la cohésion et de nouveau, la stabilité et les équilibres, la prévisibilité. C'est dans cet esprit que j'ai compris ce dossier.
-Je ne souhaitais pas intervenir, mais comme chaque canton s'est exprimé en apportant son éclairage, je vais parler encore quelques minutes de mon canton de Vaud. C'est le troisième canton suisse, bientôt à un million d'habitants, et j'en suis très fier. Cela ne me pose aucun problème que nous ayons un million d'habitants, parce que nous avons une pyramide des âges équilibrée, entre les personnes qui vieillissent, les jeunes qui doivent trouver une destinée et ceux qui sont dans le monde du travail.
- Ensuite, nous avons les hautes écoles. Nous traiterons tout à l'heure ou demain d'Erasmus plus. Là aussi il faut de la prévisibilité. Quand nous n'avons pas signé les accords avec le milieu académique et autres, on a pleuré et il a fallu trouver des solutions. On doit stabiliser ce dossier pour le bien de nos enfants. On n'a pas de pétrole, mais par contre on a des hautes écoles et nos hautes écoles doivent avoir des partenariats équilibrés avec l'étranger. Là aussi il en va de la sécurité.
-Dernier point concernant mon canton, c'est un canton ouvert qui, lors des votations, a des positions parmi les plus ouvertes au niveau suisse. L'ouverture, c'est tout le contraire de la fermeture. Quand un canton se ferme, quand un pays se ferme, pendant quelques années, il peut peut-être vivre sur cette notion de souveraineté, quoique aujourd'hui on est dépendant des uns des autres, on le voit avec les taxes américaines. C'est pour ça que le canton de Vaud a dit à la députation vaudoise dans cette chambre de soutenir le travail du Conseil fédéral que nous remercions sincèrement pour avoir atteint les objectifs et pour le projet qui est sur la table. Je vous encourage à en faire de même, à entrer en matière, à améliorer si on peut le faire deux ou trois points de l'accord général puis à l'envoyer au Conseil national pour qu'il puisse l'examiner et ainsi trouver une destinée pour notre pays, de la stabilité, de la prévisibilité et de la sécurité juridique dans un monde en pleine évolution et insécuritaire.
+Le débat que nous avons aujourd'hui - et c'est pour cela que je vous encourage à entrer en matière -, c'est un débat important, qui permettra d'avoir de la perspective et de créer justement cette Suisse qu'on aime.
+J'aimerais remercier également les partenaires sociaux. Parce que pour moi, l'Europe, c'est avant tout économique, puisqu'on contrôle notre marché du travail. Les partenaires sociaux dans ce dossier ont travaillé - c'était difficile, je le sais : notre collègue Maillard a travaillé, au nom de l'Union syndicale suisse (USS), avec d'autres partenaires. La partie adverse, l'économie, a trouvé un chemin : 14 mesures, que je soutiendrai, car je pense qu'elles s'inscrivent dans une logique très claire. Il s'agit de garantir le pouvoir d'achat, les salaires, la cohésion et, de nouveau, la stabilité et les équilibres, la prévisibilité. C'est dans cet esprit que j'ai compris ce dossier.
+Je ne souhaitais pas intervenir, mais comme chaque canton s'est exprimé en apportant son éclairage, je vais parler encore quelques minutes de mon canton de Vaud. C'est le troisième canton suisse. Bientôt un million d'habitants et j'en suis très fier. Cela ne me pose aucun problème que nous ayons un million d'habitants, parce que nous avons une pyramide des âges équilibrée, entre les personnes qui vieillissent, les jeunes qui doivent trouver une destinée et ceux qui sont dans le monde du travail.
+Ensuite, nous avons les hautes écoles. Nous traiterons tout à l'heure ou demain d'Erasmus plus. Là aussi il faut de la prévisibilité. Quand nous n'avons pas signé les accords avec le milieu académique et autres, on a pleuré et il a fallu trouver des solutions. On doit stabiliser ce dossier pour le bien de nos enfants. On n'a pas de pétrole, mais par contre on a de hautes écoles et nos hautes écoles doivent avoir des partenariats équilibrés avec l'étranger. Là aussi il en va de la sécurité.
+Dernier point concernant mon canton, c'est un canton ouvert qui, lors des votations, a des positions parmi les plus ouvertes sur le plan suisse. L'ouverture, c'est tout le contraire de la fermeture. Quand un canton se ferme, quand un pays se ferme, pendant quelques années, il peut peut-être vivre sur cette notion de souveraineté, quoiqu'aujourd'hui on soit dépendant les uns des autres, on le voit avec les taxes américaines. C'est pour cela que le canton de Vaud a dit à la députation vaudoise dans cette chambre de soutenir le travail du Conseil fédéral que nous remercions sincèrement pour avoir atteint les objectifs et pour le projet qui est sur la table. Je vous encourage à en faire de même, à entrer en matière, à améliorer, si on peut le faire, deux ou trois points de l'accord général puis à l'envoyer au Conseil national pour qu'il puisse l'examiner et ainsi trouver une destinée pour notre pays, de la stabilité, de la prévisibilité et de la sécurité juridique dans un monde en pleine évolution et insécuritaire.
 </t>
   </si>
   <si>
@@ -634,13 +634,15 @@
 Wir müssen sorgfältig abwägen, was wir heute tun. Es ist der wichtigste strategische Entscheid unseres Landes für die nächsten Jahrzehnte, ja, für die nächsten Generationen. Wir sollten nicht zaudern. Die Verträge geben uns das Instrumentarium für eine selbstbewusste Umsetzung, die unseren Interessen Rechnung trägt. Diesen Spielraum müssen wir selbstbewusst nutzen. Ich bin davon überzeugt, dass wir das tun und mit unseren Beratungen auch zeigen werden.
 Die Antwort - Sie merken es - ist daher für mich klar: Eintreten auf das Stabilisierungspaket mit der EU und Ja zur Weiterentwicklung unserer heute schon erfolgreichen Beziehungen, statt noch mehr zu verzögern. Und Ja zum fakultativen Staatsvertragsreferendum, damit die betroffenen Stimmbürgerinnen und Stimmbürger allein entscheiden können, denn sie sind direkt betroffen - sie und ihre Nachkommen.
 Die Schweiz ist nicht trotz ihrer Verflechtung mit Europa erfolgreich. Sie ist vor allem aufgrund ihrer Verbundenheit mit Europa erfolgreich. Die Schweiz ist Europa - eigentlich komisch, dass man das immer wiederholen muss. Jetzt geht es darum, diese Verbindungen für die Zukunft zu sichern. Die Welt um uns herum ist nämlich unsicherer geworden. Gerade in solchen Zeiten wäre es töricht, die Beziehungen zu unseren wichtigsten und verlässlichsten Partnern unnötig zu schwächen.
-Der internationale Handel wird härter. Macht gilt vor Recht. Wollen Sie mit solchen Staaten weitere Verträge abschliessen, Freihandelsabkommen, und Staatsverträge aushandeln, und übermorgen ist wieder alles anders? Wir haben Herausforderungen mit der zukünftigen Energieversorgung. Fragen der Forschung, Gesundheit und Sicherheit müssen wir bewältigen, und nicht nur die Schweiz steht vor diesen Herausforderungen. Wir haben mit diesem Extremsommer einen Fingerzeig der Klimakrise erlebt. Das können wir als Schweiz nicht alleine lösen, mitten in Europa. Wir sollten das gemeinsam tun. Deshalb ist es wichtig, dass wir diese Weiterentwicklung unserer Beziehungen zur EU als unserem stabilsten Partner weiterverfolgen.
-Die Herren Schmid und Stark sagten vorhin, es könnten ja einfach die Bilateralen I und II weitergeführt werden. Das ist Selbstbetrug, geschätzte Kollegen, es tut mir leid. Denn wir wissen heute, und das können Ihnen alle bestätigen, und die Wirtschaft spürt bereits, dass das nicht stimmt. Unsere heutigen Abkommen erodieren, weil es in den 25 Jahren in der EU, in der Welt und auch in der Schweiz so viele Veränderungen gegeben hat. Stellen Sie sich vor, wie schnell sich alles verändert! Wir sind weder im Jahr 1291, die geschätzte Kollegin Z'graggen ist noch nicht da, und wir sind auch nicht im Jahre 2000, geschätzter Kollege Schmid.
-Ich gebe ein Beispiel. Unsere Pharma- und Medtech-Firmen sowie die Maschinenindustrie sind ganz direkt und unmittelbar betroffen, wenn die gegenseitige Anerkennung der technischen Standards nicht mehr aktualisiert wird. Zahlreiche Konzerne und KMU mit Sitz in der Nordwestschweiz sind auf einen diskriminierungsfreien Zugang zum europäischen Markt angewiesen. Ohne die Bilateralen werden Firmen ihre Investitionen eher im Ausland tätigen. Soll ich Ihnen sagen, was das Ausland bedeutet? Es bedeutet einfach: fünf Kilometer verschieben, über die Landesgrenze ins Elsass oder nach Südbaden oder in andere Regionen. 15 Kantone in unserem Land sind Grenzregionen. Das heisst, es ist eigentlich einfach. Dies hat direkte Auswirkungen auf Arbeitsplätze und die Volkswirtschaft, und auf unser Wissen. Wissen ist nämlich die wichtigste Ressource der Schweiz, und es definiert unsere Zukunft, besonders für den Innovations- und Life-Science-Standort Nordwestschweiz. Wissen braucht Vernetzung, weswegen der Zugang zu den EU-Programmen Horizon Europe und Erasmus plus für den Forschungsplatz Schweiz unverzichtbar ist.
-Noch ein Wort als Vertreterin der Nordwestschweiz und des Kantons Basel-Landschaft: In der Nordwestschweizer Regierungskonferenz sind die Kantone Solothurn, Aargau, Basel-Stadt, Jura und Basel-Landschaft vertreten. Sie haben gemeinsam bekräftigt, dass geregelte Beziehungen zur Europäischen Union unverzichtbar sind. Sie sind überzeugt, dass das Verhandlungsergebnis geregelte Beziehungen mit der EU ermöglicht und den bilateralen Weg absichert und weiterentwickelt. Sie wissen als Grenzregionen, wie eng verflochten die Beziehungen zu den benachbarten EU-Staaten sind. Sie sind für die Nordwestschweizer Kantone existenziell. Ich möchte hier auch noch darauf hinweisen, dass es darum geht, dass daher auch offene Grenzen in Verbindung mit der Absicherung des Schweizer Lohnschutzniveaus elementar für einen funktionierenden Arbeitsmarkt, gute wirtschaftliche Zusammenarbeit und den gesellschaftlichen Zusammenhalt in einer Grenzregion sind.
-Diese klare Haltung kommt nicht von ungefähr. Die Nordwestschweiz ist die exportstärkste Region der Schweiz. Fast die Hälfte aller Schweizer Exporte kommen aus der Nordwestschweiz, wovon wiederum die Hälfte in die EU als wichtigsten Handelspartner der Schweiz geht. Das kann niemand von heute auf morgen einfach ersetzen. Es ist nicht ersetzbar. Das sind unsere Nachbarn, die wichtigsten Handelspartner.
-Ich bin überzeugt, dass wir eine Schweiz wollen, die ihre Zukunft selbstbewusst gestaltet, keine Schweiz, die aus Angst vor Veränderungen Schritt für Schritt sich selbst ins Abseits stellt und sich auch noch ideologisch verschanzt. Die Bilateralen III sind kein Abschied von unserer nationalen Entscheidungsfreiheit. Wir werden hier als Parlament immer entscheiden und immer auch das letzte Wort haben. Das ist wichtig und muss gewährleistet sein, und das ist es auch. Die Bilateralen III sind die Fortsetzung eines Weges, den die Schweiz vor 25 Jahren eingeschlagen hat: eigenständig bleiben und trotzdem eng mit unseren europäischen Nachbarn zusammenarbeiten. Genau das wird mit dem Paket bezweckt, das nun vorliegt. 
-Ich will diese souveräne Schweiz, eine Schweiz, die ihren Kindern nicht nur Wohlstand hinterlässt, sondern eben auch gesunde Lebensgrundlagen und eine vielfältige Gesellschaft sowie Freiheit, Demokratie und Rechtsstaatlichkeit. Das können wir gemeinsam erreichen. Daran müssen wir gemeinsam arbeiten. Ich will eine Schweiz, die weiterhin mitredet und mitbestimmt, und zwar dort, wo sie ihre Zukunft beeinflussen kann. Ich will keine Schweiz, die nur reagiert und immer hinterherspringt und sich dann beugen muss, wenn Macht vor Recht gilt. Daher ist für mich klar: Ich trete ein und werde auch mit Überzeugung diesem EU-Vertragspaket zustimmen.
+Der internationale Handel wird zunehmend härter. Macht gilt vor Recht. Wollen Sie mit solchen Staaten weitere Verträge, Freihandelsabkommen abschliessen und Staatsverträge aushandeln - und übermorgen ist wieder alles anders?
+Wir haben Herausforderungen mit der zukünftigen Energieversorgung, wir müssen Fragen der Forschung, Gesundheit und Sicherheit bewältigen, und vor diesen Herausforderungen steht nicht nur die Schweiz. Dieser Extremsommer war ein Fingerzeig der Klimakrise. Das alles können wir als Schweiz mitten in Europa nicht alleine lösen. Wir sollten das gemeinsam tun. Deshalb ist es wichtig, dass wir diese Weiterentwicklung unserer Beziehungen zur EU als unserem stabilsten Partner weiterverfolgen.
+Die Herren Schmid und Stark sagten vorhin, es könnten ja einfach die Bilateralen I und II weitergeführt werden. Das ist Selbstbetrug, geschätzte Kollegen, es tut mir leid. Wir wissen - das können Ihnen alle bestätigen und die Wirtschaft spürt es bereits -, dass das nicht stimmt. Unsere heutigen Abkommen erodieren, weil es in den letzten 25 Jahren in der EU, in der Welt und auch in der Schweiz sehr viele Veränderungen gegeben hat. Denken Sie daran, wie schnell sich alles verändert. Wir sind weder im Jahr 1291, geschätzte Kollegin Z'graggen, noch sind wir im Jahr 2000, geschätzter Kollege Schmid.
+Ich gebe ein Beispiel. Unsere Pharma- und Medtech-Firmen sowie die Maschinenindustrie sind ganz direkt und unmittelbar betroffen, wenn die gegenseitige Anerkennung der technischen Standards nicht mehr aktualisiert wird. Zahlreiche Konzerne und KMU mit Sitz in der Nordwestschweiz sind auf einen diskriminierungsfreien Zugang zum europäischen Markt angewiesen. Ohne die Bilateralen werden Firmen ihre Investitionen eher im Ausland tätigen. Soll ich Ihnen sagen, was das Ausland bedeutet? Es bedeutet einfach: fünf Kilometer verschieben, über die Landesgrenze ins Elsass oder nach Südbaden oder in andere Regionen. 15 Kantone in unserem Land sind Grenzregionen. Das heisst, es ist eigentlich einfach, es hat direkte Auswirkungen auf Arbeitsplätze und die Volkswirtschaft - und auf unser Wissen. Wissen ist nämlich die wichtigste Ressource der Schweiz, und es definiert unsere Zukunft, besonders für den Innovations- und Life-Science-Standort Nordwestschweiz. Wissen braucht Vernetzung, weswegen der Zugang zu den EU-Programmen Horizon Europe und Erasmus plus für den Forschungsplatz Schweiz unverzichtbar ist.
+Noch ein Wort als Vertreterin der Nordwestschweiz und des Kantons Basel-Landschaft: In der Nordwestschweizer Regierungskonferenz sind die Kantone Solothurn, Aargau, Basel-Stadt, Jura und Basel-Landschaft vertreten. Sie haben gemeinsam bekräftigt, dass geregelte Beziehungen zur Europäischen Union unverzichtbar sind. Sie sind überzeugt, dass das Verhandlungsergebnis geregelte Beziehungen mit der EU ermöglicht und den bilateralen Weg absichert und weiterentwickelt. Sie wissen als Grenzregionen, wie eng verflochten die Beziehungen zu den benachbarten EU-Staaten sind. Sie sind für die Nordwestschweizer Kantone existenziell. Ich möchte auch noch darauf hinweisen, dass offene Grenzen in Verbindung mit der Absicherung des Schweizer Lohnschutzniveaus elementar für einen funktionierenden Arbeitsmarkt, gute wirtschaftliche Zusammenarbeit und den gesellschaftlichen Zusammenhalt in einer Grenzregion sind.
+Diese klare Haltung kommt nicht von ungefähr. Die Nordwestschweiz ist die exportstärkste Region der Schweiz. Fast die Hälfte aller Schweizer Exporte kommt aus der Nordwestschweiz, wovon wiederum die Hälfte in die EU als wichtigsten Handelspartner der Schweiz geht. Das kann niemand von heute auf morgen einfach ersetzen. Es ist nicht ersetzbar. Das sind unsere Nachbarn, die wichtigsten Handelspartner.
+Ich bin überzeugt, dass wir eine Schweiz wollen, die ihre Zukunft selbstbewusst gestaltet, keine Schweiz, die aus Angst vor Veränderungen sich Schritt für Schritt selbst ins Abseits stellt und sich auch noch ideologisch verschanzt. Die Bilateralen III sind kein Abschied von unserer nationalen Entscheidungsfreiheit. Wir werden hier als Parlament immer entscheiden und immer auch das letzte Wort haben. Das ist wichtig und muss gewährleistet sein, und das ist es auch. Die Bilateralen III sind die Fortsetzung eines Weges, den die Schweiz vor 25 Jahren eingeschlagen hat: eigenständig bleiben und trotzdem eng mit unseren europäischen Nachbarn zusammenarbeiten. Genau das wird mit dem Paket bezweckt, das nun vorliegt. 
+Ich will diese souveräne Schweiz, eine Schweiz, die ihren Kindern nicht nur Wohlstand hinterlässt, sondern eben auch gesunde Lebensgrundlagen und eine vielfältige Gesellschaft sowie Freiheit, Demokratie und Rechtsstaatlichkeit. Das können wir gemeinsam erreichen. Daran müssen wir gemeinsam arbeiten. Ich will eine Schweiz, die weiterhin mitredet und mitbestimmt, und zwar dort, wo sie ihre Zukunft beeinflussen kann. Ich will keine Schweiz, die nur reagiert und immer hinterherspringt und sich dann beugen muss, wenn Macht vor Recht gilt.
+Daher ist für mich klar: Ich trete ein und werde diesem EU-Vertragspaket auch mit Überzeugung zustimmen.
 </t>
   </si>
 </sst>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -288,14 +288,14 @@
   </si>
   <si>
     <t xml:space="preserve">Il ne reste plus beaucoup de divergences par rapport à la décision du Conseil national. Il nous a rejoints sur beaucoup de points et nous l'avons également rejoint sur un certain nombre de points, ce qui est souhaitable, notamment concernant le maintien de la protection des marais, qui était vraiment l'un des impératifs et l'une des lignes rouges, à notre sens, dans ce projet. 
-Pour ce qui est de la divergence à l'article 15bbis alinéa 3, notre conseil proposait de modifier trois choses par rapp</t>
+Pour ce qui est de la divergence à l'article 15bbis alinéa 3, notre conseil proposait de modifier trois éléments par ra</t>
   </si>
   <si>
     <t xml:space="preserve">Il ne reste plus beaucoup de divergences par rapport à la décision du Conseil national. Il nous a rejoints sur beaucoup de points et nous l'avons également rejoint sur un certain nombre de points, ce qui est souhaitable, notamment concernant le maintien de la protection des marais, qui était vraiment l'un des impératifs et l'une des lignes rouges, à notre sens, dans ce projet. 
-Pour ce qui est de la divergence à l'article 15bbis alinéa 3, notre conseil proposait de modifier trois choses par rapport au projet du Conseil fédéral. Premièrement, il souhaitait que les exigences environnementales ne soient plus prises en compte, mais examinées, ce qui introduisait un affaiblissement de l'alinéa. Deuxièmement, il souhaitait introduire les intérêts des propriétaires fonciers dans cet examen. Troisièmement, il souhaitait réduire les distances légales des lignes par rapport aux forêts et aux cours d'eau. Le Conseil national proposait, lui, de maintenir la version du Conseil fédéral.
-Pourquoi vous ai-je proposé de rester sur cette version par le biais de ma minorité ? Pour trois raisons. Premièrement, l'expression "prendre en compte" plutôt qu'"examiner" entraîne plutôt des incertitudes, parce qu'examiner n'implique pas forcément que l'on prendra en compte, et, pour les autorités d'application, cette notion "d'examiner les intérêts" n'est pas claire et entraîne plutôt des incertitudes. Deuxièmement, s'agissant des intérêts des propriétaires fonciers, notre conseil a souhaité intégrer l'examen des intérêts des propriétaires fonciers dans la pesée des intérêts. Sur une ligne qui réunirait plusieurs dizaines de propriétaires fonciers, cela serait plutôt un facteur de ralentissement que d'accélération de la procédure s'il fallait véritablement examiner leurs intérêts. Dès lors, la version du Conseil des États n'est pas un facteur d'accélération, ce qui est pourtant l'objectif premier de ce projet de loi.
-Enfin - et peut-être l'élément le plus important -, c'est la réduction des distances légales pour la construction à proximité des forêts et des cours d'eau. Ce qui est important, c'est le fait que la réduction de ces distances est déjà contenue dans une autre loi, à savoir la loi sur les forêts (LFo). Il est déjà possible, en vertu de l'article 17 alinéa 3 LFo, de réduire les distances pour la construction d'infrastructures par rapport aux forêts. Dès lors, il ne serait pas nécessaire d'introduire cette mention à l'alinéa 3.
-Le deuxième problème concerne la notion d'examen : si l'on peut réduire ces distances en examinant, mais sans faire de pesée des intérêts et approfondir les problématiques en place, on pourrait être amené à créer des problèmes de sécurité en construisant de nouvelles lignes. On pense notamment - ce ne sont pas des cas fictifs - à ce qu'il pourrait arriver en cas d'incendies de forêt s'ils entraient en contact avec les lignes électriques. On pense également aux tempêtes telles qu'on les a connues ces dernières années, qui peuvent déraciner des arbres et faire tomber des branches sur la ligne de contact. Il n'est donc pas souhaitable d'introduire une disposition qui permet, sans grand examen, de réduire les distances des constructions par rapport aux forêts dans la loi en vigueur.
+Pour ce qui est de la divergence à l'article 15bbis alinéa 3, notre conseil proposait de modifier trois éléments par rapport au projet du Conseil fédéral. Premièrement, il souhaitait que les exigences environnementales ne soient plus prises en compte, mais examinées, ce qui introduisait un affaiblissement de l'alinéa. Deuxièmement, il souhaitait introduire les intérêts des propriétaires fonciers dans cet examen. Troisièmement, il souhaitait réduire les distances légales des lignes par rapport aux forêts et aux cours d'eau. Le Conseil national proposait, lui, de maintenir la version du Conseil fédéral.
+Pourquoi vous ai-je proposé d'en rester à cette version par le biais de ma minorité[NB]? Je l'ai fait pour trois raisons. Premièrement, l'expression "prendre en compte" plutôt qu'"examiner" entraîne plutôt des incertitudes, parce qu'examiner n'implique pas forcément que l'on prendra en compte, et, pour les autorités d'application, cette notion "d'examiner les intérêts" n'est pas claire et entraîne plutôt des incertitudes. Deuxièmement, s'agissant des intérêts des propriétaires fonciers, notre conseil a souhaité intégrer l'examen des intérêts des propriétaires fonciers dans la pesée des intérêts. Sur une ligne qui réunirait plusieurs dizaines de propriétaires fonciers, cela serait plutôt un facteur de ralentissement que d'accélération de la procédure s'il fallait véritablement examiner leurs intérêts. Dès lors, la version du Conseil des États n'est pas un facteur d'accélération, ce qui est pourtant l'objectif premier de ce projet de loi.
+Enfin - et peut-être l'élément le plus important -, c'est la réduction des distances légales pour la construction à proximité des forêts et des cours d'eau. La réduction de ces distances - c'est important - est déjà contenue dans une autre loi, à savoir la loi sur les forêts (LFo). Il est déjà possible, en vertu de l'article 17 alinéa 3 LFo, de réduire les distances pour la construction d'infrastructures par rapport aux forêts. Dès lors, il n'est pas nécessaire d'introduire cette mention à l'alinéa 3.
+Le deuxième problème concerne la notion d'examen[NB]: si l'on peut réduire ces distances en examinant, mais sans faire de pesée des intérêts et approfondir les problématiques en place, on pourrait être amené à créer des problèmes de sécurité en construisant de nouvelles lignes. On pense notamment - ce ne sont pas des cas fictifs - à ce qui pourrait arriver en cas d'incendie de forêt s'ils entraient en contact avec les lignes électriques. On pense également aux tempêtes telles qu'on les a connues ces dernières années, qui peuvent déraciner des arbres et faire tomber des branches sur une ligne électrique. Il n'est donc pas souhaitable d'introduire une disposition qui permet, sans grand examen, de réduire les distances des constructions par rapport aux forêts dans la loi en vigueur.
 Dès lors, je vous invite, à l'instar du Conseil fédéral, à suivre ma minorité et à vous rallier au Conseil national pour cet article 15bbis alinéa 3.
 </t>
   </si>
@@ -303,37 +303,35 @@
     <t xml:space="preserve">419872</t>
   </si>
   <si>
-    <t xml:space="preserve">La Commission des transports et des télécommunications de notre conseil propose de ne pas classer ce postulat, contrairement à ce qu'indique, ou plutôt, en complément de ce qu'indique le Conseil fédéral, qui veut peut-être intégrer cela dans son projet Transports'45. Aujourd'hui, on n'a même pas encore terminé la consultation concernant le projet Transports'45 et on voit la nécessité qu'il y a d'agir dans ce secteur, puisque la semaine passée encore, il y a eu une interruption de trafic très imp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Commission des transports et des télécommunications de notre conseil propose de ne pas classer ce postulat, contrairement à ce qu'indique, ou plutôt, en complément de ce qu'indique le Conseil fédéral, qui veut peut-être intégrer cela dans son projet Transports'45. Aujourd'hui, on n'a même pas encore terminé la consultation concernant le projet Transports'45 et on voit la nécessité qu'il y a d'agir dans ce secteur, puisque la semaine passée encore, il y a eu une interruption de trafic très importante liée à une insuffisance de l'infrastructure. Il n'y avait pas de redondance pour faire circuler les trains et même l'autoroute était bloquée à cet endroit. Si la commission peut entendre que le Conseil fédéral introduira quelque chose, aujourd'hui on n'a rien de vraiment concret, raison pour laquelle nous proposons de maintenir ce postulat encore en suspens jusqu'à ce que nous ayons des éléments plus concrets du côté du Conseil fédéral.
+    <t xml:space="preserve">La Commission des transports et des télécommunications de notre conseil propose de ne pas classer ce postulat, contrairement à ce qu'indique, ou plutôt, en complément de ce qu'indique le Conseil fédéral, qui veut peut-être intégrer cela dans son projet "Transports '45". Aujourd'hui, on n'a même pas encore terminé la consultation concernant le projet Transports'45 et on voit la nécessité qu'il y a d'agir dans ce secteur, puisque la semaine passée encore, il y a eu une interruption de trafic très </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Commission des transports et des télécommunications de notre conseil propose de ne pas classer ce postulat, contrairement à ce qu'indique, ou plutôt, en complément de ce qu'indique le Conseil fédéral, qui veut peut-être intégrer cela dans son projet "Transports '45". Aujourd'hui, on n'a même pas encore terminé la consultation concernant le projet Transports'45 et on voit la nécessité qu'il y a d'agir dans ce secteur, puisque la semaine passée encore, il y a eu une interruption de trafic très importante liée à une insuffisance de l'infrastructure. Il n'y avait pas de redondance pour faire circuler les trains et même l'autoroute était bloquée à cet endroit. Si la commission peut entendre que le Conseil fédéral introduira quelque chose dans son message, aujourd'hui on n'a rien de vraiment concret, raison pour laquelle nous proposons de maintenir ce postulat encore en suspens jusqu'à ce que nous ayons des éléments plus concrets du côté du Conseil fédéral.
 </t>
   </si>
   <si>
     <t xml:space="preserve">420151</t>
   </si>
   <si>
-    <t xml:space="preserve">Comme vous, Monsieur le président, je ne suis pas un adepte du fait que chaque membre de la commission participe au débat, mais en l'occurrence, permettez-moi quand même d'exprimer quelques mots en français, parce que, dans ce débat, il y a surtout des Alémaniques qui se sont exprimés. Je suis content d'apprendre que mon collègue Broulis va aussi intervenir ; ce qui fait qu'il ne restera plus que deux membres de la commission qui ne se seront pas exprimés, mais ça, c'est une autre question.
-Nous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comme vous, Monsieur le président, je ne suis pas un adepte du fait que chaque membre de la commission participe au débat, mais en l'occurrence, permettez-moi quand même d'exprimer quelques mots en français, parce que, dans ce débat, il y a surtout des Alémaniques qui se sont exprimés. Je suis content d'apprendre que mon collègue Broulis va aussi intervenir ; ce qui fait qu'il ne restera plus que deux membres de la commission qui ne se seront pas exprimés, mais ça, c'est une autre question.
-Nous menons aujourd'hui un débat qui engage notre responsabilité face à la sécurité du pays et de sa population. Parler d'augmenter le budget de l'armée suisse, ce n'est pas céder à un réflexe militariste. C'est regarder avec lucidité l'état de nos infrastructures de défense en parallèle de la situation du monde qui nous entoure.
-Depuis le début des années 1990, la Suisse a vécu avec l'illusion d'une fin de l'histoire, d'une paix perpétuelle sur le continent européen. Cette illusion s'est traduite par des choix comptables clairs. Quelques rappels chiffrés qui ne sont que des faits sans aucune appréciation : en 1990, le budget de l'armée représentait près de 16 pour cent des dépenses globales de la Confédération. Aujourd'hui, il atteint à peine les 6 pour cent, soit une diminution de 60 pour cent, alors que c'est une tâche régalienne de la seule responsabilité de la Confédération.
-Pendant trois décennies, la défense nationale a été la variable d'ajustement préférée des budgets, pour financer certes légitimement la croissance d'autres domaines essentiels comme la prévoyance sociale - plus 30 pour cent - ou les transports, dont les montants ont été multipliés par 3, en même temps que le budget de la Confédération était lui aussi multiplié par 3, passant de 31 milliards de francs en 1990 à 90 milliards en 2026.
-Mais le dividende de la paix a expiré. La guerre est de retour sur notre continent. Les menaces hybrides, cybernétiques, et le durcissement du contexte géopolitique ne sont plus des hypothèses d'exercices d'état-major, ce sont des réalités quotidiennes. Les rapports du Conseil fédéral et les analyses de nos propres commissions sont sans concession : en cas de conflit majeur, les deux tiers de nos troupes ne disposeraient pas d'un équipement complet et nos stocks de munitions suffiraient à peine pour quelques semaines. Notre pays n'a quasiment aucune couverture moderne face aux attaques aériennes et sol-air à basse et moyenne portées.
-Selon le Conseil fédéral, l'armée a un besoin urgent de 24 milliards de francs : 15 milliards d'investissements et 9 milliards pour parer aux augmentations inévitables sur le marché de l'armement. Ce n'est pas un chèque en blanc, mais un crédit-cadre dont l'utilisation sera soumise au Parlement lors de chaque budget, dans le respect des outils légaux à disposition. C'est vrai qu'il est plus facile de lister les titres des journaux que de donner les moyens au Conseil fédéral de remplir une de ses missions régaliennes : assurer la défense du pays pour protéger sa population.
-Dire que le budget militaire explose est un contresens statistique, je l'ai démontré. Ce que nous votons, c'est un plan de rattrapage structurel pour amener ensuite durablement nos dépenses de défense à 1 pour cent du PIB. C'est le strict minimum pour un État souverain et neutre. Comment justifier notre neutralité, dont le sens fait débat actuellement, si nous sommes incapables d'assurer de manière autonome la protection de notre espace aérien et de nos infrastructures critiques ? La neutralité n'est pas un bouclier magique, c'est une responsabilité opérationnelle. Elle doit être appuyée par une volonté et des moyens de défense crédibles qui s'insèrent dans un puzzle de la défense du continent européen.
-Le Conseil fédéral nous propose de recourir uniquement à l'augmentation de la TVA - pour rappel : 0,5 point pour le taux de TVA de base, 0,5 point pour le taux spécial - sans toucher au taux applicable aux produits de première nécessité, épargnant ainsi en grande partie le porte-monnaie des ménages et des familles. Il propose aussi la création d'un fonds pouvant s'endetter, destiné à obtenir davantage de souplesse dans la gestion des commandes d'armement.
-La Commission des finances nous a proposé un compromis avec un relèvement de la TVA de 0,2 point pour le taux de base et de 0,1 point pour le taux spécial, ainsi que l'utilisation de 50 pour cent des restes de crédit, comme pour la création d'un fonds. C'est une trajectoire financière responsable, pragmatique et surtout respectueuse du frein à l'endettement qui fait la force de notre gestion publique. Je remercie la Commission des finances des réflexions qu'elle a menées et de la proposition qu'elle a formulée. La Commission de la politique de sécurité a repris cette proposition sous forme de concept qu'elle a un peu amendé, notamment quant à la durée du fonds et à sa capacité d'endettement.
-Rappelons que sans sécurité, il n'y a ni prospérité économique, ni stabilité sociale, ni formation de qualité. La sécurité est le socle sur lequel reposent toutes nos autres politiques publiques. Investir dans l'armée, ce n'est pas préparer la guerre ; c'est garantir que notre population puisse continuer à vivre en sécurité et en liberté, à l'abri des chantages internationaux. Il est donc assez naturel de recourir notamment à cette modeste augmentation temporaire de la TVA. Certes, ce n'est pas une solution facile, mais c'est notre travail de définir des solutions et, si nécessaire, de les proposer et de les défendre devant le peuple souverain.
+    <t xml:space="preserve">Je ne suis pas un adepte du fait que chaque membre de la commission participe au débat, mais en l'occurrence, permettez-moi quand même d'exprimer quelques mots en français, parce que, dans ce débat, il y a surtout des Alémaniques qui se sont exprimés. Je suis content d'apprendre que mon collègue Broulis va aussi intervenir[NB]; ce qui fait qu'il ne restera plus que deux membres de la commission qui ne se seront pas exprimés, mais c'est une autre question.
+Nous menons aujourd'hui un débat qui eng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne suis pas un adepte du fait que chaque membre de la commission participe au débat, mais en l'occurrence, permettez-moi quand même d'exprimer quelques mots en français, parce que, dans ce débat, il y a surtout des Alémaniques qui se sont exprimés. Je suis content d'apprendre que mon collègue Broulis va aussi intervenir[NB]; ce qui fait qu'il ne restera plus que deux membres de la commission qui ne se seront pas exprimés, mais c'est une autre question.
+Nous menons aujourd'hui un débat qui engage notre responsabilité face à la sécurité du pays et de sa population. Parler d'augmenter le budget de l'armée suisse, ce n'est pas céder à un réflexe militariste, c'est regarder avec lucidité l'état de nos infrastructures de défense en parallèle de la situation du monde qui nous entoure.
+Depuis le début des années 1990, la Suisse a vécu avec l'illusion de la fin de l'histoire, d'une paix perpétuelle sur le continent européen. Cette illusion s'est traduite par des choix comptables clairs. Quelques rappels chiffrés qui ne sont que des faits sans aucune appréciation[NB]: en 1990, le budget de l'armée représentait près de 16 pour cent des dépenses globales de la Confédération. Aujourd'hui, il atteint à peine 6 pour cent, soit une diminution de 60 pour cent, alors que c'est une tâche régalienne de la seule responsabilité de la Confédération. Pendant trois décennies, la défense nationale a été la variable d'ajustement préférée des budgets, pour financer certes légitimement la croissance d'autres domaines essentiels comme la prévoyance sociale - plus 30 pour cent - ou les transports, dont les montants ont été multipliés par 3, en même temps que le budget de la Confédération était lui aussi multiplié par 3, passant de 31 milliards de francs en 1990 à 90 milliards en 2026.
+Mais les dividendes de la paix ont expiré. La guerre est de retour sur notre continent. Les menaces hybrides, cybernétiques, et le durcissement du contexte géopolitique ne sont plus des hypothèses d'exercices d'état-major, ce sont des réalités quotidiennes. Les rapports du Conseil fédéral et les analyses de nos propres commissions sont sans concession[NB]: en cas de conflit majeur, les deux tiers de nos troupes ne disposeraient pas d'un équipement complet et nos stocks de munitions suffiraient à peine pour quelques semaines. Notre pays n'a quasiment aucune couverture moderne face aux attaques aériennes et sol-air à basse et moyenne portées.
+Selon le Conseil fédéral, l'armée a un besoin urgent de 24 milliards de francs[NB]: 15 milliards d'investissements et 9 milliards pour parer aux augmentations inévitables sur le marché de l'armement. Ce n'est pas un chèque en blanc, mais un crédit-cadre dont l'utilisation sera soumise au Parlement lors de chaque budget, dans le respect des outils légaux à disposition. C'est vrai qu'il est plus facile de lister les titres des journaux que de donner les moyens au Conseil fédéral de remplir une de ses missions régaliennes[NB]: assurer la défense du pays pour protéger sa population.
+Dire que le budget militaire explose est un contresens statistique, je l'ai démontré. Ce que nous votons, c'est un plan de rattrapage structurel pour amener ensuite durablement nos dépenses de défense à 1 pour cent du PIB. C'est le strict minimum pour un État souverain et neutre. Comment justifier notre neutralité, dont le sens fait débat actuellement, si nous sommes incapables d'assurer de manière autonome la protection de notre espace aérien et de nos infrastructures critiques[NB]? La neutralité n'est pas un bouclier magique, c'est une responsabilité opérationnelle. Elle doit être appuyée par une volonté et des moyens de défense crédibles qui s'insèrent dans le puzzle de la défense du continent européen.
+Le Conseil fédéral nous propose de recourir uniquement à l'augmentation de la TVA - pour rappel[NB]: 0,5 point pour le taux de TVA de base, 0,5 point pour le taux spécial - sans toucher au taux applicable aux produits de première nécessité, épargnant ainsi en grande partie le porte-monnaie des ménages et des familles. Il propose aussi la création d'un fonds pouvant s'endetter, destiné à obtenir davantage de souplesse dans la gestion des commandes d'armement.
+La Commission des finances nous a proposé un compromis avec un relèvement de la TVA de 0,2 point pour le taux de base et de 0,1 point pour le taux spécial, ainsi que l'utilisation de 50 pour cent des restes de crédit pour la création d'un fonds. C'est une trajectoire financière responsable, pragmatique et surtout respectueuse du frein à l'endettement qui fait la force de notre gestion publique. Je remercie la Commission des finances des réflexions qu'elle a menées et de la proposition qu'elle a formulée. La Commission de la politique de sécurité a repris cette proposition sous forme de concept qu'elle a un peu amendé, notamment quant à la durée du fonds et à sa capacité d'endettement.
+Rappelons que sans sécurité, il n'y a ni prospérité économique, ni stabilité sociale, ni formation de qualité. La sécurité est le socle sur lequel reposent toutes nos autres politiques publiques. Investir dans l'armée, ce n'est pas préparer la guerre[NB]; c'est garantir que notre population puisse continuer à vivre en sécurité et en liberté, à l'abri des chantages internationaux. Il est donc assez naturel de recourir notamment à cette modeste augmentation temporaire de la TVA. Certes, ce n'est pas une solution facile, mais c'est notre travail de définir des solutions et, si nécessaire, de les proposer et de les défendre devant le peuple souverain.
 Quant aux autres propositions figurant sur le dépliant, permettez-moi d'apporter à ce stade une appréciation sur les principaux concepts, étant entendu que je n'y reviendrai pas dans la discussion par article. Je constate d'abord que toutes ces propositions retiennent la création d'un fonds pour la défense et la sécurité, et c'est une bonne chose.
-La première variante sans TVA, que propose la minorité II (Dittli), prévoit de recourir seulement à la caisse fédérale en sus des restes de crédit. Elle n'est pas très réaliste, car elle implique de prévoir des programmes d'économie. Or, après être sorti de l'un d'entre eux, on sait à quel point un tel programme est difficile et long à mener.
-Je vous invite donc à rejeter ce concept.
-L'autre concept sans la TVA est défendu par la minorité IV (Salzmann). Le fait de demander le versement d'un dividende de substance de la BNS est très compliqué, peu réaliste, voire impraticable. Qui dit dividende de substance implique en effet le fait d'être actionnaire de la BNS. Or, je vous l'apprendrai peut-être - les membres de la Commission des finances le savent sûrement -, la Confédération n'est pas actionnaire de la BNS, comme le sont les cantons, les banques cantonales et quelques privés. La Confédération n'est pas actionnaire de la BNS et on ne peut pas exiger un dividende de substance lorsqu'on n'est pas propriétaire de cette substance. De plus, en vertu de l'indépendance de la BNS, il serait peu opportun d'y toucher alors que nous l'avons toujours défendue quand il s'agissait de financer l'AVS ou un fonds pour le climat. Je vous invite également à rejeter ce concept.
-La création temporaire d'un nouvel impôt sur les fortunes particulièrement importantes a quant à elle également peu de chance d'aboutir, car elle empiète sur les compétences fiscales des cantons. De plus, qu'est-ce qu'une fortune particulièrement importante ? Il est clair qu'un problème temporel de mise en oeuvre s'installerait également.
+La première variante sans TVA, que propose la minorité II (Dittli), prévoit de recourir seulement à la caisse fédérale en sus des restes de crédit. Elle n'est pas très réaliste, car elle implique de prévoir des programmes d'économies. Or, après être sorti de l'un d'entre eux, on sait à quel point un tel programme est difficile et long à mener. Je vous invite donc à rejeter ce concept.
+L'autre concept sans la TVA est défendu par la minorité IV (Salzmann). Le fait de demander le versement d'un dividende de substance de la BNS est très compliqué, peu réaliste, voire impraticable. Qui dit dividende de substance implique en effet le fait d'être actionnaire de la BNS. Or, je vous l'apprendrai peut-être - les membres de la Commission des finances le savent sûrement -, la Confédération n'est pas actionnaire de la BNS, comme le sont les cantons, les banques cantonales et quelques privés. La Confédération n'est pas actionnaire de la BNS et on ne peut pas exiger un dividende de substance lorsqu'on n'est pas propriétaire de cette substance. De plus, en vertu de l'indépendance de la BNS, il serait peu opportun d'y toucher, alors que nous l'avons toujours défendue quand il s'agissait de financer l'AVS ou un fonds pour le climat. Je vous invite également à rejeter ce concept.
+La création temporaire d'un nouvel impôt sur les fortunes particulièrement importantes a quant à elle également peu de chance d'aboutir, car elle empiète sur les compétences fiscales des cantons. De plus, qu'est-ce qu'une fortune particulièrement importante[NB]? Il est clair qu'un problème temporel de mise en oeuvre s'installerait également.
 L'armée suisse a besoin de visibilité à long terme pour se moderniser et faire face aux menaces les plus pertinentes et les plus immédiates, ce qui ne veut pas dire qu'il faut oublier le reste de l'armée, notamment l'armée de terre.
-Pour notre souveraineté et pour la protection de nos concitoyennes et concitoyens, je vous invite instamment à entrer en matière, à soutenir l'augmentation proposée dans le concept de la majorité de votre Commission de la politique de sécurité. Je vous invite également à refuser le renvoi au Conseil fédéral, qui porte sur des objets sur lesquels le Parlement s'est déjà prononcé.
+Pour notre souveraineté et pour la protection de nos concitoyennes et concitoyens, je vous invite instamment à entrer en matière, à soutenir l'augmentation proposée dans le concept de la majorité de notre Commission de la politique de sécurité. Je vous invite également à refuser le renvoi au Conseil fédéral, qui porte sur des objets sur lesquels le Parlement s'est déjà prononcé.
 </t>
   </si>
   <si>
@@ -643,6 +641,22 @@
 Ich bin überzeugt, dass wir eine Schweiz wollen, die ihre Zukunft selbstbewusst gestaltet, keine Schweiz, die aus Angst vor Veränderungen sich Schritt für Schritt selbst ins Abseits stellt und sich auch noch ideologisch verschanzt. Die Bilateralen III sind kein Abschied von unserer nationalen Entscheidungsfreiheit. Wir werden hier als Parlament immer entscheiden und immer auch das letzte Wort haben. Das ist wichtig und muss gewährleistet sein, und das ist es auch. Die Bilateralen III sind die Fortsetzung eines Weges, den die Schweiz vor 25 Jahren eingeschlagen hat: eigenständig bleiben und trotzdem eng mit unseren europäischen Nachbarn zusammenarbeiten. Genau das wird mit dem Paket bezweckt, das nun vorliegt. 
 Ich will diese souveräne Schweiz, eine Schweiz, die ihren Kindern nicht nur Wohlstand hinterlässt, sondern eben auch gesunde Lebensgrundlagen und eine vielfältige Gesellschaft sowie Freiheit, Demokratie und Rechtsstaatlichkeit. Das können wir gemeinsam erreichen. Daran müssen wir gemeinsam arbeiten. Ich will eine Schweiz, die weiterhin mitredet und mitbestimmt, und zwar dort, wo sie ihre Zukunft beeinflussen kann. Ich will keine Schweiz, die nur reagiert und immer hinterherspringt und sich dann beugen muss, wenn Macht vor Recht gilt.
 Daher ist für mich klar: Ich trete ein und werde diesem EU-Vertragspaket auch mit Überzeugung zustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Würth Benedikt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich habe vorhin schon erwähnt, dass die APK-S insgesamt einfach eine politische Würdigung in die Richtung vorgenommen hat, dass es für die aussenpolitische Lösung eben auch innenpolitische Begleitmassnahmen braucht und die Sozialpartnerschaft in diesem Zusammenhang sehr wichtig ist. Arbeitsfrieden und Arbeitsethos - dieses möchte ich auch erwähnen - sind wesentliche Elemente unserer Standortgunst. Das ist ein Standortvorteil der Schweiz; darauf sind wir auch stolz. 
+Es war bei diesem Dossier - u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich habe vorhin schon erwähnt, dass die APK-S insgesamt einfach eine politische Würdigung in die Richtung vorgenommen hat, dass es für die aussenpolitische Lösung eben auch innenpolitische Begleitmassnahmen braucht und die Sozialpartnerschaft in diesem Zusammenhang sehr wichtig ist. Arbeitsfrieden und Arbeitsethos - dieses möchte ich auch erwähnen - sind wesentliche Elemente unserer Standortgunst. Das ist ein Standortvorteil der Schweiz; darauf sind wir auch stolz. 
+Es war bei diesem Dossier - um das nochmals zu rekapitulieren - nicht immer so, dass die Sozialpartnerschaft wirklich funktioniert hat. Ich kann mich erinnern: Ich war früher noch teilweise als KDK-Präsident bei den tripartiten Gesprächen dabei, als der Vorgänger von Herrn Maillard, unser ehemaliger Kollege und mein ehemaliger Standeskollege Paul Rechsteiner relativ bzw. ziemlich klar sagte: Ich mache da nicht mehr mit, ich verlasse den Tisch. Sie müssen sich einfach nochmals bewusst sein, wo wir damals waren und wo wir heute sind. 
+Wir haben heute eine Lösung, die in zig Runden verhandelt wurde, wie wir uns haben sagen lassen. Es ist offensichtlich ein mühsamer, aber notwendiger Prozess gewesen. Rechtlich gesehen könnte man einfach vom Ergebnis abweichen. Die APK-S ist aber der Auffassung, dass dies politisch nicht klug wäre; gerade als Ständerat sollten wir das nicht machen. Es ist ein bisschen wie beim Finanzausgleich. Wenn sich die Kantone beim Finanzausgleich verständigen, dann tun wir auch gut daran, das im Parlament nicht zu übersteuern; das kommt nicht gut. Ähnlich ist es auch hier bei der Sozialpartnerschaft. Machdem wir eine Lösung erzielen konnten bzw. die Sozialpartner eine Lösung erzielen konnten, sollte man dieses Ergebnis nicht einfach torpedieren. Vor diesem Hintergrund haben wir aus einer Gesamtwürdigung dieses ganzen Prozesses entschieden, den Bundesrat zu unterstützen. Ich bitte Sie, dies ebenfalls zu tun. 
 </t>
   </si>
 </sst>
@@ -697,8 +711,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I32" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I33" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I33"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1924,6 +1938,35 @@
         <v>133</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" t="s">
+        <v>136</v>
+      </c>
+      <c r="I33" t="s">
+        <v>137</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -217,7 +217,7 @@
 C'est précisément ce que vise ma motion[NB]: ne pas céder à la panique et ne pas imposer une technologie particulière, mais planifier la transition de manière progressive, coordonnée et fondée sur les risques. C'est un élément essentiel. Sans inventaire, nous ne pouvons pas piloter correctement une migration. C'est pourquoi la notion de cryptoagilité est particulièrement importante. Nos systèmes doivent être conçus de manière à pouvoir faire évoluer leurs mécanismes cryptographiques sans devoir tout reconstruire à chaque changement de standard.
 C'est une question de cybersécurité, mais également de bonne gestion des deniers publics. Si une migration anticipée peut être planifiée, une migration imposée dans l'urgence risque quant à elle d'être beaucoup plus coûteuse, plus complexe et plus risquée. La Suisse ne part heureusement pas de zéro. La Confédération a déjà identifié cette problématique et dispose de compétences importantes dans le domaine de la cybersécurité et de l'informatique. Ce qui manque encore, c'est précisément une vision nationale, commune, avec des responsabilités, des priorités et des échéances clairement définies.
 Nos partenaires internationaux avancent[NB]: l'Union européenne travaille sur la transition vers la cryptographie post-quantique, et les États-Unis, le Royaume-Uni, la France et l'Allemagne ont également engagé des démarches. La motion prévoit à juste titre des échéances différenciées, une priorité aux cas à haut risque d'ici 2030, puis une transition progressive des autres systèmes critiques ou sensibles d'ici 2035, en fonction de la maturité des standards et de l'interopérabilité. Cette approche permet d'éviter deux erreurs. La première serait de ne rien faire en attendant que la menace soit certaine. La seconde serait d'imposer aujourd'hui des investissements massifs dans des technologies qui pourraient encore évoluer. La bonne réponse se situe entre les deux[NB]: préparer maintenant, migrer progressivement et adapter les exigences sur le plan des risques.
-Permettez-moi de revenir encore quelques instants sur l'avis du Conseil fédéral. Il reconnaît l'importance du sujet et je l'en remercie, mais il rejette le point relatif au soutien aux cantons, aux PME, aux entreprises et aux hautes écoles au motif que certaines mesures dépasseraient les compétences actuelles de la Confédération. Je me rallie à sa proposition et ne conteste pas le rejet de la lettre i. Je souhaite néanmoins, pour la clarté des délibérations et la mise en oeuvre à venir, préciser l'esprit de cette lettre i. Mon intention n'a jamais été de créer une compétence fédérale nouvelle ni de transférer à la Confédération une responsabilité qui incombe aux cantons, aux entreprises et aux hautes écoles en matière de cybersécurité, car la responsabilité individuelle de chaque acteur demeure entière. Sur ce point, je partage entièrement l'analyse du Conseil fédéral.
+Permettez-moi de revenir encore quelques instants sur l'avis du Conseil fédéral. Il reconnaît l'importance du sujet et je l'en remercie, mais il rejette le point relatif au soutien aux cantons, aux PME, aux entreprises et aux hautes écoles au motif que certaines mesures dépasseraient les compétences actuelles de la Confédération. Je me rallie à sa proposition et ne conteste pas le rejet de la lettre[NB]i. Je souhaite néanmoins, pour la clarté des délibérations et la mise en oeuvre à venir, préciser l'esprit de cette lettre[NB]i. Mon intention n'a jamais été de créer une compétence fédérale nouvelle ni de transférer à la Confédération une responsabilité qui incombe aux cantons, aux entreprises et aux hautes écoles en matière de cybersécurité, car la responsabilité individuelle de chaque acteur demeure entière. Sur ce point, je partage entièrement l'analyse du Conseil fédéral.
 Ce que visait la lettre i, c'est la coordination et non le soutien financier. Une transition vers la cryptographie post-quantique, conduite en ordre dispersé, sans référentiel commun ni interopérabilité, coûterait beaucoup plus cher à tous et affaiblirait la sécurité de l'ensemble. Je prends donc acte du fait que le Conseil fédéral, dans le cadre de ses compétences, assurera cette coordination, avec la mise à disposition de lignes directrices, de modèles d'inventaire, de tests d'interopérabilité et de retours d'expériences utiles aux cantons et à l'économie. Je forme le voeu que le rapport biennal, prévu à la lettre c, rende compte de la manière dont cette coordination est assurée afin que le Parlement puisse en suivre les effets.
 En résumé et pour conclure, la cryptographie post-quantique n'est peut-être pas encore une urgence visible pour la population. Mais, précisément parce que la transition prendra du temps, il est nécessaire d'agir aujourd'hui avant que cela ne devienne une urgence.
 Je vous invite donc à soutenir ma motion sans la lettre i, comme le demande le Conseil fédéral, et je vous en remercie.
@@ -273,14 +273,14 @@
   <si>
     <t xml:space="preserve">Je voudrais vous parler de Pierre.
 Pierre vit depuis plusieurs années dans une institution, dans le canton du Jura. Sa soeur Jacqueline habite dans un autre canton. Elle lui rend visite régulièrement, l'accompagne dans ses démarches et organise son quotidien avec lui. Depuis la mort de leurs parents, elle est son seul lien familial. Pierre voudrait se rapprocher d'elle, vivre à côté de sa soeur, comme n'importe qui d'entre nous voudrait vivre près des siens. Sa demande a été refusée, pas parce que le projet n'est pas réaliste ni parce qu'il ne correspond pas à ses besoins, mais parce qu'un changement de canton coûterait plus cher aux autorités. Pierre ne demande pas un privilège. Il demande simplement de pouvoir choisir où il vit - ce que la plupart d'entre nous n'imaginent même pas devoir demander.
-Autre situation vécue : en arrivant au Palais fédéral cet après-midi, j'ai appris que pendant que nous débattons ici de l'inclusion, des personnes en fauteuil roulant ont été empêchées d'accéder aux tribunes et doivent suivre nos débats depuis la Galerie des Alpes. Des personnes aveugles ont, elles aussi, dû insister pour pouvoir entrer avec leur chien d'assistance. Ce n'est pas un détail logistique. Ce sont précisément ces barrières qui excluent encore les personnes en situation de handicap des débats qui les concernent directement. On parle d'elles ici, mais certaines ne peuvent même pas assister à ce débat comme les autres. Aujourd'hui, certaines d'entre elles sont littéralement tenues à l'écart du débat sur leurs propres droits.
-Ce sont ces réalités que vivent, à des degrés divers, les personnes en situation de handicap dans notre pays : un choix de vie sans cesse mis en balance avec une ligne budgétaire notamment. Le lieu de vie d'une personne ne devrait pas dépendre de frontières administratives ou de mécanismes de financement.
+Autre situation vécue[NB]: en arrivant au Palais fédéral cet après-midi, j'ai appris que pendant que nous débattons ici de l'inclusion, des personnes en fauteuil roulant ont été empêchées d'accéder aux tribunes et doivent suivre nos débats depuis la Galerie des Alpes. Des personnes aveugles ont, elles aussi, dû insister pour pouvoir entrer avec leur chien d'assistance. Ce n'est pas un détail logistique. Ce sont précisément ces barrières qui excluent encore les personnes en situation de handicap des débats qui les concernent directement. On parle d'elles ici, mais certaines ne peuvent même pas assister à ce débat comme les autres. Aujourd'hui, certaines d'entre elles sont littéralement tenues à l'écart du débat sur leurs propres droits.
+Ce sont ces réalités que vivent, à des degrés divers, les personnes en situation de handicap dans notre pays[NB]: un choix de vie sans cesse mis en balance avec une ligne budgétaire notamment. Le lieu de vie d'une personne ne devrait pas dépendre de frontières administratives ou de mécanismes de financement.
 En 2026, force est de constater que leur accès à des pans entiers de la vie - le logement, le travail, la formation, les loisirs, les transports publics ou encore le débat politique - reste incertain. L'interdiction de la discrimination figure dans notre Constitution depuis 25 ans, mais, contrairement à l'égalité entre femmes et hommes, cette égalité n'a jamais été confiée au législateur comme un mandat clair. Il est temps que cela change.
 Je salue la volonté du Conseil fédéral d'opposer un contre-projet indirect à l'initiative "pour l'égalité des personnes handicapées", ainsi que le travail accompli en commission pour s'en rapprocher. Mais à ce stade, ce contre-projet reste trop timide, et j'espère que nos débats permettront de le renforcer.
-En Suisse, 1,9 million de personnes vivent en situation de handicap - une personne sur cinq. Et contrairement à ce que l'on croit souvent, la plupart ne sont pas nées avec un handicap : il est survenu avec un accident, une maladie, l'âge. Cette réalité ne concerne donc pas seulement "les autres" ; elle peut un jour nous concerner toutes et tous.
+En Suisse, 1,9 million de personnes vivent en situation de handicap - une personne sur cinq. Et contrairement à ce que l'on croit souvent, la plupart ne sont pas nées avec un handicap[NB]: il est survenu avec un accident, une maladie, l'âge. Cette réalité ne concerne donc pas seulement "les autres"[NB]; elle peut un jour nous concerner toutes et tous.
 Le contre-projet reprend des éléments importants de l'initiative - c'est un progrès -, mais reste largement dépourvu de caractère contraignant, pour les cantons comme pour la Confédération. Il ne garantit aucune obligation cantonale d'assurer l'égalité en droit et en fait. Il n'accorde aucun droit nouveau, comme celui de décider de son propre logement ou de son lieu de vie, mais se contente d'un engagement de principe. Enfin, il ne prévoit pour l'heure aucune amélioration générale de l'accès aux prestations d'assistance, quel que soit le type de handicap.
-C'est pourquoi je soutiendrai un contre-projet qui renforce réellement l'autonomie des personnes en situation de handicap. Je recommanderai d'accepter l'initiative pour l'inclusion, parce qu'elle seule garantit ce que le contre-projet ne fait encore que promettre : l'égalité et l'autodétermination.
-Pierre ne demande rien d'extraordinaire. Il demande ce que la Constitution devrait déjà lui garantir : le droit de choisir sa vie. Les personnes en situation de handicap sont des citoyens à part entière. À nous de le traduire enfin dans la loi.
+C'est pourquoi je soutiendrai un contre-projet qui renforce réellement l'autonomie des personnes en situation de handicap. Je recommanderai d'accepter l'initiative pour l'inclusion, parce qu'elle seule garantit ce que le contre-projet ne fait encore que promettre[NB]: l'égalité et l'autodétermination.
+Pierre ne demande rien d'extraordinaire. Il demande ce que la Constitution devrait déjà lui garantir[NB]: le droit de choisir sa vie. Les personnes en situation de handicap sont des citoyens à part entière. À nous de le traduire enfin dans la loi.
 </t>
   </si>
   <si>
@@ -295,7 +295,7 @@
 Pour ce qui est de la divergence à l'article 15bbis alinéa 3, notre conseil proposait de modifier trois éléments par rapport au projet du Conseil fédéral. Premièrement, il souhaitait que les exigences environnementales ne soient plus prises en compte, mais examinées, ce qui introduisait un affaiblissement de l'alinéa. Deuxièmement, il souhaitait introduire les intérêts des propriétaires fonciers dans cet examen. Troisièmement, il souhaitait réduire les distances légales des lignes par rapport aux forêts et aux cours d'eau. Le Conseil national proposait, lui, de maintenir la version du Conseil fédéral.
 Pourquoi vous ai-je proposé d'en rester à cette version par le biais de ma minorité[NB]? Je l'ai fait pour trois raisons. Premièrement, l'expression "prendre en compte" plutôt qu'"examiner" entraîne plutôt des incertitudes, parce qu'examiner n'implique pas forcément que l'on prendra en compte, et, pour les autorités d'application, cette notion "d'examiner les intérêts" n'est pas claire et entraîne plutôt des incertitudes. Deuxièmement, s'agissant des intérêts des propriétaires fonciers, notre conseil a souhaité intégrer l'examen des intérêts des propriétaires fonciers dans la pesée des intérêts. Sur une ligne qui réunirait plusieurs dizaines de propriétaires fonciers, cela serait plutôt un facteur de ralentissement que d'accélération de la procédure s'il fallait véritablement examiner leurs intérêts. Dès lors, la version du Conseil des États n'est pas un facteur d'accélération, ce qui est pourtant l'objectif premier de ce projet de loi.
 Enfin - et peut-être l'élément le plus important -, c'est la réduction des distances légales pour la construction à proximité des forêts et des cours d'eau. La réduction de ces distances - c'est important - est déjà contenue dans une autre loi, à savoir la loi sur les forêts (LFo). Il est déjà possible, en vertu de l'article 17 alinéa 3 LFo, de réduire les distances pour la construction d'infrastructures par rapport aux forêts. Dès lors, il n'est pas nécessaire d'introduire cette mention à l'alinéa 3.
-Le deuxième problème concerne la notion d'examen[NB]: si l'on peut réduire ces distances en examinant, mais sans faire de pesée des intérêts et approfondir les problématiques en place, on pourrait être amené à créer des problèmes de sécurité en construisant de nouvelles lignes. On pense notamment - ce ne sont pas des cas fictifs - à ce qui pourrait arriver en cas d'incendie de forêt s'ils entraient en contact avec les lignes électriques. On pense également aux tempêtes telles qu'on les a connues ces dernières années, qui peuvent déraciner des arbres et faire tomber des branches sur une ligne électrique. Il n'est donc pas souhaitable d'introduire une disposition qui permet, sans grand examen, de réduire les distances des constructions par rapport aux forêts dans la loi en vigueur.
+Le deuxième problème concerne la notion d'examen[NB]: si l'on peut réduire ces distances en examinant, mais sans faire de pesée des intérêts et approfondir les problématiques en place, on pourrait être amené à créer des problèmes de sécurité en construisant de nouvelles lignes. On pense notamment - ce ne sont pas des cas fictifs - à ce qui pourrait arriver en cas d'incendies de forêt s'ils entraient en contact avec les lignes électriques. On pense également aux tempêtes telles qu'on les a connues ces dernières années, qui peuvent déraciner des arbres et faire tomber des branches sur une ligne électrique. Il n'est donc pas souhaitable d'introduire une disposition qui permet, sans grand examen, de réduire les distances des constructions par rapport aux forêts dans la loi en vigueur.
 Dès lors, je vous invite, à l'instar du Conseil fédéral, à suivre ma minorité et à vous rallier au Conseil national pour cet article 15bbis alinéa 3.
 </t>
   </si>
@@ -303,10 +303,10 @@
     <t xml:space="preserve">419872</t>
   </si>
   <si>
-    <t xml:space="preserve">La Commission des transports et des télécommunications de notre conseil propose de ne pas classer ce postulat, contrairement à ce qu'indique, ou plutôt, en complément de ce qu'indique le Conseil fédéral, qui veut peut-être intégrer cela dans son projet "Transports '45". Aujourd'hui, on n'a même pas encore terminé la consultation concernant le projet Transports'45 et on voit la nécessité qu'il y a d'agir dans ce secteur, puisque la semaine passée encore, il y a eu une interruption de trafic très </t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Commission des transports et des télécommunications de notre conseil propose de ne pas classer ce postulat, contrairement à ce qu'indique, ou plutôt, en complément de ce qu'indique le Conseil fédéral, qui veut peut-être intégrer cela dans son projet "Transports '45". Aujourd'hui, on n'a même pas encore terminé la consultation concernant le projet Transports'45 et on voit la nécessité qu'il y a d'agir dans ce secteur, puisque la semaine passée encore, il y a eu une interruption de trafic très importante liée à une insuffisance de l'infrastructure. Il n'y avait pas de redondance pour faire circuler les trains et même l'autoroute était bloquée à cet endroit. Si la commission peut entendre que le Conseil fédéral introduira quelque chose dans son message, aujourd'hui on n'a rien de vraiment concret, raison pour laquelle nous proposons de maintenir ce postulat encore en suspens jusqu'à ce que nous ayons des éléments plus concrets du côté du Conseil fédéral.
+    <t xml:space="preserve">La Commission des transports et des télécommunications de notre conseil propose de ne pas classer ce postulat, contrairement à ce qu'indique, ou plutôt, en complément de ce qu'indique le Conseil fédéral, qui veut peut-être intégrer cela dans son projet "Transports '45". Aujourd'hui, on n'a même pas encore terminé la consultation concernant le projet "Transports'45" et on voit la nécessité qu'il y a d'agir dans ce secteur, puisque la semaine passée encore, il y a eu une interruption de trafic trè</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Commission des transports et des télécommunications de notre conseil propose de ne pas classer ce postulat, contrairement à ce qu'indique, ou plutôt, en complément de ce qu'indique le Conseil fédéral, qui veut peut-être intégrer cela dans son projet "Transports '45". Aujourd'hui, on n'a même pas encore terminé la consultation concernant le projet "Transports'45" et on voit la nécessité qu'il y a d'agir dans ce secteur, puisque la semaine passée encore, il y a eu une interruption de trafic très importante liée à une insuffisance de l'infrastructure. Il n'y avait pas de redondance pour faire circuler les trains et même l'autoroute était bloquée à cet endroit. Si la commission peut entendre que le Conseil fédéral introduira quelque chose dans son message, aujourd'hui on n'a rien de vraiment concret, raison pour laquelle nous proposons de maintenir ce postulat encore en suspens jusqu'à ce que nous ayons des éléments plus concrets du côté du Conseil fédéral.
 </t>
   </si>
   <si>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">420610</t>
   </si>
   <si>
-    <t xml:space="preserve">Comme l'a dit le rapporteur, le soutien à l'initiative populaire dépend un peu de la teneur du contre-projet qui sortira finalement des conseils, dans la mesure où le Conseil national s'est rallié à notre avis s'agissant du programme de certification. C'est un point réellement primordial du contre-projet que les certifications qui sont apportées aux fourrures importées soient établies selon des standards solides et internationaux reconnus. Dans la mesure où les deux points restants ont été rempl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comme l'a dit le rapporteur, le soutien à l'initiative populaire dépend un peu de la teneur du contre-projet qui sortira finalement des conseils, dans la mesure où le Conseil national s'est rallié à notre avis s'agissant du programme de certification. C'est un point réellement primordial du contre-projet que les certifications qui sont apportées aux fourrures importées soient établies selon des standards solides et internationaux reconnus. Dans la mesure où les deux points restants ont été remplis, je retire la proposition de la minorité que je représente. Il n'y a donc plus de divergence sur ce point.
+    <t xml:space="preserve">Comme l'a dit le rapporteur, le soutien à l'initiative populaire dépend un peu de la teneur du contre-projet qui sortira finalement des conseils, dans la mesure où le Conseil national s'est rallié à notre avis s'agissant du programme de certification. C'est un point réellement primordial du contre-projet que les certifications qui sont apportées aux fourrures importées soient établies selon des standards internationaux solides et reconnus. Dans la mesure où les deux points restants ont été résol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme l'a dit le rapporteur, le soutien à l'initiative populaire dépend un peu de la teneur du contre-projet qui sortira finalement des conseils, dans la mesure où le Conseil national s'est rallié à notre avis s'agissant du programme de certification. C'est un point réellement primordial du contre-projet que les certifications qui sont apportées aux fourrures importées soient établies selon des standards internationaux solides et reconnus. Dans la mesure où les deux points restants ont été résolus, je retire la proposition de la minorité que je représente. Il n'y a donc plus de divergence sur ce point.
 </t>
   </si>
   <si>
@@ -656,7 +656,113 @@
   <si>
     <t xml:space="preserve">Ich habe vorhin schon erwähnt, dass die APK-S insgesamt einfach eine politische Würdigung in die Richtung vorgenommen hat, dass es für die aussenpolitische Lösung eben auch innenpolitische Begleitmassnahmen braucht und die Sozialpartnerschaft in diesem Zusammenhang sehr wichtig ist. Arbeitsfrieden und Arbeitsethos - dieses möchte ich auch erwähnen - sind wesentliche Elemente unserer Standortgunst. Das ist ein Standortvorteil der Schweiz; darauf sind wir auch stolz. 
 Es war bei diesem Dossier - um das nochmals zu rekapitulieren - nicht immer so, dass die Sozialpartnerschaft wirklich funktioniert hat. Ich kann mich erinnern: Ich war früher noch teilweise als KDK-Präsident bei den tripartiten Gesprächen dabei, als der Vorgänger von Herrn Maillard, unser ehemaliger Kollege und mein ehemaliger Standeskollege Paul Rechsteiner relativ bzw. ziemlich klar sagte: Ich mache da nicht mehr mit, ich verlasse den Tisch. Sie müssen sich einfach nochmals bewusst sein, wo wir damals waren und wo wir heute sind. 
-Wir haben heute eine Lösung, die in zig Runden verhandelt wurde, wie wir uns haben sagen lassen. Es ist offensichtlich ein mühsamer, aber notwendiger Prozess gewesen. Rechtlich gesehen könnte man einfach vom Ergebnis abweichen. Die APK-S ist aber der Auffassung, dass dies politisch nicht klug wäre; gerade als Ständerat sollten wir das nicht machen. Es ist ein bisschen wie beim Finanzausgleich. Wenn sich die Kantone beim Finanzausgleich verständigen, dann tun wir auch gut daran, das im Parlament nicht zu übersteuern; das kommt nicht gut. Ähnlich ist es auch hier bei der Sozialpartnerschaft. Machdem wir eine Lösung erzielen konnten bzw. die Sozialpartner eine Lösung erzielen konnten, sollte man dieses Ergebnis nicht einfach torpedieren. Vor diesem Hintergrund haben wir aus einer Gesamtwürdigung dieses ganzen Prozesses entschieden, den Bundesrat zu unterstützen. Ich bitte Sie, dies ebenfalls zu tun. 
+Wir haben heute eine Lösung, die in zig Runden verhandelt wurde, wie wir uns haben sagen lassen. Es ist offensichtlich ein mühsamer, aber notwendiger Prozess gewesen. Rechtlich gesehen könnte man einfach vom Ergebnis abweichen. Die APK-S ist aber der Auffassung, dass dies politisch nicht klug wäre; gerade als Ständerat sollten wir das nicht machen. Es ist ein bisschen wie beim Finanzausgleich. Wenn sich die Kantone beim Finanzausgleich verständigen, dann tun wir auch gut daran, das im Parlament nicht zu übersteuern; das kommt nicht gut. Ähnlich ist es auch hier bei der Sozialpartnerschaft. Nachdem wir eine Lösung erzielen konnten bzw. die Sozialpartner eine Lösung erzielen konnten, sollte man dieses Ergebnis nicht einfach torpedieren. Vor diesem Hintergrund haben wir aus einer Gesamtwürdigung dieses ganzen Prozesses entschieden, den Bundesrat zu unterstützen. Ich bitte Sie, dies ebenfalls zu tun. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keller-Sutter Karin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich gehe zuerst auf die Motionen der Fraktion der Schweizerischen Volkspartei ein, danach auf die Motion Bürgin Yvonne und dann auf die Motionen der Sozialdemokratischen Fraktion.
+Was wollen die beiden Motionen der SVP? Die beiden Motionen verlangen, dass zusätzliche Rüstungsausgaben aus dem ordentlichen Haushalt bestritten werden. Die Motion 26.3721 bezieht sich dabei explizit nur auf die zusätzlichen Armeeausgaben, die nötig sind, um bis 2032 das 1-Prozent-BIP-Ziel zu erreichen. Der Bundesrat </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich gehe zuerst auf die Motionen der Fraktion der Schweizerischen Volkspartei ein, danach auf die Motion Bürgin Yvonne und dann auf die Motionen der Sozialdemokratischen Fraktion.
+Was wollen die beiden Motionen der SVP? Die beiden Motionen verlangen, dass zusätzliche Rüstungsausgaben aus dem ordentlichen Haushalt bestritten werden. Die Motion 26.3721 bezieht sich dabei explizit nur auf die zusätzlichen Armeeausgaben, die nötig sind, um bis 2032 das 1-Prozent-BIP-Ziel zu erreichen. Der Bundesrat erachtet das Ziel dieser Motion als bereits erfüllt. Gemäss aktueller Planung kann der Wachstumspfad der Armeeausgaben auf 1 Prozent des BIP bis 2032 dank dem Entlastungspaket, das nächstes Jahr 1,4 Milliarden Franken und in den Folgejahren 2 Milliarden Franken bringt, und dank den prognostizierten Mehreinnahmen aus dem allgemeinen Bundeshaushalt finanziert werden. Weitere Sparmassnahmen sind aber nicht ausgeschlossen. Insbesondere in den Jahren 2031 und 2032 belastet der Anstieg der Armeeausgaben den Bundeshaushalt stark. Der Bundesrat wird dem Parlament die Entwicklung der Armeeausgaben in diesem Zeitraum mit dem Zahlungsrahmen der Armee für die Jahre 2029-2032 beantragen. Der Bundesrat - ich habe es bereits erwähnt - sieht die Motion entsprechend als bereits erfüllt an. Im Ständerat wurde die gleichlautende Motion Salzmann 26.3744 letzte Woche zurückgezogen.
+Ich komme zur Motion 26.3722, die sich hingegen auf sämtliche Rüstungsbeschaffungen bezieht. Mit der Motion soll der dafür notwendige Beitrag aus den allgemeinen Bundesmitteln für den Zeitraum 2028-2037 zweckgebunden werden. Der Bundesrat muss gemäss Motion hierfür Massnahmen in drei Bereichen prüfen und ergreifen, nämlich im Eigenbereich, bei den mehrjährigen Finanzbeschlüssen sowie bei den gebundenen Ausgaben.
+Der Bundesrat bittet Sie, diese Motion abzulehnen. Er teilt zwar die Einschätzung, dass die Ausgaben der Armee unter Einhaltung der Schuldenbremse und aus dem ordentlichen Haushalt finanziert werden müssen. Er schlägt dem Parlament zu diesem Zweck aber ein anderes Finanzierungskonzept vor. Wie bereits erwähnt, will der Bundesrat den Wachstumspfad der Armeeausgaben auf 1 Prozent des BIP bis 2032 aus dem allgemeinen Bundeshaushalt finanzieren. Zur Deckung des darüberhinausgehenden Mehrbedarfes von rund 24 Milliarden Franken für die Beschaffung von Rüstungsgütern hat Ihnen der Bundesrat im August die Botschaft über die Finanzierung von Rüstungsausgaben der Armee durch eine Erhöhung der Mehrwertsteuer und die Schaffung eines Rüstungsfonds vorgelegt. Darin hat er Ihnen eine auf zwölf Jahre befristete Erhöhung der Mehrwertsteuer um 0,5 Prozentpunkte unterbreitet. Der Ständerat hat diese Vorlage am 21. September behandelt und in wichtigen Teilen abgeändert. Sie ist nun im Nationalrat hängig, und Sie werden Gelegenheit haben, diese nach Ihrem Überzeugen, nach Ihrem Gusto auszugestalten.
+Darüber hinaus ist der Bundesrat bereit, für die Beschleunigung zentraler Investitionen in die Sicherheit freie Mittel im Haushalt einzusetzen. So hat er Ende August beschlossen, dem Parlament für das Jahr 2026 einen Nachtragskredit von 970 Millionen Franken zu beantragen, um Liefertermine für die Beschaffung zur Luftverteidigung, Bodluv kurzer und mittlerer Reichweite, zu sichern. Sollten in künftigen Budgets weitere Sparmassnahmen nötig sein, erachtet der Bundesrat die in der Motion genannte Priorisierung - Eigenbereich und mehrjährige Finanzbeschlüsse - zwar grundsätzlich als geeignet, um den notwendigen Handlungsspielraum sicherzustellen; allerdings ist es dafür noch zu früh. Der Bundesrat wird Ihnen bei Bedarf mögliche Massnahmen zum gegebenen Zeitpunkt und unter Berücksichtigung der konkreten Umstände vorlegen. Auch die Flexibilisierung gebundener Ausgaben ist ein berechtigtes Anliegen. Sie hilft aber nur bei vorübergehenden Engpässen und dient nicht der dauerhaften Sanierung des Bundeshaushaltes.
+Ich möchte daran erinnern, dass die vom Motionär genannten Flexibilisierungsmassnahmen primär gebundene Beiträge an Sozialversicherungen, an Investitionen im Verkehrsbereich und Verbundaufgaben mit den Kantonen, beispielsweise den Anteil der Kantone an den Einnahmen der direkten Bundessteuer und den Finanzausgleich, betreffen. Im Ständerat wurde die gleichlautende Motion Germann 26.3748 letzte Woche zurückgezogen. 
+Nun komme ich zu den beiden weiteren Vorstössen, zur Motion Bürgin Yvonne und zur Motion der SP-Fraktion. Diese Motionen wollen bei der Gewinnausschüttung der Schweizerischen Nationalbank ansetzen. Die Motion Bürgin Yvonne will die Einnahmen aus der Gewinnausschüttung der SNB für die Dauer von zehn Jahren vollumfänglich für zusätzliche Ausgaben zugunsten der Landesverteidigung zweckbinden. Wie Sie wissen, wird der Grundbetrag der Gewinnausschüttung, das sind aktuell 667 Millionen Franken, ordentlich verbucht, während die Zusatzausschüttung, im Moment rund 333 Millionen Franken, ausserordentlich verbucht wird. Der ausserordentliche Teil wird für den Abbau der Corona-Schulden verwendet. Diese sind auf dem Amortisationskonto der Schuldenbremse festgehalten. Damit es hier nicht zu einer Verzögerung kommt, soll der fehlende Betrag für den Schuldenabbau gemäss der Motion durch einen Übertrag vom Ausgleichskonto ausgeglichen werden. 
+Die Motion der SP-Fraktion möchte Gesetz und Verfassung so anpassen, dass die SNB künftig eine Eigenkapitalquote in einer Bandbreite von 10 bis 15 Prozent anstrebt. Da die Eigenkapitalquote der SNB aktuell bei gut 18 Prozent liegt, müsste sie kein weiteres Eigenkapital mehr aufbauen und könnte stattdessen jährlich mehr Gewinn an Bund und Kantone ausschütten. Den die Obergrenze von 15 Prozent übersteigenden Eigenkapitalanteil soll die SNB gemäss Motion als einmalige Sonderausschüttung an den Bund ausschütten. Die zusätzlichen Mittel des Bundes sollen in einem verschuldungsfähigen Fonds zur Finanzierung einer umfassenden Sicherheitspolitik mit einer Laufzeit von mindestens zehn Jahren eingelegt werden. 
+Ich bitte Sie, die Motion Bürgin Yvonne abzulehnen, dies aus zwei Gründen. 1. Die Gewinnausschüttungen der SNB sind nicht geeignet für eine zusätzliche Finanzierung der Landesverteidigung. Da die Jahresergebnisse der SNB volatil sind, können die effektiven Ausschüttungen stark schwanken. Unter Umständen fallen die Gewinnausschüttungen ganz aus, wie dies zuletzt in den Jahren 2023 und 2024 der Fall gewesen ist, womit die Ausschüttung, die ordentlich verbucht wird, dann natürlich im Bundeshaushalt fehlen würde. Das war ja die Frage, die auch gestellt wurde. In der Regel wird rund eine Milliarde ausgeschüttet, ein Drittel ausserordentlich und eben zwei Drittel ordentlich. Das müsste einfach im ordentlichen Haushalt dann eingespart werden. 2. Bundesrat und Parlament haben sich im Jahr 2022 gegen eine Verrechnung der Kontrollstatistiken und für einen vollständigen Abbau der Corona-Schulden ausgesprochen, dies nicht zuletzt, weil aufgrund der Corona-Ausgaben ein hoher Schuldenaufbau resultierte. Wir haben immer noch etwa 26 Milliarden Schulden. Mit der Motion blieben die Corona-Schulden im Umfang der Verrechnung bestehen und würden im Gegensatz zur aktuellen Lösung nicht weiter abgebaut.
+Noch zur Motion der SP-Fraktion. Ich bitte Sie, auch diese abzulehnen. Die von den Motionären erwarteten Mehrausschüttungen klingen zwar verlockend, sie hängen jedoch massgeblich davon ab, ob die Eigenkapitalquote über der Zielquote liegt. Dies ist derzeit der Fall, kann sich jedoch schnell ins Gegenteil verkehren. Sinkt die Eigenkapitalquote etwa im Fall eines hohen Jahresverlustes der SNB unter 10 Prozent, müsste sie zuerst wieder aufgebaut werden, bevor wieder Gewinne an Bund und Kantone ausgeschüttet werden könnten. Ob die Motion, wie behauptet, zu stabilen Mehrausschüttungen führen würde, ist somit fraglich. Davon abgesehen haben fixierte Eigenkapitalquoten bzw. Bandbreiten grundsätzlich den Nachteil, dass sie zu wenig flexibel sind, um die Bilanzrisiken der SNB angemessen abzudecken.
+Je nach Entwicklung der Risiken könnte sowohl eine höhere als auch eine tiefere Quote erforderlich sein. Die Fixierung einer Eigenkapitalquote bei 10 bis 15 Prozent ist daher abzulehnen. Darüber soll die einmalige Sonderausschüttung nur an den Bund gehen. Dies würde den in der Verfassung festgelegten Verteilschlüssel verletzen, wonach der Gewinn der SNB zu mindestens zwei Dritteln an die Kantone ausgeschüttet wird. Zwar sieht die Motion hier eine Übergangsbestimmung in der Verfassung vor, es ist indes davon auszugehen, dass die Kantone eine derartige Verletzung ihrer Ansprüche nicht hinnehmen würden, zumal sie Eigner der Nationalbank sind.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gantenbein Laura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Bundesrat, ich war diesen Sommer in der ganzen Schweiz unterwegs, in allen Sprachregionen. Überall war es heiss, aber am meisten beeindruckt hat mich bei uns der Jurasüdfuss-Wald. Werden Sie in Zukunft zusätzliche Massnahmen vorsehen, die den Schutzwald im Jura klimaresilienter machen?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le groupe UDC salue globalement les investissements prévus dans le message sur les immeubles civils 2026.
+Avec près de 774 millions de francs de crédits d'engagement prévus dans le message initial, nous assistons à un rattrapage après plusieurs années durant lesquelles les investissements dans nos immeubles ont été insuffisants. Le retard accumulé dans l'entretien est considérable : il avoisine le milliard de francs. Cette situation nous montre une chose très simple : lorsque nous repoussons l'e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le groupe UDC salue globalement les investissements prévus dans le message sur les immeubles civils 2026.
+Avec près de 774 millions de francs de crédits d'engagement prévus dans le message initial, nous assistons à un rattrapage après plusieurs années durant lesquelles les investissements dans nos immeubles ont été insuffisants. Le retard accumulé dans l'entretien est considérable : il avoisine le milliard de francs. Cette situation nous montre une chose très simple : lorsque nous repoussons l'entretien, la facture finit par être salée. Lorsque nous n'entretenons pas suffisamment nos bâtiments, nous risquons également de ne plus pouvoir les utiliser correctement. La rénovation de la Bibliothèque nationale en est un exemple particulièrement parlant. Lors de notre visite en commission, nous avons pu constater directement l'état préoccupant du bâtiment. Certains locaux ont même dû être abandonnés en raison d'un danger d'effondrement.
+Nous devons tirer les leçons de cette situation. Oui, il faut investir. Oui, il faut rattraper le retard. Oui, il faut préserver la valeur de nos immeubles. Pour cela, nous devons fixer des priorités. Chaque franc investi doit répondre à un besoin réel. Nous devons nous demander si chaque projet est véritablement nécessaire.
+Dans ce contexte, il faut également avoir le courage de questionner certaines contraintes, notamment liées à la protection du patrimoine. Nous devons naturellement respecter notre patrimoine, mais nous devons aussi nous demander si, dans chaque situation, il est raisonnable de consacrer des sommes astronomiques au maintien de structures existantes lorsque celles-ci ne répondent plus aux exigences fonctionnelles. Souvent, il serait plus rationnel de reconstruire un bâtiment, tout en conservant son caractère architectural. Le patrimoine ne doit pas devenir un prétexte pour conserver n'importe quoi à n'importe quel prix. Pour cela, nous avons le musée du Ballenberg. Entretenir d'abord, investir là où c'est nécessaire et utiliser chaque franc de l'argent public de manière responsable. C'est précisément cela qui me conduit maintenant à défendre ma minorité.
+À l'article 1 lettre i, on nous propose de financer la création du Centre de visites et d'information du Parlement. Sur le principe, personne ne peut être opposé à ce que la population puisse mieux comprendre nos institutions, notre Parlement et notre démocratie. Ma question est de savoir si ce projet-là, à cet endroit-là, est opportun. La réponse est non. Nous sommes en passe d'investir plusieurs dizaines de millions de francs dans l'aménagement d'un bâtiment dont nous ne sommes pas propriétaires et dont nous ne maîtrisons pas l'avenir. Le projet prévoit 24,6 millions de francs d'investissement pour l'architecture, la scénographie et la mise en service.
+À cela s'ajoute un loyer annuel qui se chiffre à 1,9 million de francs. Le centre entraînera environ 6,5 millions supplémentaires de charges d'exploitation chaque année pour le personnel et le loyer, alors que nous devrions rattraper un retard d'entretien considérable des immeubles de la Confédération. Où sont donc nos priorités ?
+Enfin, au-delà de la question financière, une question est beaucoup plus fondamentale : qu'est-ce qu'un visiteur vient chercher lorsqu'il vient à Berne pour visiter le Parlement ? Il ne vient pas simplement dans un local pour regarder une exposition et obtenir un exposé théorique sur la démocratie suisse. Il veut entrer dans le Palais fédéral, passer sous la coupole, voir la salle du Conseil national et voir la salle du Conseil des États. Si cela est possible, il veut assister aux débats. Il veut voir les parlementaires en action - simplement être au coeur de la démocratie suisse. C'est précisément cela qui fait la valeur d'une visite au Parlement. Les auteurs du message reconnaissent, d'ailleurs, que la visite du Palais du Parlement et le fait de vivre l'activité parlementaire de l'intérieur resteront toujours des éléments marquants pour les visiteurs. 
+Le centre projeté est présenté comme une offre complémentaire. D'ailleurs, cette nouvelle infrastructure offrira-t-elle réellement aux visiteurs ce qu'ils viennent chercher à Berne ? À mon sens, une visite du Parlement ne peut pas se faire au rabais. Une visite du Parlement, c'est sous la coupole.
+Ein Besuch von Bundesbern - das ist hier, im Herzen des Parlamentes! Ich will lieber weiterhin eine leicht beschränkte Zahl Besucher sehen, die dieses Haus mit leuchtenden Augen verlassen und dieses Erlebnis mit Begeisterung hinaustragen. Das Projekt Besuchs- und Informationszentrum ist nichts anderes als ein Abspeisen einer Masse von Besuchern, die am Ende frustriert am Bundeshaus vorbeigehen wird. Auch wir wollen Besucher empfangen, aber bitte - die lebende Demokratie erlebt man hier, unter dieser Kuppel, und nicht im ehemaligen Empfangsraum einer gescheiterten Grossbank.
+Ich bitte Sie, dafür der Minderheit I (Stettler Thomas) zu folgen und somit Artikel 1 Buchstabe i des Entwurfs 1 zum Bundesbeschluss über die zivilen Immobilien des Bundes für das Jahr 2026 zu streichen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le message sur les immeubles civils 2026 ne suscite qu'un seul débat, celui du Centre de visites et d'information du Parlement, à l'article 1 lettre i. Le groupe socialiste soutiendra le projet initial, y compris pour cet objet de 44,2 millions de francs. Ce montant peut impressionner. Il faut pourtant regarder ce qu'il finance : un lieu pour comprendre comment fonctionne notre démocratie. Une démocratie ne se maintient pas toute seule. Elle vit parce que des citoyennes et des citoyens savent co</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le message sur les immeubles civils 2026 ne suscite qu'un seul débat, celui du Centre de visites et d'information du Parlement, à l'article 1 lettre i. Le groupe socialiste soutiendra le projet initial, y compris pour cet objet de 44,2 millions de francs. Ce montant peut impressionner. Il faut pourtant regarder ce qu'il finance : un lieu pour comprendre comment fonctionne notre démocratie. Une démocratie ne se maintient pas toute seule. Elle vit parce que des citoyennes et des citoyens savent comment elle fonctionne, comment se prend une décision, à quoi sert un référendum. Ce savoir ne va pas de soi : il se transmet. Le Palais fédéral est un bâtiment magnifique, mais il n'explique pas à lui seul ce qu'il abrite. La solidité de nos institutions ne tient pas à ses pierres. Elle tient à la confiance de la population et à la connaissance qu'elle a de ses droits et de ses responsabilités. Un centre de visites répond à ce besoin. Il permet aux classes, aux familles, aux personnes venues de toutes les régions du pays et de l'étranger de découvrir l'histoire de notre démocratie et la manière dont elle s'exerce aujourd'hui. Il s'adresse en particulier aux jeunes qui voteront et s'engageront demain. Ce projet peut paraître coûteux, mais il s'agit d'une opportunité unique, un lieu situé sur la Place fédérale elle-même, à proximité immédiate du Parlement. Renvoyer le dossier, c'est prendre le risque de perdre cette occasion, sans garantie de retrouver ailleurs des conditions aussi favorables. Investir dans la compréhension de nos institutions, c'est investir dans leur avenir.
+Pour ces raisons, le groupe socialiste soutiendra le projet initial, avec le Centre de visites et d'information du Parlement, et vous invite à en faire de même.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frau Rumy, im Wissen, dass das Verständnis für Demokratie auch in einem Kantonsparlament gefördert werden kann und diese Möglichkeiten weitgehend ungenutzt sind - und dass die Bundesfinanzen nicht alle Wünsche erfüllen können: Finden Sie nicht, dass 44 Millionen Franken für ein Nice-to-have-Projekt ein Luxus sind?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michel Matthias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich bitte Sie namens der Kommissionsmehrheit - es ist die gleiche wie vorher -, die Minderheit II (Stark) abzulehnen. Dieses Ergebnis, also die Gleichbehandlung, wurde den Kantonen quasi aufoktroyiert, verhandelt hat es aber der Bund. Wer befiehlt, zahlt - Sie kennen dieses Thema aus dem Finanzausgleich. Die Kantone haben das Ergebnis zwar akzeptiert, aber irgendwie zähneknirschend, weil sie das Gesamtpaket gutheissen. Gleichzeitig mit diesem Akzept haben sie gefordert, dass der Bund sich an den</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich bitte Sie namens der Kommissionsmehrheit - es ist die gleiche wie vorher -, die Minderheit II (Stark) abzulehnen. Dieses Ergebnis, also die Gleichbehandlung, wurde den Kantonen quasi aufoktroyiert, verhandelt hat es aber der Bund. Wer befiehlt, zahlt - Sie kennen dieses Thema aus dem Finanzausgleich. Die Kantone haben das Ergebnis zwar akzeptiert, aber irgendwie zähneknirschend, weil sie das Gesamtpaket gutheissen. Gleichzeitig mit diesem Akzept haben sie gefordert, dass der Bund sich an den Kosten, die infolge der Mindereinnahmen entstehen, beteiligt. Ich glaube, es wurde eine gute Lösung gefunden: Befristet auf vier Jahre beteiligt sich der Bund nun daran - nachher aber nicht mehr. Nachher sind die Kantone auf sich gestellt.
+Ich bitte Sie, diesen innerstaatlichen, föderalen Kompromiss zu akzeptieren und die Minderheit II abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans le cadre du dernier message FRI, en septembre 2024, nous avions décidé de tripler le montant des taxes d'études pour les étudiantes et étudiants étrangers. Jusque-là, cette fixation du montant des taxes ressortait du Conseil des EPF, qui avait toujours renoncé à discriminer les personnes étrangères en la matière. Ce triplement des taxes pour les étudiants de l'Union européenne n'étant plus compatible avec la libre circulation des personnes en vertu du principe de non-discrimination - c'est </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans le cadre du dernier message FRI, en septembre 2024, nous avions décidé de tripler le montant des taxes d'études pour les étudiantes et étudiants étrangers. Jusque-là, cette fixation du montant des taxes ressortait du Conseil des EPF, qui avait toujours renoncé à discriminer les personnes étrangères en la matière. Ce triplement des taxes pour les étudiants de l'Union européenne n'étant plus compatible avec la libre circulation des personnes en vertu du principe de non-discrimination - c'est l'article 2 de l'accord en question -, il a donc été supprimé dans le cadre de la révision de cet accord. C'est pourquoi le Conseil fédéral a réintroduit dans la loi sur les EPF le principe selon lequel le montant des taxes d'études est identique pour les étudiants et étudiantes suisses et pour les ressortissants de l'Union européenne, tout en ménageant la possibilité de fixer des taxes plus élevées pour les étudiants d'États extérieurs.
+La majorité de la commission, dont je fais partie, a souhaité aller plus loin que le Conseil fédéral sur deux points. D'une part, en étendant explicitement le principe de non-discrimination aux étudiants et étudiantes de l'AELE afin de garantir qu'ils ne soient pas assimilés à des ressortissants d'États tiers qui restent soumis au triplement des taxes selon la proposition de la majorité. Cette disposition garantit, par exemple, qu'une étudiante du Liechtenstein ne paie pas à l'avenir trois fois plus que son homologue autrichienne pour étudier à l'EPFZ. Ce complément entre dans le champ de l'application de la Convention instituant l'AELE, comme l'a dit Mme Isabelle Chassot, et non de l'Accord sur la libre circulation des personnes, mais il est compatible avec la convention en vigueur qui n'impose pas aux parties le principe de l'égalité de traitement. Nous pouvons donc anticiper dès maintenant le futur écart qui s'appliquerait entre étudiants européens de l'Union européenne et étudiants européens hors Union européenne et étendre donc les dispositions de mise en oeuvre à l'espace AELE. Une mise à jour de l'annexe K de la convention serait effectivement nécessaire pour introduire la réciprocité de ce traitement, mais il est important de relever que, dans les faits, l'Islande, la Norvège et le Liechtenstein appliquent déjà volontairement les mêmes tarifs aux étudiants suisses qu'aux étudiants nationaux et de l'Union européenne.
+D'autre part, la majorité de la commission a souhaité réintroduire l'obligation du triplement des taxes qui avait été décidé il y a deux ans dans le cadre du message FRI et qui sera désormais limité aux étudiants et étudiantes hors Union européenne. La commission a en effet regretté que le Conseil fédéral soit revenu en arrière par rapport à cette décision. Il n'y a pas de minorité sur ce point, dans la mesure où cette décision, bien que nous l'ayons combattue à l'époque, en appelant de nos voeux l'application de taxes d'études identiques pour l'ensemble du corps estudiantin, a été prise et actée par le Parlement. Rien n'empêche toutefois, à quiconque estime que ce triplement des taxes et cette discrimination des étudiants d'États extraeuropéens, notamment au regard du coût de la vie extrêmement élevé dans notre pays, est injustifié, de soutenir la version du Conseil fédéral.
+Enfin, j'ajoute encore un mot sur la minorité II (Stark). Je suis ravie d'entendre que vous ne souhaitez pas créer des classes différentes parmi les étudiants étrangers et que vous militez pour ne pas différencier entre elles les personnes étrangères et pour appliquer le même traitement à tous. Cela étant, avec votre proposition, vous le savez, nous entrons en contradiction avec les révisions de l'Accord sur la libre circulation des personnes que les négociateurs ont adoptées avec l'Union européenne. Cela créerait une divergence problématique.
+Dès lors, je vous invite à ne pas créer un problème là où il ne doit pas y en avoir. Cette situation va se faire à la satisfaction de tous et toutes. Je vous invite à suivre la majorité de la commission.
 </t>
   </si>
 </sst>
@@ -711,8 +817,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I33" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I40" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I40"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1967,6 +2073,207 @@
         <v>137</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>138</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34"/>
+      <c r="F34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" t="s">
+        <v>140</v>
+      </c>
+      <c r="I34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" t="s">
+        <v>130</v>
+      </c>
+      <c r="F35" t="s">
+        <v>144</v>
+      </c>
+      <c r="G35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" t="s">
+        <v>145</v>
+      </c>
+      <c r="I35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>146</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" t="s">
+        <v>147</v>
+      </c>
+      <c r="I36" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>149</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" t="s">
+        <v>12</v>
+      </c>
+      <c r="H37" t="s">
+        <v>150</v>
+      </c>
+      <c r="I37" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" t="s">
+        <v>12</v>
+      </c>
+      <c r="H38" t="s">
+        <v>153</v>
+      </c>
+      <c r="I38" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" t="s">
+        <v>155</v>
+      </c>
+      <c r="E39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" t="s">
+        <v>156</v>
+      </c>
+      <c r="G39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" t="s">
+        <v>157</v>
+      </c>
+      <c r="I39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" t="s">
+        <v>160</v>
+      </c>
+      <c r="I40" t="s">
+        <v>161</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -747,8 +747,8 @@
     <t xml:space="preserve">Ich bitte Sie namens der Kommissionsmehrheit - es ist die gleiche wie vorher -, die Minderheit II (Stark) abzulehnen. Dieses Ergebnis, also die Gleichbehandlung, wurde den Kantonen quasi aufoktroyiert, verhandelt hat es aber der Bund. Wer befiehlt, zahlt - Sie kennen dieses Thema aus dem Finanzausgleich. Die Kantone haben das Ergebnis zwar akzeptiert, aber irgendwie zähneknirschend, weil sie das Gesamtpaket gutheissen. Gleichzeitig mit diesem Akzept haben sie gefordert, dass der Bund sich an den</t>
   </si>
   <si>
-    <t xml:space="preserve">Ich bitte Sie namens der Kommissionsmehrheit - es ist die gleiche wie vorher -, die Minderheit II (Stark) abzulehnen. Dieses Ergebnis, also die Gleichbehandlung, wurde den Kantonen quasi aufoktroyiert, verhandelt hat es aber der Bund. Wer befiehlt, zahlt - Sie kennen dieses Thema aus dem Finanzausgleich. Die Kantone haben das Ergebnis zwar akzeptiert, aber irgendwie zähneknirschend, weil sie das Gesamtpaket gutheissen. Gleichzeitig mit diesem Akzept haben sie gefordert, dass der Bund sich an den Kosten, die infolge der Mindereinnahmen entstehen, beteiligt. Ich glaube, es wurde eine gute Lösung gefunden: Befristet auf vier Jahre beteiligt sich der Bund nun daran - nachher aber nicht mehr. Nachher sind die Kantone auf sich gestellt.
-Ich bitte Sie, diesen innerstaatlichen, föderalen Kompromiss zu akzeptieren und die Minderheit II abzulehnen.
+    <t xml:space="preserve">Ich bitte Sie namens der Kommissionsmehrheit - es ist die gleiche wie vorher -, die Minderheit II (Stark) abzulehnen. Dieses Ergebnis, also die Gleichbehandlung, wurde den Kantonen quasi aufoktroyiert, verhandelt hat es aber der Bund. Wer befiehlt, zahlt - Sie kennen dieses Thema aus dem Finanzausgleich. Die Kantone haben das Ergebnis zwar akzeptiert, aber irgendwie zähneknirschend, weil sie das Gesamtpaket gutheissen. Gleichzeitig mit diesem Akzept haben sie gefordert, dass der Bund sich an den Kosten beteiligt, die infolge der Mindereinnahmen entstehen. Ich glaube, es wurde eine gute Lösung gefunden: Befristet auf vier Jahre beteiligt sich der Bund nun daran - nachher aber nicht mehr. Nachher sind die Kantone auf sich gestellt.
+Ich bitte Sie, diesen innerstaatlichen, föderalen Kompromiss zu akzeptieren und den Antrag der Minderheit II abzulehnen.
 </t>
   </si>
   <si>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -104,12 +104,13 @@
     <t xml:space="preserve">DE</t>
   </si>
   <si>
-    <t xml:space="preserve">Die SVP-Fraktion wird auf die Vorlage eintreten. Es geht um unsere Unternehmen, es geht um unsere Arbeitsplätze, es geht um Zölle; es geht nicht darum, die Welt zu retten. Mercosur umfasst 270 Millionen Menschen. Die Schweiz exportiert bereits heute Waren im Wert von mehr als 4 Milliarden Franken jährlich in die Mercosur-Länder. Mit dem Abkommen sollen rund 96 Prozent unserer Ausfuhren nach Ablauf der vorgesehenen Übergangsfrist zollfrei werden. Das eröffnet unseren Unternehmen zusätzliche Markt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die SVP-Fraktion wird auf die Vorlage eintreten. Es geht um unsere Unternehmen, es geht um unsere Arbeitsplätze, es geht um Zölle; es geht nicht darum, die Welt zu retten. Mercosur umfasst 270 Millionen Menschen. Die Schweiz exportiert bereits heute Waren im Wert von mehr als 4 Milliarden Franken jährlich in die Mercosur-Länder. Mit dem Abkommen sollen rund 96 Prozent unserer Ausfuhren nach Ablauf der vorgesehenen Übergangsfrist zollfrei werden. Das eröffnet unseren Unternehmen zusätzliche Marktchancen und ermöglicht Zollersparnisse von über 155 Millionen Franken pro Jahr.
-Gerade für ein kleines, international ausgerichtetes Land wie die Schweiz ist der Zugang zu ausländischen Märkten von zentraler Bedeutung. Wir können es uns nicht leisten, uns in wichtigen Märkten ins Abseits zu manövrieren, während andere Wirtschaftsräume ihre Beziehungen ausbauen. Natürlich gibt es berechtigte Fragen zur Landwirtschaft; diese müssen wir sehr ernst nehmen. Die SVP-Fraktion nimmt sie ernst. Entscheidend ist für uns deshalb die Frage, wie wir mit den möglichen Auswirkungen auf die Landwirtschaft umgehen. Hier liegt gegenüber der ursprünglichen Vorlage inzwischen eine Lösung auf dem Tisch. Der Ständerat hat insgesamt 517 Millionen Franken für flankierende Massnahmen beschlossen; Sie haben das auch schon gehört. Vorgesehen sind insbesondere Mittel zur Verbesserung der Wettbewerbsfähigkeit der Landwirtschaft, darunter Investitionskredite und Beiträge zur Absatzförderung. Das ist ein erheblicher Betrag. Es geht darum, unseren Landwirtschaftsbetrieben Investitionen, Anpassungen und eine Stärkung ihrer Wettbewerbsfähigkeit zu ermöglichen.
-Für eine vernünftige Wirtschaftspolitik gehört Folgendes zusammen: offene Märkte für unsere exportorientierte Wirtschaft und verlässliche Rahmenbedingungen für unsere Landwirtschaft. Wir sollten die Diskussion über Mercosur auch deshalb nüchtern führen. Es geht um Marktzugang, wirtschaftliche Chancen, konkrete Agrarkontingente und die Abgeltung für die Landwirtschaft. Es geht um weniger "tariffs" - das ist ja der Begriff, den wir kennen - für die EFTA-Länder. Zu Recht wurde gesagt, wir seien mit Südamerika zum Teil auf Trump-Niveau; davon müssen wir wegkommen. Es geht um Arbeitsplätze im Jura. Es geht um Arbeitsplätze im St. Galler Rheintal. Es geht um Arbeitsplätze im Fürstentum Liechtenstein. Es geht um Arbeitsplätze in unserem Land. Es geht um Arbeitsplätze in den angrenzenden Ländern - auch im angrenzenden Ländle. Es geht um Arbeitsplätze in den mit uns via EFTA verbundenen Ländern Island und Norwegen. Nur: Sie können das Abkommen in Kraft setzen, auch wenn wir Nein stimmen, und sie werden das Abkommen in Kraft setzen, auch wenn wir es nicht tun. Meine Damen und Herren gerade von der Opposition: Wollen wir die letzten Mohikaner sein, die mit Mercosur kein Abkommen abschliessen? Wollen Sie das ernsthaft? Wollen Sie die Landwirtschaft plagen? Wollen Sie die Arbeitsplätze gefährden?
+    <t xml:space="preserve">Die SVP-Fraktion wird auf die Vorlage eintreten. Es geht um unsere Unternehmen, es geht um unsere Arbeitsplätze, es geht um Zölle; es geht nicht darum, die Welt zu retten. Der Mercosur umfasst 270 Millionen Menschen. Die Schweiz exportiert bereits heute Waren im Wert von mehr als 4 Milliarden Franken jährlich in die Mercosur-Länder. Mit dem Abkommen sollen rund 96 Prozent unserer Ausfuhren nach Ablauf der vorgesehenen Übergangsfrist zollfrei werden. Das eröffnet unseren Unternehmen zusätzliche M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die SVP-Fraktion wird auf die Vorlage eintreten. Es geht um unsere Unternehmen, es geht um unsere Arbeitsplätze, es geht um Zölle; es geht nicht darum, die Welt zu retten. Der Mercosur umfasst 270 Millionen Menschen. Die Schweiz exportiert bereits heute Waren im Wert von mehr als 4 Milliarden Franken jährlich in die Mercosur-Länder. Mit dem Abkommen sollen rund 96 Prozent unserer Ausfuhren nach Ablauf der vorgesehenen Übergangsfrist zollfrei werden. Das eröffnet unseren Unternehmen zusätzliche Marktchancen und ermöglicht Zollersparnisse von über 155 Millionen Franken pro Jahr.
+Gerade für ein kleines, international ausgerichtetes Land wie die Schweiz ist der Zugang zu ausländischen Märkten von zentraler Bedeutung. Wir können es uns nicht leisten, uns in wichtigen Märkten ins Abseits zu manövrieren, während andere Wirtschaftsräume ihre Beziehungen ausbauen. 
+Natürlich gibt es berechtigte Fragen zur Landwirtschaft; diese müssen wir sehr ernst nehmen. Die SVP-Fraktion nimmt sie ernst. Entscheidend ist für uns deshalb die Frage, wie wir mit den möglichen Auswirkungen auf die Landwirtschaft umgehen. Hier liegt gegenüber der ursprünglichen Vorlage inzwischen eine Lösung auf dem Tisch. Der Ständerat hat insgesamt 517 Millionen Franken für flankierende Massnahmen beschlossen; Sie haben das auch schon gehört. Vorgesehen sind insbesondere Mittel zur Verbesserung der Wettbewerbsfähigkeit der Landwirtschaft, darunter Investitionskredite und Beiträge zur Absatzförderung. Das ist ein erheblicher Betrag. Es geht darum, unseren Landwirtschaftsbetrieben Investitionen, Anpassungen und eine Stärkung ihrer Wettbewerbsfähigkeit zu ermöglichen.
+Für eine vernünftige Wirtschaftspolitik gehört Folgendes zusammen: offene Märkte für unsere exportorientierte Wirtschaft und verlässliche Rahmenbedingungen für unsere Landwirtschaft. Wir sollten die Diskussion über den Mercosur auch deshalb nüchtern führen. Es geht um Marktzugang, wirtschaftliche Chancen, konkrete Agrarkontingente und die Abgeltung für die Landwirtschaft. Es geht um weniger "tariffs" - das ist ja der Begriff, den wir kennen - für die EFTA-Länder. Zu Recht wurde gesagt, wir seien mit Südamerika zum Teil auf Trump-Niveau; davon müssen wir wegkommen. Es geht um Arbeitsplätze im Jura. Es geht um Arbeitsplätze im St.[NB]Galler Rheintal. Es geht um Arbeitsplätze im Fürstentum Liechtenstein. Es geht um Arbeitsplätze in unserem Land. Es geht um Arbeitsplätze in den angrenzenden Ländern - auch im angrenzenden Ländle. Es geht um Arbeitsplätze in den mit uns via EFTA verbundenen Ländern Island und Norwegen. Nur: Sie können das Abkommen in Kraft setzen, auch wenn wir Nein stimmen, und sie werden das Abkommen in Kraft setzen, auch wenn wir es nicht tun. Meine Damen und Herren gerade von der Opposition, wollen wir die letzten Mohikaner sein, die mit dem Mercosur kein Abkommen abschliessen? Wollen Sie das ernsthaft? Wollen Sie die Landwirtschaft plagen? Wollen Sie die Arbeitsplätze gefährden?
 Der Ständerat ist zu durchaus vernünftigen Schlüssen gekommen. Die SVP-Fraktion wird diese unterstützen und nicht das fantasievolle Durcheinander, inklusive Millionenraubzug auf die Steuergelder, das Ihnen von der Aussenpolitischen Kommission des Nationalrates, teils in der Minderheit und teils in der Mehrheit, präsentiert worden ist.
 </t>
   </si>
@@ -349,15 +350,15 @@
   </si>
   <si>
     <t xml:space="preserve">Der Titel dieses Geschäfts täuscht etwas, wir haben hier nur noch einen Punkt zu klären; dahinter steht eine etwas längere Geschichte.
-Am 18. Juni 2023 fanden in mehreren Kantonen Volksabstimmungen statt. In Bern wurde eine Schuldenbremse, in der Waadt ein Klimaartikel und im Kanton Jura ein Amtsenthebungsverfahren für kantonale und kommunale Behördenmitglieder eingeführt. In Genf kamen drei Vorlagen zur Abstimmung; erstens wurde ein Integritätsartikel für die digitale Welt, zweitens ein Recht auf Ernährung und drittens ein neuer Verfassungsartikel eingeführt. Abgesehen von letzterem waren alle diese Punkte unbestritten, und das Parlament hat sie bereits genehmigt, der Ständerat am 10. September 2024 und der Nationalrat am 18. September 2024.
-Die dritte Genfer Vorlage war der neu verfasste Artikel 205 der Genfer Kantonsverfassung. Dieser sieht im neuen Absatz 3 vor, dass der Kanton Genf in Ergänzung zur Bundesgesetzgebung eine durch paritätische Beiträge der Arbeitgeber und Arbeitnehmer finanzierte Mutterschaftsversicherung von mindestens sechzehn Wochen und einen bezahlten Urlaub von mindestens acht Wochen für den anderen Elternteil gewährleistet. Dies soll gemäss Absatz 4 bei Adoptionen und bei der Aufnahme zur dauerhaften Unterbringung, auf Französisch "accueil avec hébergement à caractère permanent", analog gelten. Was die Erweiterung auf sechzehn Wochen Mutterschaftsversicherung betrifft, war die Revision von Beginn weg mit Bundesrecht konform und gemäss Artikel 51 Absatz 2 der Bundesverfassung zu gewährleisten, der Rest jedoch nicht bzw. damals noch nicht.
-Der Nationalrat hat in der Herbstsession 2024 beschlossen, mit der Gewährleistung zuzuwarten, bis das sich damals in Revision befindliche Erwerbsersatzgesetz (EOG) in Kraft ist. Auf der Basis von Artikel 116 Absatz 3 der Bundesverfassung und des EOG wurden einst nicht nur die Mutterschaftsversicherung, sondern in den letzten Jahren auch die Vaterschaftsentschädigung und die Adoptionsentschädigung eingerichtet. Ein Vorbehalt zugunsten der Kantone für eine weitergehende Regelung enthielt das EOG zum Zeitpunkt der Abstimmung in Genf nur im Bereich der Mutterschafts- und der Adoptionsentschädigung, nicht aber im Bereich des Vaterschaftsurlaubs.
-Folglich war der Teil über den achtwöchigen Vaterschaftsurlaub bundesrechtswidrig und durfte zum damaligen Zeitpunkt von uns nicht genehmigt werden. 
+Am 18. Juni 2023 fanden in mehreren Kantonen Volksabstimmungen statt. In Bern wurde eine Schuldenbremse, in der Waadt ein Klimaartikel und im Kanton Jura ein Amtsenthebungsverfahren für kantonale und kommunale Behördenmitglieder eingeführt. In Genf kamen drei Vorlagen zur Abstimmung; erstens wurde ein Integritätsartikel für die digitale Welt, zweitens ein Recht auf Ernährung und drittens ein neuer Verfassungsartikel eingeführt. Abgesehen von Letzterem waren alle diese Punkte unbestritten, und das Parlament hat sie bereits genehmigt, der Ständerat am 10. September 2024 und der Nationalrat am 18. September 2024.
+Die dritte Genfer Vorlage betraf den neu verfassten Artikel 205 der Genfer Kantonsverfassung. Darin ist im neuen Absatz 3 vorgesehen, dass der Kanton Genf in Ergänzung zur Bundesgesetzgebung eine durch paritätische Beiträge der Arbeitgeber und Arbeitnehmer finanzierte Mutterschaftsversicherung von mindestens sechzehn Wochen und einen bezahlten Urlaub von mindestens acht Wochen für den anderen Elternteil gewährleistet. Dies soll gemäss Absatz 4 analog bei Adoptionen und bei der Aufnahme zur dauerhaften Unterbringung, auf Französisch "accueil avec hébergement à caractère permanent", gelten. Was die Erweiterung der Mutterschaftsversicherung auf sechzehn Wochen betrifft, war die Revision von Beginn weg mit Bundesrecht konform und gemäss Artikel 51 Absatz 2 der Bundesverfassung zu gewährleisten, der Rest jedoch nicht bzw. damals noch nicht.
+Der Nationalrat beschloss in der Herbstsession 2024, mit der Gewährleistung zuzuwarten, bis die sich damals in Revision befindlichen Bestimmungen im Erwerbsersatzgesetz (EOG) in Kraft sind.
+Auf der Basis von Artikel 116 Absatz 3 der Bundesverfassung und des EOG wurden einst nicht nur die Mutterschaftsversicherung, sondern in den letzten Jahren auch die Vaterschaftsentschädigung und die Adoptionsentschädigung eingerichtet. Ein Vorbehalt zugunsten der Kantone für eine weitergehende Regelung enthielt das EOG zum Zeitpunkt der Abstimmung in Genf nur im Bereich der Mutterschafts- und der Adoptionsentschädigung, nicht aber im Bereich des Vaterschaftsurlaubs. Folglich war der Teil über den achtwöchigen Vaterschaftsurlaub bundesrechtswidrig und durfte zum damaligen Zeitpunkt von uns nicht genehmigt werden. 
 Die Vorlage wurde im Herbst 2024 auf Antrag der Staatspolitischen Kommission des Ständerates gesplittet: Jener Teil, der höchstens teilweise hätte gewährleistet werden können, wurde aus dem Bundesbeschluss gestrichen und in eine Vorlage 2 verschoben, die heute und jetzt Beratungsgegenstand ist. 
 Der Vaterschaftsurlaub wurde 2021 auf Bundesebene eingeführt. Ab 2023 lief eine Vernehmlassung zu einer Änderung des EOG, die es den Kantonen erlaubt, einen längeren Vaterschaftsurlaub zu gewähren und diesen beispielsweise mit einem kantonalen Zuschlag auf die EO-Beiträge zu finanzieren. 
-Mit Beschlüssen vom 19. Dezember 2025 haben die beiden Räte das Bundesgesetz über den Erwerbsersatz revidiert. Die Referendumsfrist lief am 17. April 2026 ungenutzt ab. Artikel 16mbis sieht nun explizit vor, dass Kantone bei der Versicherung für den anderen Elternteil weiter gehen können als der Bund. Diese Regelung gilt gemäss Artikel 16x auch bei Adoptionen. Folglich wurde nur dieser Punkt bundesrechtskonform. 
-Artikel 205 Absatz 4 der Genfer Kantonsverfassung sieht des Weiteren vor, dass auch für Pflegemütter eine Entschädigungsleistung für mindestens sechzehn Wochen und für Pflegeväter von mindestens acht Wochen auszurichten sei. Für diesen Teil in Artikel 205 der Genfer KV fehlt weiterhin die entsprechende Grundlage im Bundesrecht. 
-Wir sind Zweitrat. Der Ständerat hat diese Änderung am 15. Juni 2026 genehmigt bzw. eben nicht genehmigt. Ihre Staatspolitische Kommission hat sich am 13. August 2026 mit der Angelegenheit befasst. Sie beantragt einstimmig, Artikel 205 Absätze 3 und 4 der in der Volksabstimmung vom 18. Juni 2023 revidierten Genfer KV in den Punkten über die kantonale Versicherung für den anderen Elternteil zu gewährleisten; dies auch bei Adoptionen, nicht aber bei der Aufnahme zur dauerhaften Unterbringung von Pflegekindern. Die Textelemente "ou d'accueil avec hébergement à caractère permanent" und "ou accueillant" dürfen folglich nicht genehmigt werden. 
+Mit Beschlüssen vom 19. Dezember 2025 revidierten die beiden Räte das Bundesgesetz über den Erwerbsersatz. Die Referendumsfrist lief am 17. April 2026 ungenutzt ab. Artikel 16mbis sieht nun explizit vor, dass Kantone bei der Versicherung für den anderen Elternteil weiter gehen können als der Bund. Diese Regelung gilt gemäss Artikel 16x auch bei Adoptionen. Folglich war nun nur dieser Punkt bundesrechtskonform. 
+Artikel 205 Absatz 4 der Genfer Kantonsverfassung sieht des Weiteren vor, dass auch für Pflegemütter eine Entschädigungsleistung von mindestens sechzehn Wochen und für Pflegeväter von mindestens acht Wochen auszurichten sei. Für diesen Teil in Artikel 205 der Genfer Kantonsverfassung fehlt weiterhin die entsprechende Grundlage im Bundesrecht. 
+Wir sind Zweitrat. Der Ständerat hat diese Änderung am 15. Juni 2026 genehmigt bzw. eben nicht genehmigt. Ihre Staatspolitische Kommission hat sich am 13. August 2026 mit der Angelegenheit befasst. Sie beantragt einstimmig, Artikel 205 Absätze 3 und 4 der in der Volksabstimmung vom 18. Juni 2023 revidierten Genfer Kantonsverfassung in den Punkten über die kantonale Versicherung für den anderen Elternteil zu gewährleisten; dies gilt auch bei Adoptionen, nicht aber bei der Aufnahme zur dauerhaften Unterbringung von Pflegekindern. Die Textelemente "ou d'accueil avec hébergement à caractère permanent" und "ou accueillant" dürfen folglich nicht genehmigt werden. 
 Ich bitte Sie, dem Antrag Ihrer SPK zuzustimmen.
 </t>
   </si>
@@ -650,11 +651,11 @@
     <t xml:space="preserve">Würth Benedikt</t>
   </si>
   <si>
-    <t xml:space="preserve">Ich habe vorhin schon erwähnt, dass die APK-S insgesamt einfach eine politische Würdigung in die Richtung vorgenommen hat, dass es für die aussenpolitische Lösung eben auch innenpolitische Begleitmassnahmen braucht und die Sozialpartnerschaft in diesem Zusammenhang sehr wichtig ist. Arbeitsfrieden und Arbeitsethos - dieses möchte ich auch erwähnen - sind wesentliche Elemente unserer Standortgunst. Das ist ein Standortvorteil der Schweiz; darauf sind wir auch stolz. 
-Es war bei diesem Dossier - u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ich habe vorhin schon erwähnt, dass die APK-S insgesamt einfach eine politische Würdigung in die Richtung vorgenommen hat, dass es für die aussenpolitische Lösung eben auch innenpolitische Begleitmassnahmen braucht und die Sozialpartnerschaft in diesem Zusammenhang sehr wichtig ist. Arbeitsfrieden und Arbeitsethos - dieses möchte ich auch erwähnen - sind wesentliche Elemente unserer Standortgunst. Das ist ein Standortvorteil der Schweiz; darauf sind wir auch stolz. 
+    <t xml:space="preserve">Ich habe vorhin schon erwähnt, dass die APK-S insgesamt eine politische Würdigung in die Richtung vorgenommen hat, dass es für die aussenpolitische Lösung eben auch innenpolitische Begleitmassnahmen braucht und die Sozialpartnerschaft in diesem Zusammenhang sehr wichtig ist. Arbeitsfrieden und Arbeitsethos - dies möchte ich auch erwähnen - sind wesentliche Elemente unserer Standortgunst. Das ist ein Standortvorteil der Schweiz; darauf sind wir auch stolz. 
+Es war bei diesem Dossier - um das noch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich habe vorhin schon erwähnt, dass die APK-S insgesamt eine politische Würdigung in die Richtung vorgenommen hat, dass es für die aussenpolitische Lösung eben auch innenpolitische Begleitmassnahmen braucht und die Sozialpartnerschaft in diesem Zusammenhang sehr wichtig ist. Arbeitsfrieden und Arbeitsethos - dies möchte ich auch erwähnen - sind wesentliche Elemente unserer Standortgunst. Das ist ein Standortvorteil der Schweiz; darauf sind wir auch stolz. 
 Es war bei diesem Dossier - um das nochmals zu rekapitulieren - nicht immer so, dass die Sozialpartnerschaft wirklich funktioniert hat. Ich kann mich erinnern: Ich war früher noch teilweise als KDK-Präsident bei den tripartiten Gesprächen dabei, als der Vorgänger von Herrn Maillard, unser ehemaliger Kollege und mein ehemaliger Standeskollege Paul Rechsteiner relativ bzw. ziemlich klar sagte: Ich mache da nicht mehr mit, ich verlasse den Tisch. Sie müssen sich einfach nochmals bewusst sein, wo wir damals waren und wo wir heute sind. 
 Wir haben heute eine Lösung, die in zig Runden verhandelt wurde, wie wir uns haben sagen lassen. Es ist offensichtlich ein mühsamer, aber notwendiger Prozess gewesen. Rechtlich gesehen könnte man einfach vom Ergebnis abweichen. Die APK-S ist aber der Auffassung, dass dies politisch nicht klug wäre; gerade als Ständerat sollten wir das nicht machen. Es ist ein bisschen wie beim Finanzausgleich. Wenn sich die Kantone beim Finanzausgleich verständigen, dann tun wir auch gut daran, das im Parlament nicht zu übersteuern; das kommt nicht gut. Ähnlich ist es auch hier bei der Sozialpartnerschaft. Nachdem wir eine Lösung erzielen konnten bzw. die Sozialpartner eine Lösung erzielen konnten, sollte man dieses Ergebnis nicht einfach torpedieren. Vor diesem Hintergrund haben wir aus einer Gesamtwürdigung dieses ganzen Prozesses entschieden, den Bundesrat zu unterstützen. Ich bitte Sie, dies ebenfalls zu tun. 
 </t>
@@ -763,6 +764,84 @@
 D'autre part, la majorité de la commission a souhaité réintroduire l'obligation du triplement des taxes qui avait été décidé il y a deux ans dans le cadre du message FRI et qui sera désormais limité aux étudiants et étudiantes hors Union européenne. La commission a en effet regretté que le Conseil fédéral soit revenu en arrière par rapport à cette décision. Il n'y a pas de minorité sur ce point, dans la mesure où cette décision, bien que nous l'ayons combattue à l'époque, en appelant de nos voeux l'application de taxes d'études identiques pour l'ensemble du corps estudiantin, a été prise et actée par le Parlement. Rien n'empêche toutefois, à quiconque estime que ce triplement des taxes et cette discrimination des étudiants d'États extraeuropéens, notamment au regard du coût de la vie extrêmement élevé dans notre pays, est injustifié, de soutenir la version du Conseil fédéral.
 Enfin, j'ajoute encore un mot sur la minorité II (Stark). Je suis ravie d'entendre que vous ne souhaitez pas créer des classes différentes parmi les étudiants étrangers et que vous militez pour ne pas différencier entre elles les personnes étrangères et pour appliquer le même traitement à tous. Cela étant, avec votre proposition, vous le savez, nous entrons en contradiction avec les révisions de l'Accord sur la libre circulation des personnes que les négociateurs ont adoptées avec l'Union européenne. Cela créerait une divergence problématique.
 Dès lors, je vous invite à ne pas créer un problème là où il ne doit pas y en avoir. Cette situation va se faire à la satisfaction de tous et toutes. Je vous invite à suivre la majorité de la commission.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne vais pas répéter ce qui a très bien été dit par mes préopinantes et préopinants, mais plutôt revenir sur certains points particuliers. On a dit que la solution suisse pour Erasmus plus n'était pas si mauvaise, si je traduis un peu littéralement. Certes, mais elle n'est pas si géniale non plus. En devant faire usage de cette solution de remplacement, voire de bricolage, la Suisse s'est maintenue dans un statut peu satisfaisant de "junior partner". Cela lui a permis de promouvoir des activit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne vais pas répéter ce qui a très bien été dit par mes préopinantes et préopinants, mais plutôt revenir sur certains points particuliers. On a dit que la solution suisse pour Erasmus plus n'était pas si mauvaise, si je traduis un peu littéralement. Certes, mais elle n'est pas si géniale non plus. En devant faire usage de cette solution de remplacement, voire de bricolage, la Suisse s'est maintenue dans un statut peu satisfaisant de "junior partner". Cela lui a permis de promouvoir des activités de mobilité, certes. Par contre, pour tous les autres volets d'Erasmus plus, que sont par exemple la coopération, l'innovation, l'excellence et l'expertise, notre pays a manqué la grande majorité des opportunités, y compris celle de proposer et de diriger des programmes dans le cadre d'Erasmus plus.
+La solution suisse, qui se concentre sur la mobilité, n'exploite environ qu'un tiers des opportunités d'Erasmus plus. L'augmentation du financement, en revanche, si l'on acceptait ce crédit, permettrait aux acteurs et actrices suisses de bénéficier de la totalité du dispositif. Il faut relever que la Suisse, dans sa participation aux programmes de recherche et d'innovation en général, est particulièrement performante pour décrocher des financements européens, pour capter des mannes financières et ainsi, assurer qu'une partie des montants européens dédiés à la recherche et à la formation viennent dans notre pays. Peut-être que celles et ceux d'entre vous qui ont eu la curiosité ou la patience de lire le message du Conseil fédéral jusqu'au bout auront vu que des tableaux figurent aux pages 1073 et suivantes de la version française du message présentent une comparaison entre la solution Erasmus plus complète et la solution suisse. Ces personnes auront vu combien notre pays manque des pans entiers de ce programme.
+Je rappelle également que l'arrêté 9 qu'on est appelés à approuver ou non aujourd'hui concerne uniquement la période actuelle jusqu'à fin 2027. Cela constituera-t-il un signal positif ou négatif pour l'année prochaine, pour la prochaine génération de programmes ? Oui, c'est évident, mais la décision d'aujourd'hui ne présume pas de futures décisions concernant l'association à la prochaine génération de programmes. Les personnes sceptiques face à la pertinence pour la Suisse de s'associer à ce programme pourront manifester ces doutes lorsque nous aurons sur la table le message du Conseil fédéral pour l'association à la prochaine génération. C'est à ce moment qu'il faudra exprimer notre volonté ou non de poursuivre notre collaboration dans le cadre d'Erasmus plus. 
+M. Pierre-Yves Maillard a dit cette semaine "pacta sunt servanda". J'aurais envie d'employer une formule encore plus simple, c'est "dire ce qu'on fait et faire ce qu'on dit", c'est-à-dire qu'une "réassociation" au programme de l'Union européenne de manière provisoire depuis 2025 ouvrait aussi la participation à Erasmus plus à partir de 2027. C'est dans ce cadre et dans cet esprit que nous devons adopter cet arrêté fédéral.
+Je rappelle également que l'association bénéficie d'un très large soutien. Les cantons qui se sont exprimés dans la consultation ont tous soutenu la "réassociation" à Erasmus plus. Nous avons vu que ce sont de nombreuses organisations du domaine de l'éducation, mais également du sport et des organisations de jeunesse, qui sont concernées.
+C'est peut-être le moment de dissiper un doute. Les cinéphiles d'entre vous se souviennent peut-être du film sympathique "L'Auberge espagnole", qui, tout sympathique qu'il était, avait peut-être imprimé durablement une image pas tout à fait complète de ce qu'est Erasmus. Je tiens à rappeler que ce programme ne concerne pas que les étudiants du domaine universitaire : il concerne également la formation professionnelle et l'enseignement scolaire, que ce soit l'école obligatoire ou secondaire II. Cela concerne également la formation continue, la formation des adultes et - comme dit - les activités de jeunesse et aussi le sport.
+Il faut peut-être rappeler que la décision de la Commission de la science, de l'éducation et de la culture est intervenue ce printemps et que les perspectives budgétaires étaient encore largement méconnues. Entre-temps, nous avons reçu le projet de budget 2027 du Conseil fédéral qui, comme cela a été dit, prévoit d'intégrer le financement d'Erasmus plus ; une hausse de 1,3 pour cent pour le domaine FRI, qui englobe évidemment la contribution à Erasmus, mais également d'autres secteurs de ce domaine FRI.
+Je rappelle enfin que la Commission des affaires étrangères du Parlement européen a approuvé les accords le 10 septembre dernier et qu'en cas de refus de s'associer à Erasmus, la Suisse deviendrait le seul pays d'Europe continentale à ne pas faire partie de ce programme et de ce réseau, ce qui constituerait un handicap de taille pour notre pays. L'Union européenne apprécie la Suisse, cela a été dit à la conférence de presse qui a suivi l'approbation du paquet d'accords par la Commission des affaires étrangères du Parlement européen ; cela ne fait aucun doute. Nos relations sont étroites et fructueuses. Elles sont mutuellement bénéfiques.
+Ce serait faire preuve au mieux de naïveté, au pire d'une hubris mal placée, que de croire que la patience de l'Union européenne à l'égard de nos tergiversations ne finira pas par se tarir. Rester à l'écart d'Erasmus plus n'est bon ni pour la Suisse ni pour nos relations avec l'Union européenne. Le jeu n'en vaut pas la chandelle. C'est pourquoi je vous invite instamment à adopter l'arrêté fédéral 9.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oui, je vous invite vraiment à vous rallier à la proposition de la majorité de la commission. 
+On parle de "Swiss finish" quand il s'agit de l'article 12, mais c'est le "Swiss finish" actuel, c'est le droit en vigueur. La modification qui est proposée à l'article 12 alinéa 2 lettre a, c'est uniquement pour se conformer au résultat des négociations et au fait que le droit suisse en vigueur protège les consommateurs et les consommatrices en obligeant à indiquer le pays de provenance. On est donc l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oui, je vous invite vraiment à vous rallier à la proposition de la majorité de la commission. 
+On parle de "Swiss finish" quand il s'agit de l'article 12, mais c'est le "Swiss finish" actuel, c'est le droit en vigueur. La modification qui est proposée à l'article 12 alinéa 2 lettre a, c'est uniquement pour se conformer au résultat des négociations et au fait que le droit suisse en vigueur protège les consommateurs et les consommatrices en obligeant à indiquer le pays de provenance. On est donc là dans une proposition d'opportunité qui vise à affaiblir le droit suisse en vigueur, qui n'a pas de rapport, matériellement, avec les accords qui ont été négociés. Au contraire, l'exception que les négociateurs et négociatrices suisses ont obtenue, c'est justement pour que le droit suisse en vigueur puisse continuer de s'appliquer. L'obligation de renseigner sur le pays de provenance est évidemment un plus pour les consommateurs et les consommatrices, pour leur information. On sait, ces dernières années, combien de scandales en matière alimentaire il y a eu. Je crois que c'est une volonté de la population, mais la grande distribution est, en général, plutôt contente aussi de pouvoir signaler ce genre d'information, conformément au droit à l'information. C'est aussi, pour l'agriculture de notre pays, une manière de signaler - l'information figurant clairement sur les produits importés - que ces denrées alimentaires ne sont pas produites en Suisse. 
+Dès lors, je vous invite à ne pas affaiblir le droit en vigueur et, pour ce faire, à vous rallier à la proposition de la majorité de la commission.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À l'article 41, la majorité entend entraver les compétences du Conseil fédéral en matière de contrôle des denrées alimentaires en biffant les lettres c et d. Ainsi, contrairement au projet présenté, le Conseil fédéral ne pourrait plus décider de réaliser des contrôles de catégories de produits dans le cadre de programmes d'analyse.
+Je rappelle que la lettre c met en oeuvre les recommandations du Contrôle fédéral des finances, qui visent à fixer des objectifs pour la réalisation de contrôles de p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À l'article 41, la majorité entend entraver les compétences du Conseil fédéral en matière de contrôle des denrées alimentaires en biffant les lettres c et d. Ainsi, contrairement au projet présenté, le Conseil fédéral ne pourrait plus décider de réaliser des contrôles de catégories de produits dans le cadre de programmes d'analyse.
+Je rappelle que la lettre c met en oeuvre les recommandations du Contrôle fédéral des finances, qui visent à fixer des objectifs pour la réalisation de contrôles de produits. Le fait que le Conseil fédéral disposera de cette compétence à l'avenir est important ; d'autant plus important que l'article 58 de la loi sur les denrées alimentaires prévoit que les autorités fédérales collaborent "avec les institutions et organes spécialisés étrangers et internationaux". Cette nouvelle compétence permet de garantir que la Suisse participe à des programmes de contrôle coordonnés, par exemple le programme national d'analyse et de détection de substances étrangères. Il s'agit aussi de lutter contre les fraudes et d'essayer de combattre la criminalité liée aux denrées alimentaires. Pour ce faire, il est important de pouvoir agir de façon coordonnée en cas de soupçons d'infraction.
+Ainsi, en biffant la lettre d, c'est-à-dire en privant le Conseil fédéral de la possibilité d'obliger les autorités cantonales d'exécution de signaler des cas manifestes et graves de fraude ou d'infraction à la loi sur les denrées alimentaires, on entrave cette collaboration et cette possibilité d'avoir un signalement fluide, un flux fluide d'informations.
+Ainsi, je vous invite à en rester à la version du Conseil fédéral en adoptant la proposition de la minorité.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je dois vous avouer que j'aurais souhaité que cette motion soit transmise en commission ; cela nous aurait permis, peut-être, de l'aborder sous différents angles, mais la proposition n'a pas été faite et je crois savoir que l'auteur de la motion n'était pas très disposé à ce qu'elle le soit. Pour ma part, je suis partagé. Partagé, non pas sur le fond de la question, parce que j'ai les mêmes craintes que M. Chiesa, les mêmes craintes que celles exprimées par notre collègue Poggia, mais plutôt sur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je dois vous avouer que j'aurais souhaité que cette motion soit transmise en commission ; cela nous aurait permis, peut-être, de l'aborder sous différents angles, mais la proposition n'a pas été faite et je crois savoir que l'auteur de la motion n'était pas très disposé à ce qu'elle le soit. Pour ma part, je suis partagé. Partagé, non pas sur le fond de la question, parce que j'ai les mêmes craintes que M. Chiesa, les mêmes craintes que celles exprimées par notre collègue Poggia, mais plutôt sur la procédure. Est-ce qu'il faut stopper ici, tout de suite, par l'acceptation de cette motion, toute discussion possible avec la France ou est-ce qu'il faut accepter d'entrer en discussion selon le droit encore actuel ? Il reste à préciser, j'espère par le Conseil fédéral, si c'est encore ce droit-là qui s'appliquera ou si, avec les nouveaux accords, comme l'a dit M. Poggia, ce sera automatiquement le droit suisse qui s'appliquera aux frontaliers, avec toutes les conséquences que cela peut avoir. Est-ce que ce sera le plus bel exemple, ou le premier exemple, d'un différend entre l'application du droit suisse et l'application du droit européen, avec un processus de règlement des différends et la question d'éventuelles compensations qui pourrait se poser ? J'ai un doute. Je vais écouter ce que nous dira le Conseil fédéral en la matière.
+S'il est vrai qu'appliquer le droit suisse dans sa plénitude aux chômeurs frontaliers, en soi et intellectuellement, peut paraître normal, équitable et équilibré, je crois qu'il faut voir la réalité du terrain. Quand il s'agira de certifier que les chômeurs frontaliers manifestent de l'intérêt pour rechercher des emplois valables, des emplois qu'ils ne pourraient pas refuser en vertu et en application du droit suisse, il y a une forte crainte, quand même, qu'il y ait deux poids et deux mesures dans l'application du droit suisse selon que nous habitions de ce côté-ci de la frontière, à proximité des contrôleurs des ORP ou du contrôle social qui se fait presque indirectement, notamment dans des régions un peu moins peuplées que les villes. Mais pour aller chercher ces mêmes renseignements de l'autre côté de la frontière, je le dis franchement et même un peu crûment, je souhaite bonne chance pour arriver à les obtenir.
+À ce stade, je dirais que, sur le fond, je suis prêt à accepter cette motion, sauf si le Conseil fédéral arrive à me convaincre que cela n'est pas nécessaire.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme l'a dit le rapporteur, nous terminons aujourd'hui la discussion sur les PFAS que nous avions entamée lors de la première semaine de session. C'est un peu malheureux que cette discussion ait été scindée en deux, puisque cela dépendait des compétences départementales, mais cela souligne bien combien la problématique est large et concerne une multitude de domaines qui vont de la santé humaine à la pollution des sols et des eaux, en passant par la sécurité alimentaire.
+La majorité de la commis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme l'a dit le rapporteur, nous terminons aujourd'hui la discussion sur les PFAS que nous avions entamée lors de la première semaine de session. C'est un peu malheureux que cette discussion ait été scindée en deux, puisque cela dépendait des compétences départementales, mais cela souligne bien combien la problématique est large et concerne une multitude de domaines qui vont de la santé humaine à la pollution des sols et des eaux, en passant par la sécurité alimentaire.
+La majorité de la commission, à l'instar du Conseil fédéral, propose d'attendre paisiblement les résultats des processus déjà mis en oeuvre, à savoir la mise en oeuvre de la motion 25.3421, "Fixer des valeurs limites pertinentes pour les PFAS en tenant compte des conséquences pour l'agriculture et les distributeurs d'eau et introduire des mesures de soutien à l'agriculture", et du plan d'action pour la réduction de l'exposition de l'homme et de l'environnement aux substances chimiques persistantes.
+J'aimerais rappeler que l'argument selon lequel nous avons donné les mandats nécessaires et qu'il faut laisser le Conseil fédéral faire son travail est un argument à géométrie très variable et que notre conseil n'hésite pas, assez régulièrement, sur d'autres thèmes, et notamment concernant l'environnement, à adopter plusieurs textes alors que des travaux législatifs sont déjà en cours. On pense notamment au domaine du loup, où on a empilé les motions alors qu'on avait déjà donné des mandats très clairs au Conseil fédéral. L'argument qui est employé, dans ces cas, est qu'il faut mettre une certaine pression au regard de l'urgence d'agir et donner des orientations plus précises au Conseil fédéral.
+Cet argument s'applique tout à fait dans le cas présent pour les PFAS. En effet, il ne se passe pas une semaine sans que des informations plutôt alarmantes, je dirais, ne fassent surface par rapport aux PFAS, que ce soit concernant l'ampleur de la contamination ou la dangerosité de ces substances pour la santé environnementale, animale et humaine. Parallèlement, je rappelle aussi que nous avons donné le mandat au Conseil fédéral d'adapter à la hausse les valeurs limites de manière à ce que les produits contaminés - on se rappelle que l'origine de toute cette histoire est de la viande saint-galloise - rentrent à nouveau dans les valeurs admises. Il serait donc bon aussi de donner quelques orientations dans la politique de gestion des PFAS qui n'aillent pas dans le sens d'un affaiblissement de la législation.
+Ainsi, l'approche proposée par la motion Graf Maya 25.3746 - puisque c'est celle-là que je défends plus spécifiquement - est raisonnable. Elle fait appel à un principe qui est bien connu de la législation sur l'environnement, celui du pollueur-payeur. Quiconque emploie des substances nuisibles à la santé et à l'environnement doit également en supporter les coûts. Il en va aussi de la santé des finances publiques, car les coûts générés par les contaminations échoient encore très largement aux collectivités publiques.
+Enfin, j'aimerais rappeler qu'une taxe à la source a un effet incitatif assez simple, qui est celui de rediriger les domaines concernés vers des alternatives qui sont moins problématiques. Elle a ainsi pour effet d'encourager la recherche et l'innovation.
+Pour limiter les coûts susmentionnés pour les entreprises par l'instauration d'une taxe, cette mesure serait idéalement couplée à la limitation des PFAS aux usages essentiels. C'est le but de la motion 25.3868 que j'ai déposée, qui aurait ce double effet de stimuler encore une fois la recherche et l'innovation, de rediriger les entreprises - sans créer d'interdiction - vers des alternatives qui sont plus compétitives économiquement aussi et qui sont meilleures pour l'environnement et la santé humaine.
+J'aimerais encore rappeler que ces motions sur les PFAS ont reçu un large soutien. Vous avez toutes et tous reçu un certain nombre de courriers. Ce sont notamment les villes suisses, mais également les communes suisses qui relèvent que les communes se trouvent souvent en bout de chaîne pour supporter les dégâts, qui sont notamment causés à l'eau potable, et pour assumer les conséquences techniques, organisationnelles et financières des pollutions. Elles appellent aussi de leurs voeux une législation plus claire et plus stricte sur le plan fédéral pour les aider à faire face à ces problématiques. La Fédération suisse de pêche prône aussi une taxe sur l'utilisation de l'ensemble des PFAS, relevant que cela constitue une étape importante pour atténuer les coûts sociaux liés à l'assainissement et à la dépollution en raison des PFAS. La Fédération des industries alimentaires suisses, qui est présidée par notre collègue Petra Gössi, a aussi fait part de ses inquiétudes quant à la multiplication des PFAS et appelé à soutenir plusieurs des motions qui sont soumises aujourd'hui.
+Je rappelle encore le rapport du Conseil fédéral rédigé en réponse au postulat Clivaz Christophe 20.4087, qui faisait état de la possibilité ou jugeait qu'il était réalisable de mettre en oeuvre une taxe sur les PFAS à moyen terme. Je rappelle aussi les travaux qui sont en cours dans l'Union européenne. Si l'Union européenne venait à adopter une telle taxe, qui est actuellement en discussion comme de nombreuses autres mesures, l'adoption de cette motion permettrait d'anticiper les changements nécessaires et de mettre en oeuvre les travaux préparatoires.
+Vous l'avez compris, je vous demande de tenir compte à la fois du risque que présentent les PFAS à de multiples égards et peut-être aussi, d'entendre les préoccupations qui viennent de nombreux domaines, non pas seulement des domaines spécifiquement écologiques, mais aussi de nombreux domaines de la consommation et de la grande distribution quant à la dangerosité de ces substances.
+Je vous invite donc à adopter l'ensemble de ces motions.
 </t>
   </si>
 </sst>
@@ -817,8 +896,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I40" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I45" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I45"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -2274,6 +2353,151 @@
         <v>161</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C41" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" t="s">
+        <v>163</v>
+      </c>
+      <c r="I41" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" t="s">
+        <v>12</v>
+      </c>
+      <c r="H42" t="s">
+        <v>166</v>
+      </c>
+      <c r="I42" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>168</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43" t="s">
+        <v>169</v>
+      </c>
+      <c r="I43" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>171</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44" t="s">
+        <v>172</v>
+      </c>
+      <c r="I44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" t="s">
+        <v>12</v>
+      </c>
+      <c r="H45" t="s">
+        <v>175</v>
+      </c>
+      <c r="I45" t="s">
+        <v>176</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -842,6 +842,47 @@
 Je rappelle encore le rapport du Conseil fédéral rédigé en réponse au postulat Clivaz Christophe 20.4087, qui faisait état de la possibilité ou jugeait qu'il était réalisable de mettre en oeuvre une taxe sur les PFAS à moyen terme. Je rappelle aussi les travaux qui sont en cours dans l'Union européenne. Si l'Union européenne venait à adopter une telle taxe, qui est actuellement en discussion comme de nombreuses autres mesures, l'adoption de cette motion permettrait d'anticiper les changements nécessaires et de mettre en oeuvre les travaux préparatoires.
 Vous l'avez compris, je vous demande de tenir compte à la fois du risque que présentent les PFAS à de multiples égards et peut-être aussi, d'entendre les préoccupations qui viennent de nombreux domaines, non pas seulement des domaines spécifiquement écologiques, mais aussi de nombreux domaines de la consommation et de la grande distribution quant à la dangerosité de ces substances.
 Je vous invite donc à adopter l'ensemble de ces motions.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amaudruz Céline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réunie le 21 août 2026, la Commission de la sécurité sociale et de la santé publique du Conseil national (CSSS-N) a examiné l'opportunité de classer l'initiative 19.320 du canton du Jura, "Stopper une évolution scandaleuse des prix des médicaments". L'initiative, comme vous le savez, vise à édicter de nouvelles bases légales donnant les moyens à l'Office fédéral de la santé publique de stopper la hausse des prix des médicaments, notamment des médicaments destinés au traitement du cancer, et à te</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réunie le 21 août 2026, la Commission de la sécurité sociale et de la santé publique du Conseil national (CSSS-N) a examiné l'opportunité de classer l'initiative 19.320 du canton du Jura, "Stopper une évolution scandaleuse des prix des médicaments". L'initiative, comme vous le savez, vise à édicter de nouvelles bases légales donnant les moyens à l'Office fédéral de la santé publique de stopper la hausse des prix des médicaments, notamment des médicaments destinés au traitement du cancer, et à terme, de les faire baisser dans une mesure conforme à la raison. Je ne reviendrai pas sur le fond de cette initiative dans la mesure où nous en avons d'ores et déjà discuté. Je me permettrai peut-être un récapitulatif chronologique.
+La Commission de la sécurité sociale et de la santé publique du Conseil des États (CSSS-E) a donné suite à l'initiative le 13 avril 2021, par 11 voix contre 0 et 1 abstention. La CSSS-N a également donné suite à cette initiative le 13 janvier 2022, par 12 voix contre 10 et 2 abstentions. Le Conseil des États a alors été désigné comme conseil prioritaire pour son examen.
+L'examen de l'initiative du canton du Jura a toujours été lié au deuxième volet de mesures visant à freiner la hausse des coûts dans le domaine de la santé. La CSSS-E a donné suite à l'initiative dans l'intention d'examiner son objectif dans le cadre de ce deuxième volet de mesures. C'est la raison pour laquelle elle n'a pas commencé les travaux d'élaboration d'un projet d'acte visant à mettre en oeuvre cette initiative. Elle souhaitait attendre l'adoption du deuxième volet de mesures. Le 30 janvier 2024, elle a donc proposé à son conseil, à l'unanimité, de prolonger le délai de traitement de l'initiative. À l'époque, la CSSS-E était encore en plein examen du deuxième volet de mesures visant à freiner la hausse des coûts dans le domaine de la santé. Le 5 mars 2024, le Conseil des États a suivi cette proposition sans opposition.
+Le 27 janvier 2026, la CSSS-E s'est à nouveau penchée sur l'initiative. Par 6 voix contre 4 et 1 abstention, elle a proposé à son conseil de classer l'initiative, le Parlement ayant entre-temps adopté le deuxième volet de mesures visant à freiner la hausse des coûts dans le domaine de la santé.
+Le 3 mars 2026, le Conseil des États a suivi cette proposition sans opposition.
+La majorité de la commission propose de classer l'initiative, le Parlement ayant adopté au printemps 2025 le deuxième volet de mesures visant à freiner la hausse des coûts dans le domaine de la santé, dont une partie importante concerne les médicaments. Les mesures adoptées s'attaquent à différentes problématiques. Grâce à un examen différencié des critères d'efficacité, d'adéquation et d'économicité, il s'agit notamment de garantir l'approvisionnement en génériques ou en autres médicaments peu coûteux. Les modèles d'impact budgétaire, quant à eux, visent à freiner la hausse des coûts des médicaments bien établis, générant un chiffre d'affaires important. En outre, l'inscription dans la loi des modèles de prix déjà pratiqués et un nouveau modèle de remboursement des médicaments dès le premier jour de l'autorisation doivent garantir l'accès aux médicaments innovants.
+Pour la majorité de la commission, il est incontestable qu'il faut, malgré ces mesures, poursuivre les efforts pour freiner la hausse des coûts dans le domaine des médicaments et que toutes les questions portant sur l'accès aux médicaments ou leur approvisionnement ne sont pas réglées. Elle estime toutefois que l'objectif de l'initiative du canton du Jura a été pris en considération dans le deuxième volet de mesures visant à freiner la hausse des coûts et que l'initiative peut donc être classée.
+La minorité de la commission souligne que le problème des prix élevés, voire excessifs, des médicaments est toujours d'actualité en dépit de l'adoption par le Parlement du deuxième volet de mesures visant à freiner la hausse des coûts dans le domaine de la santé. Selon elle, les débats sur les répercussions de la politique des États-Unis dans ce domaine montrent que les prix des médicaments restent sous pression. C'est pourquoi elle estime que classer l'initiative maintenant enverrait un mauvais signal. Il faut continuer de tout mettre en oeuvre pour que les assurés et les assurées ne payent pas les médicaments au prix fort. Pour ces raisons, la minorité propose de ne pas classer l'initiative.
+La commission vous recommande de classer l'initiative, par 17 voix contre 7.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weichelt Manuela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon canton nage dans l'argent des riches, qu'ils soient étrangers ou Suisses, provenant d'autres cantons, attirés par le fisc zougois. Le canton du Jura est un canton qui doit se débattre avec une situation financière beaucoup plus compliquée. Il entend sa population qui souffre et il nous demande quelque chose de simple : la hausse du prix des médicaments doit être stoppée. Nous devons l'écouter attentivement et répondre à cette demande. La majorité de la commission ne l'a malheureusement pas f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon canton nage dans l'argent des riches, qu'ils soient étrangers ou Suisses, provenant d'autres cantons, attirés par le fisc zougois. Le canton du Jura est un canton qui doit se débattre avec une situation financière beaucoup plus compliquée. Il entend sa population qui souffre et il nous demande quelque chose de simple : la hausse du prix des médicaments doit être stoppée. Nous devons l'écouter attentivement et répondre à cette demande. La majorité de la commission ne l'a malheureusement pas fait.
+La majorité propose de classer l'initiative du canton du Jura, car le Parlement aurait adopté des mesures importantes dans le domaine des médicaments au printemps 2025, dans le cadre du deuxième volet de mesures visant à freiner la hausse des coûts. C'est une grande hypocrisie que de prétendre cela.
+Selon son communiqué de presse du 21 août 2026, la commission a, en effet, recommandé au Conseil fédéral d'attendre avant d'adopter la plupart des modifications d'ordonnances visant à mettre en oeuvre les rabais de quantité et d'autres nouvelles mesures dans le domaine des médicaments.
+Nous avons appris mardi que la hausse des primes d'assurance-maladie sera de 5 pour cent. La hausse du prix des médicaments est à nouveau responsable, pour une part, de cette explosion des primes. Même la très libérale "NZZ" a dénoncé les marges de bénéfices sur les médicaments contre le cancer. Elle a écrit il y a un an que les chiffres qu'elle a recueillis montrent que les bénéfices des grands laboratoires pharmaceutiques ne sont que partiellement consacrés à la recherche et au développement et que ce sont surtout les actionnaires qui profitent de dividendes en constante augmentation.
+La "NZZ" en déduit donc qu'il y aurait une marge de manoeuvre pour compenser la pression sur les prix aux États-Unis.
+Conclusion : nous avons décidé des mesures au printemps 2025, qui n'ont pas été mises en oeuvre et qui n'auront que peu d'effet. Le code pénal suisse réprime l'omission de porter secours. Le Parlement n'a moralement pas le droit d'ignorer et de classer l'initiative déposée par le canton du Jura. Le Parlement jurassien compte sur nous. Il nous l'a écrit il y a deux jours.
+Je vous remercie de suivre la minorité de la commission.
+Für die Deutschschweizerinnen und Deutschschweizer: Ich bitte Sie, die Standesinitiative Jura zu unterstützen. 
 </t>
   </si>
 </sst>
@@ -896,8 +937,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I45" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I45"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I47" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I47"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -2498,6 +2539,64 @@
         <v>176</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>177</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" t="s">
+        <v>178</v>
+      </c>
+      <c r="E46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" t="s">
+        <v>179</v>
+      </c>
+      <c r="I46" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>181</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" t="s">
+        <v>182</v>
+      </c>
+      <c r="E47" t="s">
+        <v>130</v>
+      </c>
+      <c r="F47" t="s">
+        <v>156</v>
+      </c>
+      <c r="G47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" t="s">
+        <v>183</v>
+      </c>
+      <c r="I47" t="s">
+        <v>184</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
